--- a/spib_en_fr.xlsx
+++ b/spib_en_fr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,125 +424,130 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>pib_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>bank_number_en</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>bank_number_fr</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>entry_id_en</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>entry_id_fr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>entry_title_en</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>entry_title_fr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>description_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>description_fr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>note_en</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>note_fr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>date_last_modified</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>class_of_individuals_en</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>class_of_individuals_fr</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>purpose_en</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>purpose_fr</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>consistent_uses_en</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>consistent_uses_fr</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>retention_disposal_en</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retention_disposal_fr</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rda_number_en</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>rda_number_fr</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>related_record_number_en</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>related_record_number_fr</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>url_en</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>url_fr</t>
         </is>
@@ -556,117 +561,120 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>PSU 901</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>psu901</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>pou901</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Access to Information Act and Privacy Act Requests</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Demandes en vertu de la Loi sur l’accès à l’information et de la Loi sur la protection des renseignements personnels</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>This bank describes information that is related to formal requests for access to information and, access to or correction of personal information made by individuals in accordance with the Access to Information Act and the Privacy Act. The personal information may include: name, contact information, credit information, identification numbers, Social Insurance Number (SIN) and other processing information related to the request, as well as personal information contained in institution records that are relevant to the request.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information liée aux demandes officielles d’accès à l’information et aux demandes d’accès ou de correction de renseignements personnels formulées par des personnes en vertu de la Loi sur l’accès à l’information et de la Loi sur la protection des renseignements personnels. Les renseignements personnels peuvent comprendre des noms, des coordonnées, des renseignements de solvabilité, des numéros d’identification, des numéros d’assurance sociale (NAS) et d’autres renseignements sur le traitement des demandes, ainsi que des renseignements personnels contenus dans des dossiers institutionnels pertinents aux demandes.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bank formerly called Access to Information and Privacy Requests. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Fichier auparavant intitulé Accès à l’information et la protection des renseignements personnels. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Individuals and their representatives who make formal requests to either obtain information or correct personal information under the control of the government institution.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Les personnes et leurs représentants qui soumettent des demandes officielles soit pour obtenir de l’information, des renseignements ou corriger des renseignements personnels relevant d’une institution fédérale.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>The personal information is used to process and respond to formal requests made under the Access to Information Act and the Privacy Act, including subsequent complaints, investigations and judicial review when applicable. Personal information is collected pursuant to section 13 of the Privacy Act, sections 8 and 11 of the Privacy Regulations, sections 6 and 11 of the Access to Information Act and section 4 of the Access to Information Regulations. The SIN is collected when required to locate personal information held by a program authorized through legislation or policy approval to use the SIN.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour traiter les demandes officielles – et y répondre – formulées en vertu de la Loi sur l’accès à l’information et de la Loi sur la protection des renseignements personnels, y compris, le cas échéant, les plaintes, enquêtes et demandes de révision judiciaire subséquentes. Les renseignements personnels sont recueillis en vertu de l’article 13 de la Loi sur la protection des renseignements personnels, des articles 8 et 11 du Règlement sur la protection des renseignements personnels, des articles 6 et 11 de la Loi sur l’accès à l’information et de l’article 4 du Règlement sur l’accès à l’information. Le NAS est recueilli lorsqu’il est nécessaire pour repérer des renseignements personnels détenus dans le cadre d’un programme qui, en vertu d’une loi ou d’une politique, est autorisé à utiliser le NAS.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Information may be shared with other government institutions during consultations required to process and respond to formal requests made under the Acts. Information may be shared with the Office of the Privacy Commissioner during investigations, refer to Privacy Complaints and Investigations – OPC PPU 005 and Privacy Commissioner Ad Hoc – Complaints and Investigations – OPC PPU 008 . Information may be shared with the Office of the Information Commissioner during investigations, refer to Complaint Investigations – OIC PPU 3100 and Ad Hoc Information Commissioner Complaint Investigations – OIC PPU 123 . Personal information may be shared with a government institution providing internal support services in accordance with section 29.2 of the Financial Administration Act. For information about the internal support services used, please contact the institution’s Access to Information and Privacy Coordinator. The information may be used for planning and evaluation purposes. Depersonalized and aggregated information is used to report to Parliament on the administration of the Access to Information Act and the Privacy Act.  |  Links: Privacy Complaints and Investigations – OPC PPU 005 (https://www.priv.gc.ca/au-ans/atip-aiprp/infosource_e.asp); Privacy Commissioner Ad Hoc – Complaints and Investigations – OPC PPU 008 (https://www.priv.gc.ca/au-ans/atip-aiprp/infosource_e.asp); Complaint Investigations – OIC PPU 3100 (http://www.oic-ci.gc.ca/eng/info-source.aspx); Ad Hoc Information Commissioner Complaint Investigations – OIC PPU 123 (http://www.oic-ci.gc.ca/eng/info-source.aspx)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>PRN 930</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>NDP 930</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu901</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou901</t>
         </is>
@@ -680,117 +688,120 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>PSU 931</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>psu931</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>pou931</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Comptes créditeurs</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>This bank describes information related to individuals who are issued payments by government institutions, including by the Receiver General for Canada. Payments may be issued in any form of payment approved by the Canadian Payment Association established under the Canadian Payments Act. Payments maybe in respect of: travel and hospitality claims, education course fees, program payments, isolation allowances, membership fees, awards, ex gratia, and other sundry payments. Personal information may include: name, contact information, financial information, nature of expenses/claim, employee identification number, other identifying numbers, signature, and Social Insurance Number (SIN).</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Ce fichier décrit des renseignements personnels concernant des personnes à qui des institutions fédérales, dont le Receveur général du Canada, ont émis des paiements. Les paiements peuvent revêtir n’importe lequel des modes de paiement approuvés par l’Association canadienne des paiements en vertu de la Loi canadienne sur les paiements. Les paiements peuvent comprendre des demandes de remboursement de frais de voyage et d’accueil ou de frais de cours, des paiements de programmes, d’indemnité d’isolement, de frais d’adhésion, de bourses, de compensation à titre gracieux et d’autres paiements divers. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements financiers, la nature des dépenses/des demandes de prestations, le numéro d’identification d’employé, d’autres numéros d’identification, la signature et le numéro d’assurance sociale (NAS).</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Individuals seeking access to this bank should specify whether they are an employee, claimant from the general public, contractor or representative of a company, corporation or association, and provide details of the payment such as amount, type, date(s), payment number, and type of program or service and name of institution. Personal information may be found in the institution’s Financial Management Systems and/or in Public Works and Government Services Canada’s Standard Payment System. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Les personnes qui désirent avoir accès à ce fichier doivent spécifier si elles sont des employés, des membres du grand public, des entrepreneurs ou des représentants d’une société, d’une corporation ou d’une association et fournir les détails du paiement, comme le montant, le type, la ou les dates, le numéro du paiement, le type du programme ou du service et le nom de l’institution. Les renseignements personnels peuvent se trouver dans les systèmes de gestion financière de l’institution ou dans le Système normalisé des paiements de Travaux publics et Services gouvernementaux Canada. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions; claimants from the general public, contractors, and representatives of companies, corporations, and associations.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Les employés actuels ou anciens d’institutions fédérales; les demandeurs dans le grand public, les entrepreneurs, et les représentants des sociétés, des corporations et des associations.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Personal information is used to support the payment of financial benefits and entitlements in relation to expenses, fees, claims and other non-payroll payments. For many institutions, personal information is collected pursuant to sections 33 and 34 of the Financial Administration Act (FAA). For those institutions not subject to the FAA, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection. The SIN is collected pursuant to the Income Tax Act and may be used to issue various income reporting slips.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont recueillis afin d’appuyer le paiement des avantages financiers et des versements se rapportant aux dépenses, aux frais, aux demandes de prestations et aux paiements autres que les salaires. Pour plusieurs institutions, les renseignements personnels sont recueillis en vertu des articles 33 et 34 de la Loi sur la gestion des finances publiques (LGFP). En ce qui concerne les institutions qui ne sont pas assujetties à la LGFP, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte. Le NAS est recueilli conformément à la Loi de l’impôt sur le revenu et peut être utilisé dans le but d’émettre divers feuillets de déclaration de revenu.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Information may be shared with Public Works and Government Services Canada (Receiver General for Canada) for payment purposes refer to Receiver General Payments - PWGSC PCU 712. Where applicable, information may be shared with the Bank of Canada and financial institutions of foreign countries for transactions purposes. In some cases, the SIN and other information is shared with the Canada Revenue Agency and the Province of Quebec, and is used for data matching purposes, including income verification, refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 . Information may be used or disclosed for financial reporting and program evaluation.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs commun s par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>PRN 914</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>NDP 914</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou931</t>
         </is>
@@ -804,117 +815,120 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>PSU 932</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>psu932</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>pou932</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Comptes débiteurs</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>This bank describes information related to individuals who remit monies payable to government institutions, including the Receiver General for Canada. Payments may be issued in any form of payment approved by the Canadian Payment Association established under the Canadian Payment Act. Types of remittances include reimbursement of overpayments, payments for goods or services, including institutional merchandise (e.g., publications, coins, stamps, memorabilia, etc.), royalties, loan payments, etc. Personal information may include: name, contact information, credit information, financial information, nature of remittance, employee identification number, other identification numbers, signature, and Social Insurance Number (SIN).</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information sur les personnes qui remettent des sommes d’argent à l’ordre d’institutions fédérales, dont le Receveur général du Canada. Les paiements peuvent revêtir la forme n’importe lequel des modes de paiement approuvés par l’Association canadienne des paiements en vertu de la Loi canadienne sur les paiements. Les types de versements comprennent le remboursement de paiements en trop, les paiements au titre de biens et services, y compris des produits institutionnels (p. ex., publications, pièces de monnaie, timbres, souvenirs, etc.), les redevances, le remboursement de prêts, etc. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements de solvabilité, les renseignements financiers, la nature du versement, le numéro d’identification d’employé, d’autres numéros d’identification, la signature et le numéro d’assurance sociale (NAS).</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Individuals seeking access to this bank should specify whether they are an employee, member of the general public, contractor, representative of a company, corporation, or association, and provide details of the monies remitted such as amount, type, date(s), relevant account number, and type of program or service and name of institution. Personal information may be found in the institution’s Financial Management Systems and/or in Public Works and Government Services Canada’s Standard Payment System. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Les personnes qui souhaitent avoir accès à ce fichier doivent préciser si elles sont un employé, un membre du public en général, un entrepreneur, le représentant d’une entreprise, d’une société ou d’une association, et fournir des détails sur les sommes versées, comme le montant, le genre, les dates, le numéro de compte pertinent, le genre de programme ou de service et le nom de l’institution. Les renseignements personnels peuvent se trouver dans les systèmes de gestion financière de l’institution ou dans le Système normalisé des paiements de Travaux publics et Services gouvernementaux Canada. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Individuals who remit monies to the institution/Receiver General for Canada, including representatives of companies, corporations, and associations; current and former employees of government institutions.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Les personnes qui remettent des sommes à l’institution/au Receveur général du Canada, dont les représentant des sociétés, des corporations et des associations, les employés actuels ou les anciens employés des institutions fédérales.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Personal information is used to support the collection of monies owing to the institution/Receiver General for Canada in relation to goods and services, loans and investments, etc. Personal information is collected pursuant to various federal laws and regulations. For the specific legal authority for the collection, consult the institution’s Access to Information and Privacy Coordinator. The SIN is collected pursuant to the Income Tax Act and may be used to issue income reporting documentation.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont recueillis afin d’appuyer la collecte des sommes dues à l’institution/au Receveur général du Canada quant aux biens et services, aux prêts et aux investissements, etc. Les renseignements personnels sont recueillis conformément aux diverses lois et règlements fédéraux. Il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte. Le NAS est recueilli conformément à la Loi de l’impôt sur le revenu et peut être utilisé pour émettre des documents de déclaration des revenus.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Information may be shared with Public Works and Government Services Canada (Receiver General for Canada) to process payments to the government institution; refer to Receiver General Payments - PWGSC PCU 712. Information may be shared with the government institution’s own financial institution. Information may be shared with financial institutions of foreign countries for transactions purposes. Information may also be shared with collection agencies for debt recovery purposes. In some cases, the SIN and other information is shared with the Canada Revenue Agency and the Province of Quebec, and is used for data matching purposes, including income verification, refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 . Information may be used or disclosed for financial reporting and program evaluation.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>PRN 914</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>NDP 914</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou932</t>
         </is>
@@ -928,105 +942,105 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>PSU 940</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>psu940</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>pou940</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Acquisition Cards</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Cartes d’achat</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>This bank describes information that is used in support of an institution’s acquisition card program. Acquisition cards are used for the procurement and payment of goods and services, but not for travel-related expenses or for vehicle operating and maintenance expenses. The personal information may include: the card holder’s name, contact information, language, employee identification number, card number, expiration date, credit limit, and information related to any audits or compliance processes and investigations.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Le fichier décrit l’information utilisée à l’appui d’un programme de cartes d’achats d’une institution. Les cartes d’achat sont utilisées pour acquérir et payer des biens et des services, mais ne servent pas pour les dépenses liées aux voyages ou pour les dépenses liées à l’opération et à l’entretien de véhicules. Les renseignements personnels peuvent comprendre le nom du détenteur d’une carte, les coordonnées, la langue, le numéro d’identification d’employé, le numéro de la carte, la date d’expiration, la limite de crédit, et les renseignements relatifs aux vérifications ou à la conformité aux règles, et aux enquêtes.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Individuals who apply for an acquisition card and those who are issued such cards.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Personnes qui font une demande pour obtenir une carte d’achat ou pour lesquelles on émet une telle carte.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Personal information is used to administer an acquisition card program and may be used to issue, cancel, and renew cards, and to monitor transactions to ensure compliance. For many institutions, information is collected pursuant to Part III of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à administrer un programme de carte d’achats et peuvent être utilisés pour émettre, annuler ou renouveler des cartes ainsi que pour surveiller les transactions pour s’assurer de la conformité aux règles. Pour nombre d’institutions, les renseignements personnels sont recueillis conformément à la partie III de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties par la Loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Information may be shared with Public Works and Government Services Canada to monitor the operation of the acquisition card program and to take corrective action when required. Information may also be shared with the private sector card issuer, namely, financial institutions. The information may be also be used or disclosed for program evaluation, enforcement (refer to Security Incidents and Privacy Breaches - PSU 939 and Discipline - PSE 911 ), and for reporting to Senior Management.  |  Links: Security Incidents and Privacy Breaches - PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de dossiers administratifs courants par une institution fédérale, y compris la destruction finale de ces dossiers, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>PRN 914</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>NDP 914</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu940</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou940</t>
         </is>
@@ -1040,105 +1054,105 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>PSU 911</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>psu911</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>pou911</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Applications for Employment</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Demandes d’emploi</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>This bank describes personal information related to individuals who have submitted applications for employment or provided curricula vitae (solicited or unsolicited) and related correspondence. The personal information provided by individuals on application forms, curricula vitae, and correspondence may include: name, contact information, employment status and history, educational background, marital status, date of birth, gender, official language proficiency, employment equity, physical disability considerations, citizenship, Personal Record Identifier, Client Service Number, transcripts, letters of recommendation, and other personal information.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Ce fichier décrit des renseignements personnels sur les personnes ayant présenté des demandes d’emploi ou fourni les curricula vitae (réclamés ou non) et une correspondance connexe. Les renseignements personnels fournis par une personne dans les formulaires de demande, les curricula vitae et la correspondance peuvent comprendre son nom, ses coordonnées, sa situation et ses antécédents professionnels, ses études, son état matrimonial, sa date de naissance, son sexe, sa connaissance des langues officielles, sa situation au regard de l’équité en emploi, ses handicaps physiques, sa citoyenneté, son code d’identification de dossier personnel, son Numéro de service client, ses relevés de notes, ses lettres de recommandation et d’autres renseignements personnels.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Public service employees and non-public service employees seeking employment with the institution; individuals whose names have been provided as employment references, personal references, or both; and individuals referring another individual for a position.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Ces renseignements concernent des fonctionnaires et des non-fonctionnaires qui demandent un emploi au sein de l’institution; des personnes dont le nom a été fourni comme répondant professionnel ou personnel ou les deux; des personnes qui recommandent une autre personne pour un poste.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>To maintain an inventory of potential candidates that may be used for consideration in a staffing process when vacancies arise within the institution.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tenir à jour une liste de candidats à des fins de dotation en personnel en cas de postes vacants au sein de l’institution.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Relevant information would be transferred to an employee personnel record (refer to Standard Personal Information Bank Employee Personnel Record - PSE 901 ) if the individual accepts an offer of employment. This information may also be used for planning and evaluation purposes. The information may also be transferred to another institution, if the other institution is deemed to be more appropriate for potential employment opportunities for the individual. The data collected and maintained may be used for statistical purposes, training requirements, and other development opportunities. The personal information about individuals self-identified in employment equity groups may be used for statistical purposes by the institution and may be shared with the Public Service Commission of Canada, Treasury Board of Canada Secretariat, and the Canada Public Service Agency for the same purpose.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>PRN 920</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>NDP 920</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu911</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou911</t>
         </is>
@@ -1152,105 +1166,105 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>PSE 903</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>pse903</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>poe903</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Attendance and Leave</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Présences et congés</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>The records containing the information described in this bank may include absence reports and leave applications, as well as physicians’ certificates associated with sick leave, all of which include the individual’s Personal Record Identifier and correspondence about attendance and leave. The annual record of attendance and leave may be attached to the Employee Personnel Record. Some attendance and leave information exists in automated form in institutional personnel databases, especially in time/attendance, leave control and absenteeism systems.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Les dossiers contenant les renseignements décrits dans ce fichier peuvent comprendre des rapports sur les absences et les demandes de congé, ainsi que les certificats médicaux produits pour des congés de maladie. Sur tous ces documents, on doit inscrire le Code d’identification de dossier personnel et on doit également joindre la correspondance connexe aux présences et congés. Le dossier annuel portant sur les congés et les présences peut être joint au dossier personnel d’un employé. Certains renseignements relatifs aux congés et aux présences sont présentés sous forme de modules automatisés enregistrés dans des bases de données sur le personnel de l’organisme ou du ministère (systèmes présence/temps, congés et absences.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>The purpose of these records is to support administration of employee attendance and leave within government institutions.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Ces dossiers ont pour but d’étayer l’administration des congés et des présences des employés au sein des institutions fédérales.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>To record attendance  and authorize leave. To support decisions on pay and benefits, such as those  concerning leave and termination of employment, to evaluate use of leave and  rates of absenteeism and to verify policy compliance. This information may be  shared for disciplinary purposes (refer to PSE  901 Employee Personnel Record and PSE  911 Discipline ).  |  Links: PSE  901 Employee Personnel Record (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse901); PSE  911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>PRN 941</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>NDP 941</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse903</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe903</t>
         </is>
@@ -1262,63 +1276,52 @@
           <t>PSU 904</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>psu904</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>pou904</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Automated Document, Records, and Information Management Systems</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Systèmes automatisés de gestion des documents, des dossiers et de l’information</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>This standard personal information bank was terminated since all personal information retained in the systems is accounted for in personal information banks or classes of personal information of the programs or activities for which it was collected. Description terminated: December 2013.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Ce fichier de renseignements personnels ordinaire a été supprimé car tous les renseignements personnels conservés dans ces systèmes se trouvent dans les fichiers de renseignements personnels ou dans les catégories de renseignements personnels des programmes ou activités au titre desquels ils ont été recueillis. Description supprimé : en décembre 2013.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu904</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou904</t>
         </is>
@@ -1332,101 +1335,100 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>PSU 903</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>psu903</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>pou903</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Business Continuity Planning</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Planification de la continuité des activités</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>This bank describes information that is used in support of Business Continuity Management functions which include the development and timely execution of plans, measures and procedures to minimize interruption to the availability of critical services and assets in the event of an emergency or disruption of service. Personal information may include: name, contact information, biographical information, employee personnel information and medical information. Personal information may also include the names and contact information of individuals identified by employees as emergency contacts.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements qui sont utilisés à l’appui des fonctions de gestion de la continuité des opérations, qui comprennent l’élaboration et l’exécution, dans les délais prévus, des plans, des mesures et des procédures afin de minimiser l’interruption des services et de la disponibilité des immobilisations en cas d’urgence ou d’interruption de service. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements personnels de l’employé, et les renseignements médicaux. Les renseignements personnels peuvent aussi comprendre les noms et les coordonnées des personnes désignées par les employés comme personnes avec qui communiquer en cas d’urgence.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Employees of the government institution; Ministers and exempt staff and other personnel of offices of Ministers or Ministers of State; emergency contacts identified by employees; private sector emergency response officials and service providers; and other federal, provincial or municipal officials who may need to be contacted in the event of an emergency or disruption of services.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Personal information is used to plan and respond in a timely and effective manner to an emergency or to a disruption of service, to establish a list of employees, appropriate officials and their contact information. The list may be used to contact such individuals in the event of an emergency or the execution of the Business Continuity Plan. Some institutions may also require that supervisors maintain a list of direct reports, home telephone numbers and the emergency contacts identified by the direct reports. For most government institutions, personal information is collected pursuant to the Financial Administration Act (as required under the Policy on Government Security) and the Emergency Management Act. For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Les renseignements personnels permettent de faire face à une urgence ou à une interruption de service et d’y répondre dans des délais convenables et de manière efficace; d’établir une liste d’employés, de responsables pertinents et de leurs coordonnées. Cette liste peut servir à communiquer avec ces personnes en cas d’urgence ou d’exécution du Plan de continuité des opérations. Certaines institutions peuvent aussi exiger que les superviseurs tiennent à jour une liste de subordonnés directs, de numéros de téléphone à la maison et des personnes à contacter en cas d’urgence désignées par les subordonnés directs. Pour la plupart des institutions gouvernementales, les renseignements personnels sont recueillis conformément à la Loi sur la gestion des finances publiques (conformément à la Politique sur la sécurité du gouvernement) et la Loi sur la gestion des urgences. En ce qui concerne les institutions qui ne sont pas assujetties à ces lois il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Information may be shared with other federal, provincial, and municipal institutions, police, fire and other emergency response agencies as required. Some information may be shared with/described in the Standard Personal Information Banks Employee Personnel Record - PSE 901 and Occupational Health and Safety - PSE 907 . Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Occupational Health and Safety - PSE 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse907)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>PRN 928</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>NDP 928</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu903</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou903</t>
         </is>
@@ -1440,101 +1442,100 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>PSU 933</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>psu933</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>pou933</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Canadian Human Rights Act - Complaints</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Plaintes déposées en vertu de la Loi canadienne sur les droits de la personne</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>This bank describes information related to complaints filed pursuant to part III of the Canadian Human Rights Act. Complaints under part III of the Canadian Human Rights Act may be filed against any federally regulated organization and concern allegations of discriminatory practices based on any of the prohibited grounds. Personal information may include: name, contact information, biographical information, criminal checks/history, educational information, employee identification number, employee equity information, employee personnel information, nature of complaint, opinions and views of, or about, individuals, other identification numbers, medical information, physical attributes, and signature.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés aux plaintes déposées en vertu de la partie III de la Loi canadienne sur les droits de la personne. Les plaintes, conformément à la partie III de la Loi canadienne sur les droits de la personne, peuvent être déposées contre une organisation réglementée par le gouvernement fédéral et se rapporter à des allégations de pratiques discriminatoires fondées sur tout motif illicite. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les vérifications de casier judiciaire/antécédents criminels, les renseignements sur les études, le numéro d’identification d’employé, les renseignements personnels de l’employé, des renseignements sur l’équité en emploi, la nature de la plainte, les opinions et les points de vue sur, ou concernant, des individus, d’autres numéros d’identification, les renseignements médicaux, les signes distinctifs, et la signature.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Individuals and representatives of individuals or groups who make a complaint, respondents, and witnesses.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Personal information is collected pursuant to Part III of the Canadian Human Rights Act and is used to record, enquire into and resolve complaints of discrimination.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont recueillis conformément à la partie III de la Loi canadienne sur les droits de la personne, et sont utilisés pour enregistrer les plaintes de discrimination, pour enquêter sur le sujet et pour régler ces plaintes.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Information may be shared with the Department of Justice Canada to provide evidence for the hearing of a complaint by the Canadian Human Rights Tribunal, the Federal Court of Canada, the Appeal Court and/or the Supreme Court of Canada. Information may be also be used or disclosed for program evaluation.</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>PRN 926</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>NDP 926</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu933</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou933</t>
         </is>
@@ -1548,101 +1549,100 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>PSE 911</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>pse911</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>poe911</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Mesures disciplinaires</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>This bank describes personal information related to the application of discipline standards in the federal public service and related penalties, including termination of employment, suspension, demotion to a position at a lower maximum rate of pay and financial penalties that may be applied for breaches of discipline or misconduct in government institutions. Personal information may include: name, contact information, biographical information, date of birth, employee identification number, employee personnel information, financial information, legal advice, medical information, nature of the misconduct and the disciplinary measure, opinions and views of, or about, individuals, and signature.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels reliés à la demande de normes disciplinaires dans la fonction publique fédérale et les pénalités connexes, y compris le licenciement, la suspension, la rétrogradation à un poste situé dans une échelle de traitement comportant un plafond inférieur et les sanctions pécuniaires qui peuvent être appliquées en raison de manquements à la discipline ou de mauvaise conduite dans les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, la date de naissance, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, les avis juridiques, les renseignements médicaux, la nature de la mauvaise conduite et la mesure disciplinaire, les opinions et les points de vue sur, ou concernant, des individus, et la signature.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Employees and former employees of the institution who are/were the subject of the alleged misconduct, interviewees, medical practitioners, representatives or bargaining agents, and witnesses.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Personal information is used to investigate alleged misconduct in government institutions and to determine the need for, and nature of, disciplinary actions. Information is also collected to support decisions on pay and benefits, attendance and leave, transfer, demotion and termination of employment. For many institutions, personal information is collected pursuant to paragraph 12(1)(c) of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour enquêter sur une mauvaise conduite présumée dans les institutions fédérales, pour déterminer si des mesures disciplinaires sont requises et leur nature. Les renseignements sont également recueillis à l’appui des décisions sur la rémunération et les avantages sociaux, les présences et les congés, les transferts, les rétrogradations et les licenciements. Pour un bon nombre d’institutions, les renseignements personnels sont recueillis conformément à l’alinéa 12(1)c) de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Some discipline measures may also be described in Standard Personal Information Bank Employee Personnel Record - PSE 901 . Information concerning grievances is described in Standard Personal Information Bank Grievances - PSE 910 . Where applicable, information may be shared with the following entities: 1) the Treasury Board of Canada Secretariat in cases of terminations / demotions, interpretation / application of cases involving important jurisprudential issues, and other special instances; 2) professional regulatory bodies, as required; and 3) law enforcement agencies in the event of an alleged criminal offence. Information may also be used or disclosed for program evaluation.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>(1) For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator. (2) Documentation concerning a specific employee including documentation related to disciplinary action - the time limit for disposal is that specified in applicable collective agreements or a minimum of two years following the date of disciplinary action, provided no further disciplinary action has been recorded in the meantime. (3) In cases where a disciplinary action has been rescinded, the onus is on the institution to ensure that the documentation of the action concerned is immediately destroyed.</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>(1) Pour obtenir de plus amples renseignements sur la durée de conservation d’un type précis de documents administratifs communs par une institution fédérale, y compris sur la suppression de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution. (2) La documentation concernant un employé particulier, y compris celle liée à une mesure disciplinaire : le calendrier de suppression est celui indiqué dans les conventions collectives applicables ou au moins deux ans après la date de la mesure disciplinaire, en autant qu’aucune autre mesure disciplinaire n’ait été consignée dans l’intervalle. (3) Dans les cas où une mesure disciplinaire a été annulée, il incombe à l’institution de s’assurer que la documentation sur la mesure concernée soit immédiatement supprimée.</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>PRN 926, PRN 946</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>NDP 926, NDP 946</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe911</t>
         </is>
@@ -1656,113 +1656,115 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>PSU 906</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>psu906</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>pou906</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Disclosure of Wrongdoing in the Workplace</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Divulgation d’information sur les actes fautifs commis en milieu de travail</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>This bank describes information related to disclosures of alleged wrongdoing in the public sector, as defined in section 8 of the Public Servants Disclosure Protection Act (PSDPA). Personal information may include name, contact information, biographical information, employee personnel information, employee identification number, opinions and views of, or about, individuals, signature and other personal information which may be contained in the investigation documentation.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés aux divulgations d’actes fautifs présumés dans le secteur public, au sens de l’article 8 de la Loi sur la protection des fonctionnaires divulgateurs d’actes répréhensibles (LPFDAR ) . Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements personnels de l’employé, le numéro d’identification d’employé, les opinions et points de vue sur, ou concernant, des individus, ainsi que des signatures et autres renseignements personnels pouvant se trouver dans la documentation sur l’enquête.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Individuals, who are public servants, making a disclosure of wrongdoing may do so to their supervisor, to the Senior Officer for Disclosure of their institution, or directly to the Public Sector Integrity Canada; individuals, who are not public servants, making a disclosure of wrongdoing pertaining to the organization may do so directly to an organizational point of contact that has been designated for the handling of such concerns or the Office of the Public Sector Integrity Commissioner of Canada; refer to Case Review and Investigations Files - PSIC PPU 005 . Disclosures of wrongdoing pertaining to the Office of the Office of the Public Sector Integrity Commissioner of Canada must be made to the Auditor General of Canada. Bank formerly called: Internal Disclosure of Wrongdoing in the Workplace. Description last updated: December 2013.  |  Links: Case Review and Investigations Files - PSIC PPU 005 (http://www.psic.gc.ca/eng/content/access-information-and-privacy/infosource)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Les personnes qui sont des fonctionnaires et qui font une divulgation concernant la commission d’un acte fautif peuvent la faire à leur superviseur, à l’agent supérieur en matière de divulgations d’actes fautifs de l’institution ou directement au Commissariat à l’intégrité du secteur public du Canada. Les personnes qui ne sont pas des fonctionnaires et qui font une divulgation concernant la commission d’un acte fautif auprès d’une organisation peuvent la faire directement au responsable de l’institution qui a été chargée du traitement de telles préoccupations ou au Commissariat à l’intégrité du secteur public du Canada; voir Examen des cas et dossiers d’enquêtes – ISPC PPU 005 .La divulgation d’actes répréhensibles concernant le Commissariat à l’intégrité du secteur public du Canada doit être signalée au Vérificateur général du Canada. Ancien titre du fichier : Divulgation interne d’information sur les actes fautifs commis en milieu de travail. Dernière mise à jour de la description : décembre 2013.  |  Links: Examen des cas et dossiers d’enquêtes – ISPC PPU 005 (http://www.psic.gc.ca/fra/contenu/acc%C3%A8s-%C3%A0-linformation-et-protection-des-renseignements-personnels/infosource)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Individuals who report an alleged wrongdoing in the public sector as well as individuals who are alleged to have committed wrongdoing, witnesses, representatives of individuals such as union representatives and legal counsel, investigators and any other party affected by the allegation(s).</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Personal information is used to assess, investigate, report and resolve alleged wrongdoing in the public sector. When warranted, personal information may also be used to temporarily assign other duties to a public servant and provide notice of actions taken, or proposed to be taken, to the Public Sector Integrity Commissioner on recommendations made by the Commissioner. Personal information is collected pursuant to sections 12 to 14, 22(g), 22(h), 26 and 27 of the PSDPA.</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à évaluer, à faire enquête, à établir des rapports et à statuer sur des cas d’actes fautifs commis dans le secteur public. Quand les circonstances le justifient, les renseignements personnels peuvent aussi servir à affecter provisoirement un fonctionnaire à d’autres tâches et à donner avis des mesures prises ou proposées au Commissariat à l’intégrité du secteur public du Canada à la lumière des recommandations formulées par le commissaire. Les renseignements personnels sont recueillis en vertu des articles 12 à 14, 22g), 22 h), 26 et 27 de la LPFDAR.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>The information may be used or disclosed for evaluation and reporting to senior management. In limited circumstances under applicable laws, reporting purposes may include reporting to the Minister, or governing council, responsible for the government institution and publicly reporting on the wrongdoing. Depersonalized and aggregated information may be shared with the Treasury Board Secretariat (Office of the Chief Human Resources Officer) for reporting purposes. Information may be shared with internal security officials, refer to Security Incidents and Privacy Breaches- PSU 939 , or other authorities having the powers to investigate under federal, provincial and municipal statutes if the investigation reveals potential fraud or other criminal wrongdoing. Information may be shared with the government institution’s labour relations division when the chief executive officer of the government institution decides to apply disciplinary measures to public servants who perpetrated wrongdoings, refer to Discipline – PSE 911 .  |  Links: Security Incidents and Privacy Breaches- PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939); Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>PRN 926, PRN 931</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>NDP 926, NDP 931</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu906</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou906</t>
         </is>
@@ -1776,109 +1778,110 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>PSU 913</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>psu913</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>pou913</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Disclosure to Investigative Bodies</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Divulgation aux organismes d’enquête</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>This bank describes personal information about individuals that may be requested by and/or disclosed to an investigative body pursuant to paragraph 8(2)(e) of the Privacy Act. The personal information may include any personal information element that a government institution collects about an individual as part of one of its authorized program or activity and that is subsequently requested by an investigative body listed in Schedule 2 of the Privacy Regulations.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Ce fichier décrit des renseignements personnels qui peuvent être demandés par un organisme d’enquête en vertu de l’alinéa 8(2)e) de la Loi sur la protection des renseignements personnels ou qui peuvent lui être divulgués. Les renseignements personnels peuvent inclure tous les éléments de renseignements personnels qu’une institution fédérale recueille à propos des personnes dans le cadre d’un programme ou d’une activité autorisé et qui pourraient être demandés ultérieurement par un organisme d’enquête figurant à l’annexe 2 du Règlement sur la protection des renseignements personnels. Remarque : Le responsable d’une institution fédérale n’est pas tenu, conformément au paragraphe 9(2) de la Loi sur la protection des renseignements personnels, de faire un relevé des cas d’usages dans le fichier de renseignements personnels visé par la demande dans le cas de renseignements communiqués en vertu de l’alinéa 8(2)(e). Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>The head of a government institution is not required, in accordance to sub-section 9(2) Privacy Act, to account for the disclosure of the information under section 8(2)(e) in the personal information bank from which the personal information was requested. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Individuals whose personal information has been requested by federal investigative bodies pursuant to paragraph 8(2)(e) of the Privacy Act.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Les personnes dont leurs les renseignements personnels ont été demandés par des organismes d’enquête fédéraux en vertu de l’alinéa 8(2)e) de la Loi sur la protection des renseignements personnels. But : Les renseignements personnels servent à documenter les demandes qui ont été reçues d’organismes d’enquête en vertu de l’alinéa 8(2)e) de la Loi sur la protection des renseignements personnels et les réponses à ces demandes. Les renseignements personnels sont recueillis en vertu du paragraphe 8(4) de la Loi sur la protection des renseignements personnels et de l’article 7 du Règlement sur la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>The personal information is used to document requests received from investigative bodies pursuant to paragraph 8(2)(e) of the Privacy Act and the responses to such requests. Personal information is collected pursuant to section 8(4) of the Privacy Act and section 7 of the Privacy Regulations.</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>The information may be used or disclosed for statistical and audit purposes. Information may be shared with government institutions who are investigative bodies listed in Schedule 2 of the Privacy Regulations. Investigative bodies that receive personal information as a result of disclosures pursuant to paragraph 8(2)(e) of the Privacy Act may subsequently share such personal information with other federal investigative bodies or law enforcement agencies, for the purpose of the administration or enforcement of a law and/or the detection, prevention, or suppression of crime.</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Propre à l’institution.</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>PRN 937</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>NDP 937</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu913</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou913</t>
         </is>
@@ -1892,105 +1895,105 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>PSU 905</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>psu905</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>pou905</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Electronic Network Monitoring Logs</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Journaux de contrôle des réseaux électroniques</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>The records containing the information described in this bank relate to the use by individuals of government institutions electronic networks. Logs containing details of network use by individuals are compiled and are reviewed by appropriate officials of the institution when there is suspected misuse, policy non-compliance, or potential compromise of a government institution’s electronic network, as defined by the government institution’s policies or the Policy on the Use of Electronic Networks, or other relevant Treasury Board policy instruments or policy directions. Examples of information that may be in the records include network logs that may link an employee’s workstation to an Internet Protocol address, listings of sites visited and information on any transactions conducted, including date, time, duration and nature of the visit or transaction. The records may also include information on the use of authorization codes assigned to particular individuals, including successful or unsuccessful use of the codes, date, time and frequency.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Les dossiers contenant les renseignements décrits dans ce fichier se rapportent à l’utilisation des réseaux électroniques des institutions fédérales. Des journaux contenant le détail sur l’utilisation des réseaux sont compilés et revus par les agents appropriés de l’institution lorsqu’il y a lieu de soupçonner la non-conformité aux politiques ou qu’un réseau électronique d’une institution fédérale est soumis à un usage détourné, au sens donné à ce terme dans les politiques en la matière de l’institution intéressée ou de la Politique d’utilisation des réseaux  électroniques, ou autres instruments de politiques et orientations pertinents du Conseil du Trésor. Ces dossiers peuvent comprendre par exemple des journaux de réseau qui  établissent des liens entre le poste de travail d’un employé et une adresse du protocole Internet, les listes de sites consultés et des renseignements sur les opérations effectuées, y compris la date, l’heure, la durée et la nature de la visite ou de l’opération. Ils peuvent aussi s’étendre à de l’information sur l’usage fait de codes d’autorisation attribués à des particuliers, y compris les cas où les codes ont pu être utilisés avec succès ou non, la date, l’heure et la fréquence d’utilisation.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Employees of the government institution and other individuals using institutional electronic networks, including: student employees; contract staff and agency personnel; members of the public; Ministerial staff; or Members of Parliament that send e-mail to the government institution or specific individuals within the government institution.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Les employés de l’institution fédérale et les autres personnes qui font usage des réseaux électroniques des institutions fédérales, y compris les employés étudiants, le personnel sous contrat, le personnel d’agence, les membres du public, le personnel ministériel ou les députés qui envoient des courriels à l’institution fédérale ou à des employés particuliers de l’institution.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>The information contained in the records may be compiled to support the investigation of suspected or alleged misuse, policy non-compliance, or deliberate or inadvertent impairment or compromise of government electronic networks by persons employed by the institution or by other individuals from outside the institution.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Les renseignements versés dans ces dossiers sont recueillis aux fins des enquêtes sur les cas soupçonnés ou présumés de non-conformité aux politiques, d’usage détourné des réseaux  électroniques de l’état ou encore sur les tentatives délibérées ou non de personnes travaillant pour l’institution ou d’individus de l’extérieur de l’organisme de nuire au fonctionnement des réseaux électroniques ou de les compromettre.</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>The information may be used to substantiate any disciplinary action taken where violation of institutional policies or the Policy on the Use of Electronic Networks is determined, and to support compliance with other relevant Treasury Board policy instruments or policy directions. This information may be shared for disciplinary purposes (refer to PSE 901 Employee Personnel Record and PSE 911 Discipline ). If an internal investigation determines that criminal actions may have taken place, the information may be shared with appropriate police authorities. This information may be used to provide reports to management. The information may also be used for research, planning, audit and evaluation purposes.  |  Links: PSE 901 Employee Personnel Record (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse901); PSE 911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>PRN 932</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>NDP 932</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu905</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou905</t>
         </is>
@@ -2004,105 +2007,105 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>PSE 916</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>pse916</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>poe916</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Employee Assistance</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aide aux employés</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>The records containing the information described in this bank are treated in a confidential fashion that is relative to an employee’s involvement in an Employee Assistance Program. These records may include notice of voluntary or mandatory (supervisory work performance related) referral; records of reference to, or reports and correspondence from a health professional or rehabilitation agency; and only non-medical interpretations concerning an employee’s work capability or limitations. All personal medical data shall be maintained in a medical protected status under the control of the Occupational and Environmental Health Services Agency. Records relating to work performance deficiencies, absenteeism and disciplinary matters are to be held in the appropriate institutional record (with its related personal information bank) and not held with Employee Assistance Program files.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Les dossiers contenant des renseignements décrits dans ce fichier sont traités de façon confidentielle en ce qui touche la participation d’un employé au Programme d’aide aux employés. Ces dossiers peuvent comprendre des avis de mise en rapport volontaire ou obligatoire (connexe au rendement au travail); des dossiers de mise en rapport avec des professionnels de la santé ou un organisme de réadaptation, et les rapports et la correspondance provenant de ces derniers; les interprétations non médicales concernant les capacités ou les limites de travail de l’employé. Tous les renseignements médicaux personnels sont conservés à titre de renseignements médicaux protégés dans un fichier administré par l’Agence des services d’hygiène du travail et du milieu. Les dossiers ayant trait aux lacunes en matière de rendement de l’employé, à l’absentéisme et aux questions disciplinaires doivent être conservés dans le fichier pertinent de renseignements personnels de l’organisme ou du ministère, et non dans les dossiers du Programme d’aide aux employés.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>The purpose of these records is to document information necessary for the administration of the Employee Assistance Program. To determine the need for employee assistance counselling, referrals for medical evaluations and participation in rehabilitation programs.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Ces dossiers ont pour but d’étayer les renseignements nécessaires à l’administration du Programme d’aide aux employés. Il vise à déterminer si les employés ont besoin de l’aide, s’il est nécessaire de leur faire passer une évaluation sur le plan médical ou de les faire participer à des programmes de réadaptation.</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>To support decisions regarding employee assistance measures.</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>PRN 922</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>NDP 922</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse916</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe916</t>
         </is>
@@ -2116,117 +2119,120 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>PSE 912</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>pse912</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>poe912</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Employee Performance Management Program</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Programme de gestion du rendement des employés</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>This bank describes information that is used in support of performance management of employees of the government institution. The personal information may include: name, biographical information, educational information, employee personnel information, medical information, employee identification number, other identification numbers, signature, views and opinions of, and about an individual.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information utilisée dans le but d’appuyer la gestion du rendement des employés d’une institution fédérale. Les renseignements personnels peuvent comprendre le nom, les renseignements biographiques, les renseignements sur les études, les renseignements qui figurent au dossier de l’employé, les renseignements médicaux, le numéro d’identification d’employé, d’autres numéros d’identification, la signature et des opinions et points de vue sur, ou concernant, l’individu.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Bank formerly called Performance Management Reviews. Description last updated: March 2014.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Employees of the government institution.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>The personal information is used to assess and rate employee performance against established expectations (work competencies and objectives) and rating scale. The personal information is also used to support decisions in respect of assigning recognition, undertaking remedial action plans, identification of training and development needs, approval of performance compensation and annual increments, promotions, transfers, retention, demotion of employees, termination of employment, extension of probation and rejection of employees on probation, employee assistance and occupational health and safety. For many institutions, personal information is collected pursuant to section 12 of the Financial Administration Act (FAA). For institutions that are not part of the core public administration, consult the institution’s Access to Information Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à évaluer et à noter le rendement de l’employé en fonction d’attentes établies (compétences professionnelles et objectifs de travail) et de l’échelle de notation. Les données servent aussi à justifier les décisions relatives à l’attribution d’une reconnaissance, à l’établissement de plans de mesures correctives, à la détermination du besoin de formation et de perfectionnement et à l’approbation de la rémunération au rendement et des hausses annuelles, de même que les décisions concernant les promotions, les mutations, le maintien en fonction, les rétrogradations, la fin d’emploi, la prolongation de la période de stage et le renvoi en cours de stage, ainsi que l’aide aux employés et la santé et la sécurité au travail. Pour plusieurs institutions, les renseignements personnels sont recueillis en vertu de l’article 12 de la Loi sur la gestion des finances publiques (LGFP). En ce qui concerne les institutions qui ne font pas partie de l’administration publique centrale, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>The information may be used or disclosed for the following purposes: reporting to senior management, evaluation, audit, talent management and succession planning, policy analysis, research and statistics. For institutions of the core public administration, information may be shared with Treasury Board of Canada Secretariat, refer to TBS PCE 754 Performance Management Program for Employees . Information may be shared with other programs or activities of the government institution; refer to PSE 911 Discipline , PSE 916 Employee Assistance , PSE 901 Employee Personnel Record , PSE 910 Grievances , PSU 935 Human Resources Planning , PSE 907 Occupational Health and Safety , PSE 904 Pay and Benefits , PSE 920 Recognition Program , PSE 902 Staffing , PSE 905 Training and Development .  |  Links: TBS PCE 754 Performance Management Program for Employees (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp#TBSPCE754); PSE 911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911); PSE 916 Employee Assistance (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse916); PSE 901 Employee Personnel Record (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); PSE 910 Grievances (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910); PSU 935 Human Resources Planning (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935); PSE 907 Occupational Health and Safety (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse907); PSE 904 Pay and Benefits (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904); PSE 920 Recognition Program (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse920); PSE 902 Staffing (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse902); PSE 905 Training and Development (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Les renseignements peuvent être utilisés ou divulgués pour les raisons suivantes : établissement de rapports à la haute direction, évaluation, audit, gestion des talents et planification de la relève, analyse des politiques, recherche et statistique. Dans le cas des institutions faisant partie de l’administration publique centrale, les renseignements peuvent être communiqués au Secrétariat du Conseil du Trésor du Canada; voir SCT PCE 754 Programme de gestion du rendement pour les employés . Les renseignements peuvent être communiqués à d’autres programmes et activités de l’institution; voir POE 911 – Mesures disciplinaires , POE 916 – Aide aux employés , POE 901 – Dossier personnel d’un employé , POE 910 – Griefs , POU 935 – Planification des ressources humaines , POE 907 – Santé et sécurité au travail , POE 904 – Rémunération et avantages , POE 920 – Programme de la reconnaissance , POE 902 – Dotation et POE 905 – Formation et perfectionnement .  |  Links: SCT PCE 754 Programme de gestion du rendement pour les employés (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-fra.asp#SCTPCE754); POE 911 – Mesures disciplinaires (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe911); POE 916 – Aide aux employés (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe916); POE 901 – Dossier personnel d’un employé (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe901); POE 910 – Griefs (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe910); POU 935 – Planification des ressources humaines (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou935); POE 907 – Santé et sécurité au travail (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071); POE 904 – Rémunération et avantages (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe904); POE 920 – Programme de la reconnaissance (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe920); POE 902 – Dotation (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021); POE 905 – Formation et perfectionnement (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe905)</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>PRN 946</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>NDP 946</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse912</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe912</t>
         </is>
@@ -2240,97 +2246,95 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>PSE 901</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>POE 901</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>pse901</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>poe901</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Employee Personnel Record</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Dossier personnel d’un employé</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>This bank describes information about an individual’s employment with government institutions. Personal information may include name, contact information, biographical information (including any military service, professional certifications or designations), citizenship status, date and place of birth, educational information, employee identification number, employment equity information, delegated authorities given or assets loaned to employees (e.g., staffing and financial signing authorities, usage of institutional materiel), alternative work arrangements (e.g., telework, compressed work week), information related to superannuation, benefits, training and development, grievances, security incidents, any other employment-related requirements (e.g., firearms permits, security clearances, passport/visa information), financial information (for pay administration), medical information (including any special needs identified under duty to accommodate, or in the event of an emergency), other identification numbers, signature and Social Insurance Number (SIN). Employment equity information will only be used for the primary purposes, not for the consistent uses listed.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Ce dossier décrit les renseignements sur l’emploi d’une personne dans les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques (y compris le service militaire, les désignations ou certifications professionnelles), la citoyenneté, la date et le lieu de naissance, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, les pouvoirs délégués accordés ou les biens prêtés aux employés (p. ex., les pouvoirs de dotation ou de signature de documents financiers, l’utilisation de matériel institutionnel), les réaménagements des horaires de travail (p. ex., télétravail, semaine de travail comprimée), les renseignements liés à la pension de retraite, les avantages sociaux, la formation et le perfectionnement, les griefs, les incidents de sécurité, toute autre exigence liée à l’emploi (p. ex., permis de port d’arme à feu, autorisations de sécurité, renseignements sur le passeport/visa), les renseignements financiers (pour l’administration de la paye), les renseignements médicaux (y compris tous les besoins spéciaux déterminés dans le cadre de l’obligation de prendre des mesures d’adaptation, ou en cas d’urgence), d’autres numéros d’identification, la signature et le numéro d’assurance sociale (NAS). Les informations sur l'équité en matière d'emploi ne seront utilisées qu'aux fins principales, et non pour les utilisations compatibles énumérées.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, emergency contacts of employees, and may also include spouses, dependants, and beneficiaries.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Personal information is used to facilitate personnel administration in the employing institution and to ensure continuity and accuracy when an employee is transferred to another institution. For most government institutions, personal information is collected under the authority of the Public Service Employment Act (PSEA). For those institutions not subject to the (PSEA), consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection. The Social Insurance Number is collected pursuant to the Income Tax Act.</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à faciliter l’administration du personnel par l’employeur et à assurer la continuité et l’exactitude lorsqu’un employé est transféré dans une autre institution. Pour la plupart des institutions gouvernementales, les renseignements personnels sont recueillis aux termes de la Loi sur l’emploi dans la fonction publique (LEFP). En ce qui concerne les institutions qui ne sont pas assujetties à la LEFP, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte. Le numéro d’assurance sociale est recueilli conformément à la Loi de l’impôt sur le revenu.</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Information is disclosed to Canada Revenue Agency refer to Individual Returns and Payment Processing – CRA PPU 005 and to the Province of Quebec (where applicable) for income tax purposes. Information is also disclosed to Employment and Social Development Canada (ESDC) for employment insurance and pension purposes. Information may also be disclosed to Public Works and Government Services Canada (PWGSC) to facilitate payment of salary including direct deposit refer to Bank Public Service Compensation Systems - PWGSC PCE 705 . Where applicable, information may also be disclosed to various provincial health insurance plans or third-party group insurance companies. Information may be used to confirm the identity of employees for access to government and institutional information technology infrastructure. Where applicable, information may be disclosed to Shared Services Canada (SSC). Selected information is shared with previous employers for the purpose of finalizing payments, including retroactive payments and the recovery of outstanding amounts owing to the Crown. Information may be used for general human resource management purposes, including to verify and report on policy compliance. In instances of suspected non-compliance, information may be disclosed to the institution’s security and/or staff relations officials for further investigations or disciplinary actions (refer to PSU 939 Security Incidents and Privacy Breaches and PSE 911 Discipline ). Information may also be used or disclosed for program evaluation purposes.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Public Service Compensation Systems - PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); PSU 939 Security Incidents and Privacy Breaches (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#psu939); PSE 911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>98/005 and 98/018</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>PRN 920</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe901</t>
         </is>
@@ -2344,105 +2348,105 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>PSE 918</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>pse918</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>poe918</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Employment Equity and Diversity</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Équité en emploi et diversité</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>The records containing the information described in this bank include personal information on employees such as education, work history and career aspirations, and training and development, which is collected by means of questionnaires and/or interviews or compiled from employees’ files or automated data systems. The information is collected on a voluntary basis, and respondents are asked to identify whether they are male or female, whether they are an aboriginal person, and whether they have a disability or are a member of a visible minority group. The Personal Record Identifier may be used to identify employees in instances where government institutions are not able to employ an anonymous questionnaire, as well as when these identifiers are required to locate employee records.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Les dossiers contenant les renseignements décrits dans ce fichier comprennent des renseignements personnels sur les employés, notamment sur leurs études; leurs antécédents professionnels et leurs projets de carrière; leur formation et leur perfectionnement. Tous ces renseignements ont été recueillis au moyen de questionnaires ou d’entrevues, ou compilés à partir de leurs dossiers ou des systèmes de données automatisés. Les répondants, qui sont libres de fournir ces renseignements, indiquent leur sexe et s’ils sont autochtones, handicapés ou font partie d’une minorité visible. Le Code d’identification de dossier personnel peut servir à identifier les employés lorsque les institutions fédérales ne peuvent pas utiliser un questionnaire anonyme ou lorsqu’il est nécessaire d’avoir ces indicatifs afin de pouvoir trouver le dossier de l’employé.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Related records provide documentation for the implementation of the employment equity policy in government institutions. Data are collected to provide a comprehensive picture of employees by sex and by target group status (e.g., women, aboriginal peoples, persons with disabilities and members of visible minority groups). This information is used to compile a personnel profile of employees and to compare the situation of target group members with non-target group members within a government institution and with their counterparts in the general labour market. The Personal Record Identifier (PRI) may be used to link information in this bank with that in another bank containing employee information (e.g., the Personnel Management Information System) in order to obtain statistical information, where the securing of such information would be consistent with the uses for which the personal information was collected. Self-identification information may be obtained from the institutional records as described in the Standard Personal Information Bank Staffing - PSE 902 .  |  Links: Staffing - PSE 902 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse902)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Ces dossiers ont pour but de recueillir toute la documentation nécessaire à la mise en œuvre de la politique relative à l’équité en matière d’emploi pour toutes les institutions fédérales. C’est grâce à ces renseignements qu’il est possible d’avoir toutes les données au sujet des employés, présentées selon leur sexe et leur groupe cible (femmes, autochtones et personnes handicapées et personnes faisant partie de minorités visibles). Ces renseignements sont utilisés afin de réaliser un profil personnel des employés et de comparer la situation des membres des groupes cibles avec celles des autres groupes au sein des ministères et organismes fédéraux et avec leurs homologues sur le marché du travail. Le Code d’identification de dossier personnel peut servir à établir un lien entre les renseignements contenus dans ce fichier et ceux conservés dans un autre fichier comprenant des renseignements sur les employés (p. ex., le Système d’information pour la gestion du personnel) et ce, à des fins statistiques et lorsque la conservation de tels renseignements est conforme aux usages pour lesquels les renseignements personnels ont été recueillis. Il est possible d’obtenir des données d’auto-identification des dossiers institutionnels qui sont décrits dans le Fichier de renseignements personnels Dotation – POE 902 .  |  Links: Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>The government institution may collect data for statistical purposes, for purposes relating to individuals, or for both. Personal data are released to the Treasury Board of Canada Secretariat for statistical purposes only (refer to Central Personal Information Bank Employment Equity Data Bank - TBS PCE 739 ). The information gathered will be used for institutional purposes in the government’s employment equity program to identify and eliminate systemic discrimination in employment and to introduce temporary special measures to ensure that target groups participate in and are equitably represented in the federal public service. It may also be used for policy and planning purposes related to employment equity.  |  Links: Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>PRN 942</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>NDP 942</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse918</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe918</t>
         </is>
@@ -2456,105 +2460,105 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>PSU 902</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>psu902</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>poe902</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Executive Correspondence</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Correspondance à la direction</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>The records containing the information described in this bank include general correspondence to the Minister or Secretary of State, their Staff and other senior executives within the institution. Records used in preparation of responses to incoming correspondence may also contain personal information about individuals that is sometimes provided by institutional officials to address issues and concerns raised in the incoming correspondence. Personal information may include the name of the correspondent, contact information and other personal information that may be included by the originator and/or respondent within the content of the correspondence.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Les dossiers contenant les renseignements décrits dans ce fichier comprennent la correspondance générale du ministre ou du secrétaire d’État, de leur personnel ainsi que celle d’autres cadres supérieurs au sein de l’institution. Les dossiers utilisés pour préparer les réponses à la correspondance reçue peuvent contenir des renseignements personnels particuliers qui sont fournis parfois par des agents de l’institution afin de donner suite aux questions et aux préoccupations soulevées dans le courrier d’arrivée. Les renseignements personnels peuvent comprendre le nom du correspondant, ses coordonnées ainsi que d’autres renseignements que l’expéditeur et/ou le répondant a inclus dans la correspondance.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>General public, Members of Parliament, and officials representing other levels of government or international governments and agencies, external organizations and/or businesses.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Le grand public, les députés ainsi que les représentants des organisations, d’autres ordres de gouvernements, des gouvernements étrangers, des organismes internationaux, des organisations externes et des entreprises.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>To manage, in a consistent and time-efficient manner, the receipt of, and responses to, correspondence or inquiries received from outside the institution that require replies from senior executives of the institution.</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Pour gérer de manière cohérente et opportune la réception et la réponse de la correspondance et des demandes de renseignements reçues de l’extérieur de l’institution. Les réponses doivent provenir des cadres supérieurs de l’institution.</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Incoming correspondence may be forwarded to other federal or provincial institutions for a full or partial response if it is determined by the receiving institution that the issue(s) contained within the correspondence fall under the jurisdiction of, and should be addressed by, the other institution(s). In some cases, incoming correspondence and the response may be copied to another federal or provincial institution where the correspondence impacts on their roles and responsibilities. The information may be used in an aggregate format to report on system use, growth of the information collection, etc. The Executive Correspondence Management System may be integrated with the institution’s Automated Document, Records and Information Management System.</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>PRN 943</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>NDP 943</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu902</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902</t>
         </is>
@@ -2568,101 +2572,100 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>PSU 942</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>psu942</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>pou942</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Évaluation</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>This bank describes personal information related to a government institution’s evaluation function and activities. Personal information may include name, contact information, biographical information, demographic information, financial information, identification numbers, gender, job titles, and opinions and views of, or about, individuals, which in some cases, are collected with informed consent.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Ce fichier décrit des renseignements personnels inhérents à la fonction et aux activités d’évaluation d’une institution fédérale. Les renseignements personnels dont il est question peuvent comprendre le nom, les coordonnées, des données démographiques, des renseignements financiers, des numéros d’identification, le sexe, des titres de poste, ainsi que des opinions et des points de vue sur, ou concernant, des individus et recueillis, dans certains cas, avec le consentement éclairé des personnes visées.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Program participants, managers, employees, or partners of the program or institution, including government representatives from other jurisdictions, representatives of businesses and private sector organizations, academics or other experts in the program area, and other stakeholders including members of the general public.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Personal information is used in data collection and analysis when undertaking evaluations. In some cases, a limited amount of personal information, (typically names and /or titles of academics or other experts) may appear in evaluation reports where informed consent has been given by the person or persons to whom the information relates. For many institutions, information is collected pursuant to sections 7 and 42.1 of the Financial Administration Act. For those not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés aux fins de collecte et d’analyse des données au moment d’entreprendre des évaluations. Parfois, les rapports d’évaluation comportent un nombre limité de renseignements personnels (généralement le nom, le grade universitaire ou d’autres champs d’expertise). Il s’agit des rapports pour lesquels la ou les personnes concernées ont donné leur consentement éclairé. Plusieurs institutions recueillent des renseignements personnels conformément aux articles 7 et 42.1 de la Loi sur la gestion des finances publiques. Les autres, soit celles qui ne sont pas assujetties à cette Loi, doivent consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Information may be shared with the deputy head of the institution, the government institution Evaluation Committee, and program managers. Information may be also be shared with (1) other government institutions or other partners involved in managing or delivering the program and in undertaking the evaluation; (2) Treasury Board Secretariat officials; and (3) consultants performing evaluation work on behalf of the institution. Final evaluation reports are made publicly available.</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>98/004</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>98/004</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>PRN 916</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>NDP 916</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu942</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou942</t>
         </is>
@@ -2676,109 +2679,110 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>PSU 934</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>POU 934</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>psu934</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>pou934</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>EX Talent Management</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Gestion des talents des cadres supérieurs</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>This bank describes information about government institution employees in the Executive (EX) category who register for the EX Talent Management tool. Personal information may include name and contact information of the individual and supervisor, employee identification number, employment equity information, biographical information, educational information, employee personnel information, date of birth, gender, opinions and views of, or about, individuals, photograph, and signature.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information sur les employés fédéraux de la catégorie EX qui s’inscrivent à l’outil de gestion des talents des cadres supérieurs. Les renseignements personnels peuvent comprendre le nom, les coordonnées de la personne et du superviseur, le numéro d’identification de l’employé, de l’information sur l’équité en emploi, des renseignements biographiques, des renseignements sur les études, des renseignements personnels de l’employé, la date de naissance, le sexe, les opinions et points de vue sur, ou concernant, des individus, la photo et la signature.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Employees at the EX-01 to EX-02 category and levels who choose to register for this tool. The tool is mandatory for employees at the EX-03, EX-04 and EX-05 levels (Assistant Deputy Minister levels).</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Les employés des catégories et niveaux EX-01 à EX-02 qui choisissent de s’inscrire à cet outil. L’outil est obligatoire pour les employés des niveaux EX-03, EX-0 et EX-05 (niveaux de sous-ministre adjoint).</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Personal information is collected by Treasury Board of Canada Secretariat for the purpose of assisting government institutions in managing executive talent through activities such as succession planning, and the identification of talent gaps and learning and development needs and responding strategies refer to EX Talent Management - TBS PCU 715 . In addition, with respect to EX 04 and EX 05 levels, the purpose is also to support the collective management system of Assistant Deputy Ministers. For institutions that participate, Treasury Board Secretariat will return analysed data which can then be used by the institutions to identify trends and critical gaps, for the EXs, Levels 1-5. Participating institutions may also receive aggregated enterprise-wide data reports for benchmarking purposes. For many institutions, personal information is collected pursuant to the Financial Administration Act and the Public Service Employment Act. For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.  |  Links: EX Talent Management - TBS PCU 715 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp)</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Le Secrétariat du Conseil du Trésor recueille des renseignements personnels afin d’aider les institutions du gouvernement à gérer le talent du groupe de la direction en menant des activités, comme la planification de la relève, l’identification des lacunes dans les talents, la détermination des besoins en apprentissage et en perfectionnement, et les stratégies qui en découlent, voir Gestion des talents des cadres supérieurs – SCT PCU 715 . De plus, pour les niveaux EX 04 et EX 05, l’objectif consiste également à appuyer le système de gestion collectif des sous-ministres adjoints. Dans le cas des institutions participantes, le Secrétariat du Conseil du Trésor renverra des données analysées, qu’elles peuvent ensuite utiliser pour déterminer les tendances et les lacunes importantes concernant les niveaux EX-01 à EX-05. Les institutions participantes peuvent également recevoir des rapports de données pangouvernementales à des fins d’analyse comparative. Pour nombre d’institutions, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques et la Loi sur l’emploi dans la fonction publique. En ce qui concerne les institutions qui ne sont pas assujetties à ces lois, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.  |  Links: Gestion des talents des cadres supérieurs – SCT PCU 715 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-fra.asp)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Information collected for executives who are at the ADM or equivalent level may be shared with the Clerk of the Privy Council’s Committee of Senior Officials. Information may also be shared with/described in the Standard Personal Information Banks: Employee Performance Management Program – PSE 912 , Training and Development - PSE 905 , and Human Resources Planning - PSU 935 . Information may also be used or disclosed for program evaluation.  |  Links: Employee Performance Management Program – PSE 912 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse912); Training and Development - PSE 905 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905); Human Resources Planning - PSU 935 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>PRN 920</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>NDP 920</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu934</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou934</t>
         </is>
@@ -2792,105 +2796,105 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>PSU 918</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>psu918</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>pou918</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Governor in Council Appointments</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Nominations par le Gouverneur en conseil</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>This bank describes information that is collected to support Governor in Council appointments to government institutions. The personal information collected may include: the individual’s full name, contact information, official language of choice, date of birth, country of birth, citizenship, gender, marital status, Social Insurance Number (SIN), unique identification number (e.g., unique employee number), terms and conditions of appointment including remuneration (e.g., salary, honoraria, per diem rate) and benefits, signature, physical limitations and any other relevant medical information, photographs or other image recordings, educational background, employment status, work history, professional affiliations, credit card and financial institution information, government security clearances, biographical information (including information about family members), conflict of interest declarations, appointment date and duration and resignation dates, if applicable.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Sont décrits dans ce fichier les renseignements recueillis à l’appui des nominations du gouverneur en conseil dans les institutions fédérales. Les renseignements personnels recueillis peuvent comprendre: le nom complet de la personne, ses coordonnées, sa langue officielle de préférence, sa date de naissance, son pays natal, sa citoyenneté, son sexe, sa situation de famille, son numéro d’assurance sociale (NAS), un numéro d’identification exclusif (p. ex., un numéro d’employé unique), les modalités de sa nomination, y compris sa rémunération (p. ex., traitement, honoraires, indemnité quotidienne) et ses avantages sociaux, sa signature, ses limitations physiques et toute autre information médicale pertinente, des photographies ou d’autres enregistrements visuels, sa scolarité, sa situation d’emploi, ses antécédents de travail, ses affiliations professionnelles, de l’information sur ses cartes de crédit et son établissement bancaire, sa cote de sécurité au gouvernement, des données biographiques (y compris des renseignements sur les membres de sa famille), toute déclaration de conflit d’intérêts, des lettres de référence/de recommandation, la date de nomination, la durée de la nomination et la date de démission, s’il y a lieu.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Current and former appointees and their family members.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Les titulaires actuels et les anciens titulaires des postes dotés par décret ainsi que les membres de leur famille.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>The personal information collected is used to support the identification and selection of individuals to serve as Governor in Council appointments which include Chairpersons and Chief Executive Officers of Crown Corporations, Heads of Agencies, and Boards of Governors. Successful individuals are named through an Order in Council - a process that is managed by the Privy Council Office. The personal information is also used to manage the administration of expenses (e.g., travel) and compensation and benefits packages, conduct performance evaluations, maintain an inventory of current and former appointees, record potential conflicts of interest and any compliance action required, and to communicate with these individuals.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Les renseignements personnels recueillis servent dans le processus d’identification et de sélection des personnes nommées par décret, comme les présidents et les chefs de la direction de sociétés d’état, les dirigeants d’organismes et les membres des conseils d’administration. Les candidats retenus sont nommés par décret, selon un processus géré par le Bureau du Conseil privé. Les renseignements personnels servent aussi à gérer l’administration des dépenses (p. ex., les frais de voyage) et les régimes de rémunération et d’avantages sociaux, à faire des évaluations du rendement, à tenir un répertoire des membres actuels et des anciens membres, à enregistrer d’éventuels conflits d’intérêts et toute mesure de conformité nécessaire, ainsi qu’à communiquer avec ces personnes.</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Personal information about the appointee is contained in the Order in Council document which includes full name, contact information, the position to which s/he is being appointed, the length and tenure of the appointment, and the terms and conditions of the appointment (e.g., remuneration, benefits, vacation leave, etc.). This information is provided by the Privy Council Office to the institution (refer to Governor in Council Personnel Records - PCO PPU 020 ). Governor in Council Personnel Records - PCO PPU 020). Additionally, this information may be used in the preparation of reports for senior management and broader audiences (e.g., Annual Reports) and communications materials (e.g., press releases, biographies, etc.) that may be disseminated in multiple formats, including the institution’s website. In some instances, the Privy Council Office receives notes and performance ratings to support the conduct of performance evaluations of selected individuals (refer to Governor in Council Personnel Records - PCO PPU 020 ). The Social Insurance Number (SIN) is collected pursuant to the Income Tax Act (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and, where applicable, the Province of Quebec Income Tax Act.  |  Links: Governor in Council Personnel Records - PCO PPU 020 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Governor in Council Personnel Records - PCO PPU 020 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>PRN 938</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>NDP 938</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu918</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou918</t>
         </is>
@@ -2904,113 +2908,115 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>PSE 910</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>pse910</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>poe910</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Grievances</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Griefs</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>This bank describes personal information related to the grievance process, through which employees may formally seek redress/resolution of any disagreements pertaining to terms and conditions of employment. In addition to the formal process, this bank also describes personal information related to any informal conflict management process. Personal information may include name, contact information, employee personnel information, biographical information, educational information, employee identification number, employment equity information, nature of the grievance, medical information; opinions and views of, or about, individuals; and signature.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels liés à la procédure de règlement des griefs au moyen de laquelle les employés peuvent officiellement demander réparation/chercher une solution pour tout désaccord concernant les conditions de travail. Outre le processus officiel, ce fichier décrit aussi les renseignements personnels liés à tout processus de gestion informelle du conflit. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements personnels de l’employé, les renseignements biographiques, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, la nature du grief, les renseignements médicaux, les opinions et les points de vue sur, ou concernant, des individus, et la signature.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>For those institutions subject to the Public Service Labour Relations Act, section 208 of the Act gives an employee the right to present an individual grievance unless an administrative procedure for redress is provided under any Act of Parliament, other than the Canadian Human Rights Act.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Pour les institutions assujetties à la Loi sur les relations de travail dans la fonction publique, l’article 208 de la Loi confère à un employé le droit de présenter un grief individuel à moins qu’une procédure administrative de réparation ne soit prévue dans une loi fédérale, distincte de la Loi canadienne sur les droits de la personne.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Current and past employees of government institutions, their representatives or bargaining agents, and any other witness or individual who may be involved in the grievance process including individuals who serve as mediators, adjudicators, or arbitrators.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Les employés actuels et les anciens employés des institutions fédérales, leurs représentants ou agents négociateurs, et tout autre témoin ou personne associé à la procédure de règlement des griefs, y compris les personnes qui agissent comme médiateurs, membres de jury ou arbitres.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Personal information is used for informal conflict resolution and/or to administer individual or group grievances at each of the levels in the grievance process. For most government institutions, personal information is collected pursuant to sections 207 and 208 of the Public Service Labour Relations Act and sections 66 and 76 of the Public Service Labour Relations Board Regulations. For those institutions not subject to the Act or Regulations, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour résoudre les conflits et/ou administrer des griefs individuels ou collectifs à chacun des niveaux de la procédure de règlement des griefs. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis conformément aux articles 207 et 208 de la Loi sur les relations de travail dans la fonction publique, et aux articles 66 et 76 du Règlement de la Commission des relations de travail dans la fonction publique. En ce qui concerne les institutions qui ne sont pas assujetties à ces lois, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Information concerning grievances filed under the Public Service Labour Relations Act may be shared with the Public Service Labour Relations Board (refer to Central Personal Information Banks: Applications for Extension of Time - PSLRB PCE 710 , Applications for an extension of time in respect of a grievance - PSLRB PCE 715 , Complaint/Grievance Mediation - PSLRB PCE 726 , Complaints under Section 190 of the Public Service Labour Relations Act (PSLRA) - RLT PCE 730 , and Requests for Review of Decisions – PSLRB PCE 793 . Certain complaints may be referred to mediation, adjudication, or arbitration by the Public Service Labour Relations Board (refer to Central Personal Information Banks: References of Grievances to Adjudication - PSLRB PCE 791 and Reference to Adjudication of Individual Grievances - PSLRB PCE 792 ). In these cases, information may be disclosed to individuals who are appointed by the Public Service Labour Relations Board or by a government institution to serve as mediators, adjudicators or arbitrators. Full-text versions of decisions are posted on the Public Service Labour Relations Board website. In some cases, information may be shared with the Canadian Human Rights Commission where a party to a grievance raises an issue involving the interpretation or application of the Canadian Human Rights Act within the context of a request for arbitration of the grievance. Aggregate information may be used or disclosed for annual reporting purposes. Some information about grievances may also be shared with/described in Standard Personal Information Banks Employee Personnel Record - PSE 901 and Discipline - PSE 911 . Information may also be used or disclosed for evaluation purposes.  |  Links: Applications for Extension of Time - PSLRB PCE 710 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Applications for an extension of time in respect of a grievance - PSLRB PCE 715 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Complaint/Grievance Mediation - PSLRB PCE 726 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Complaints under Section 190 of the Public Service Labour Relations Act (PSLRA) - RLT PCE 730 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Requests for Review of Decisions – PSLRB PCE 793 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); References of Grievances to Adjudication - PSLRB PCE 791 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Reference to Adjudication of Individual Grievances - PSLRB PCE 792 (http://pslrb-crtfp.gc.ca/reports/intro_e.asp); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>PRN 926</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>NDP 926</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe910</t>
         </is>
@@ -3024,117 +3030,120 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>PSE 919</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>pse919</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>poe919</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Harassment and Violence</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Harcèlement et violence</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>This bank describes personal information related to the resolution process for occurrences of harassment and violence. In addition to the formal process, this bank also describes personal information related to any informal conflict management process. Personal information may include, but is not limited to name(s) of principal and responding parties and witnesses, contact information, physical attributes, employee personnel information, criminal charges/investigation information, financial information, biographical information, employment equity information, medical information, the date, nature, and location of the alleged occurrence, opinions and views of or about individuals, signatures.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels liés au processus de règlement des incidents de harcèlement et de violence. Outre le processus officiel, ce fichier décrit aussi les renseignements personnels liés à tout processus de gestion informelle du conflit. Les renseignements personnels peuvent comprendre, entre autres, le ou les noms de la partie principale, de la partie intimée et des témoins, les coordonnées, les attributs physiques, les renseignements personnels de l’employé, le numéro d’identification de l’employé, les renseignements relatifs à des accusations au criminel ou à une enquête criminelle, les renseignements financiers, les renseignements biographiques, les renseignements sur l’équité en emploi, les renseignements médicaux, la date, la nature et le lieu de l’incident présumé, les opinions et les points de vue sur, ou concernant, des individus et les signatures.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>This standard personal information bank was last updated in July 2025.</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Le présent fichier de renseignements personnels ordinaire a été mis à jour en juillet 2025.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Employees and other persons working for a government institution, or other persons involved in alleged occurrences of harassment and violence in federal institutions.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Information is used to prevent, resolve and investigate harassment and violence notices of occurrence (including through early resolution and conciliation processes), ensuring that all parties involved are treated with respect and dignity throughout the process. Procedural fairness is upheld by providing the principal party and responding party with the opportunity to be heard, ensuring that decisions are made impartially and maintaining transparency in the resolution process.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Les renseignements sont utilisés pour prévenir et régler les incidents de harcèlement et de violence et mener des enquêtes sur les avis d’incident reçus (notamment au moyen de processus de règlement rapide et de conciliation), en veillant à ce que toutes les parties concernées soient traitées avec respect et dignité tout au long du processus. L’équité procédurale est garantie en donnant  à la partie principale et à la partie intimée la possibilité d’être entendues, en veillant à ce que les décisions soient prises de manière impartiale et en assurant en tout temps la transparence du processus de règlement.</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Information may be disclosed to third-party mediation services and investigators. Occurrence allegations, drafts, and final reports may be disclosed to the principal party and the responding party in accordance with the principles of procedural fairness. Reports that do not reveal, directly or indirectly, the identity of persons who are involved in an occurrence or the resolution process for an occurrence may be disclosed to managers, designated recipients, labour relations, workplace health and safety committees, health and safety representatives.</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Les renseignements peuvent être communiqués à des services de médiation tiers et à des enquêteurs. Les allégations d’incident, les rapports provisoires et finaux peuvent être communiqués à la partie principale et à la partie intimée, conformément aux principes d’équité procédurale. Les rapports qui ne révèlent pas, directement ou indirectement, l’identité des personnes en cause dans un incident ou dans le processus de règlement d’un incident peuvent être communiqués aux gestionnaires, aux destinataires désignés, aux relations de travail, aux comités de santé et de sécurité au travail et aux représentants en matière de santé et de sécurité.</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>PRN 922, PRN 926</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>NDP 922, NDP 926</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse919</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe919</t>
         </is>
@@ -3148,97 +3157,95 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>PSU 908</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>psu908</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>pou908</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>This bank describes information related to the provision of beverages, meals, tours or other entertainment reimbursed by government institutions. Personal information may include name, contact information, employee personnel information, employee identification number, and financial information.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés à la fourniture de breuvages, de repas, de visites guidées ou d’autres divertissements remboursés par les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements personnels de l’employé, le numéro d’identification d’employé et les renseignements financiers.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Employees of the government institution who incur hospitality expenses, their spouses, other attendees, private sector hospitality providers and/or other individuals who may be paid out of the Consolidated Revenue Fund (i.e. who receive a fee, honorarium or per diem allowance).</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Personal information is used to administer the hospitality expenses and reimbursements of government institutions. For most government institutions, personal information is collected pursuant to the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour administrer les frais d’accueil et les remboursements des institutions fédérales. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis conformément à la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Where applicable, hospitality expenses incurred by the Minister, Parliamentary Secretary, exempt staff, and by senior level employees (i.e. Deputy Minister, Associate Deputy Minister, Assistant Deputy Minister, and equivalent) may be proactively disclosed on government institutions’ websites. Information may be shared with/described in Standard Personal Information Bank Accounts Payable - PSU 931 . Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931)</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>PRN 933, PRN 935</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu908</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou908</t>
         </is>
@@ -3252,109 +3259,110 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>PSU 935</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>POU 935</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>psu935</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>pou935</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Human Resources Planning</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Planification des ressources humaines</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>This bank describes information related to salary management and human resources planning, including reporting and forecasting functions. Personal information may include name, contact information, biographical information, educational information, employee identification number, employee equity information, employee personnel information, and opinions and views of, or about, individuals.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information liée à la gestion salariale et à la planification des ressources humaines, ce qui comprend les fonctions de compte rendu et d’établissement des prévisions. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements sur l’éducation, le numéro d’identification de l’employé, les renseignements sur l’équité en emploi, les renseignements personnels de l’employé, et les opinions et points de vue sur, ou concernant, des individus.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, job applicants, students, casual and contract employees, and Interchange Canada participants.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Les employés actuels et les anciens employés d’institutions fédérales, y compris les demandeurs d’emploi, les étudiants, les employés occasionnels et contractuels, et les participants à échanges Canada.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Personal information is collected to assess current and future human resources and salary requirements. Information may be used for a number of activities, including succession planning, facilities management, duty to accommodate persons with disabilities, determining vacancy and turnover rates, and workforce adjustment. Some information may be collected by means of employee exit interviews, which are used to identify issues, trends, and needs in the organization. For many institutions, personal information is collected pursuant to the Financial Administration Act, Public Service Employment Act, Employment Equity Act, and the Canadian Human Rights Act (section 16). For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont recueillis pour évaluer les besoins actuels et à venir en ressources humaines et en salaires. Ces renseignements peuvent servir à diverses activités, notamment la planification de la relève, la gestion des installations, l’obligation de prendre des mesures d’adaptation pour les personnes handicapées, déterminer les taux de roulement et de postes vacants et le réaménagement de l’effectif. Pour nombre d’institutions, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques, la Loi sur l’emploi dans la fonction publique, la Loi sur l’équité en matière d’emploi et la Loi canadienne sur les droits de la personne (article 16). En ce qui concerne les institutions qui ne sont pas assujetties à ces lois, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Personal information may be shared with other government institutions in cases of transfer of section of the public service under the Public Service Rearrangement and Transfer of Duties Act. Personal information may be shared with provincial or municipal governments, and institutions thereof, or private sector institutions in cases of devolution or privatization of a program or activity. Some employee information may also be shared with/described in the Standard Personal Information Banks Employment Equity Program - PSE 918 , Employee Personal Record - PSE 901 , Pay and Benefits - PSE 904 , Staffing - PSE 902 , Training and Development - PSE 905 , and Official Languages - PSE 906 . Information may be also be used or disclosed for program evaluation.  |  Links: Employment Equity Program - PSE 918 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse918); Employee Personal Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904); Staffing - PSE 902 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse902); Training and Development - PSE 905 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905); Official Languages - PSE 906 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse906)</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>PRN 949</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>NDP 949</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou935</t>
         </is>
@@ -3368,109 +3376,110 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>PSU 941</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>psu941</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>pou941</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Internal Audit</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Vérification interne</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>This bank describes personal information related to a government institution’s internal audit program, or horizontal audits directed, led or performed by the Office of the Comptroller General (Treasury Board of Canada Secretariat) or the Office of the Auditor General. Personal information may include name, contact information, signature, employee identification number, financial information, gender, and other personal information in relevant records held by the institution.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Le présent fichier décrit les renseignements personnels ayant trait à un programme de vérification interne d’une institution fédérale ou aux vérifications horizontales orientées, dirigées ou exécutées par le Bureau du contrôleur général (Secrétariat du Conseil du Trésor du Canada) ou par le Bureau du vérificateur général. Les renseignements personnels peuvent inclure le nom, les coordonnées, la signature, le numéro d’identification d’employé, des renseignements financiers, le sexe, et les renseignements qui figurent dans les documents pertinents détenus par l’institution.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Personal information in the institution’s records may be disclosed to the Office of the Auditor General for the purposes of audits or studies.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Les renseignements personnels qui se trouvent dans les documents de l’institution peuvent être divulgués au Bureau du vérificateur général pour des études ou des vérifications.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Employees and former employees of the institution, contractors, representatives of companies.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Les employés et les anciens employés de l’institution, les entrepreneurs, les représentants d’entreprises.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Personal information is used to perform the  institution’s internal audit program. In some cases, the audit program may  include an investigative function (e.g., fraud, investigation). For many  institutions, information is collected pursuant to an internal audit  contemplated in sections 7 and 16.1 or 133 of the Financial Administration Act.  For those institutions not subject to the Act, consult the institution’s Access  to Information and Privacy Coordinator or their legal services to determine the  legal authority for the internal audit for which the collection is required.</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à mettre en œuvre le programme de vérification interne de l’institution. Dans certains cas, il se peut que le programme de vérification comporte une fonction d’enquête (p. ex., fraude, enquête). Pour nombre d’institutions, les renseignements sont recueillis dans le cadre d’une vérification interne prévue aux articles 7 et 16.1 ou 133 de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi, il faut consulter le coordonnateur de l’accès à  l’information et de la protection des renseignements personnels de l’institution ou ses services juridiques afin de déterminer l’autorité législative pour la vérification interne pour laquelle la collecte est requise.</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Information may be shared with responsible managers, and in some cases, the government institution Audit Committee, the Audit Committee of the Board of Directors, the Board of Directors, and/or the Office of the Auditor General. Information may be also be shared with: 1) Human Resources for disciplinary measures (refer to Discipline – PSE 911 ); 2) Security (refer to Security Incidents and Privacy Breaches – PSU 939 ); 3) Investigative personnel and law enforcement agencies in the event of an alleged criminal offence; and 4) consultants performing internal audit work on behalf of the institution’s Chief Audit Executive.  |  Links: Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911); Security Incidents and Privacy Breaches – PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939)</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>NDP 916</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu941</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou941</t>
         </is>
@@ -3484,109 +3493,110 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>PSU 915</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>psu915</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>pou915</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Internal Communications</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Communications internes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>This bank describes information used to communicate with individuals internal to the institution and may include employee surveys (which are considered to be public opinion research), internal communications material, internal mailing and distribution lists, success stories, and information posted to social media sites including wikis, blogs, and other collaborative technologies that are utilized or hosted by the institution. Personal information may include name, work contact information, user names and passwords, employee personnel information, biographical information, photographs, video and audio recordings, views and opinions of, or about, individuals, and Internet Protocol routing addresses.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements utilisés pour communiquer avec les personnes qui travaillent dans l’institution et peut comprendre les sondages auprès des employés (qui sont considérés comme étant de la recherche sur l’opinion publique), le matériel de communication interne, les listes internes d’envoi/de distribution, les histoires de réussite, et l’information publiée dans les sites des médias sociaux, y compris les wikis, les blogues, ainsi que d’autres technologies collaboratives qui sont utilisées ou hébergées par l’institution. Les renseignements personnels peuvent comprendre le nom, les coordonnées au travail, les noms d’utilisateur et les mots de passe, les renseignements personnels de l’employé, les renseignements biographiques, les photos, les enregistrements audio et vidéo, les opinions et points de vue sur, ou concernant, des individus, ainsi que les adresses de transmission du protocole Internet.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>This information may be stored in either hard copy format or electronically (e.g., in databases or on websites, including social media applications, etc.). Although Internet Protocol addresses are not specifically requested by an institution, they may be captured electronically when an e-mail is received.</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Ces renseignements peuvent être stockés sous forme papier ou électronique (p. ex., dans des bases de données ou dans des sites Web, y compris les applications de médias sociaux, etc.). Bien qu’une institution ne demande pas les adresses du protocole Internet expressément, celles-ci peuvent être saisies de manière électronique à la réception d’un courriel.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Employees and other individuals with access to institutional networks including individuals who have prepared information for dissemination, such as publication on the institution’s intranet, or who act as contact points within the institution.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Personal information is used to manage internal communications. For many institutions, personal information is collected under the authority of the Financial Administration Act, and in accordance with the Communications Policy of the Government of Canada. For those institutions not subject to the Act or the Policy, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour gérer les communications internes. Pour un bon nombre d’institutions, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques, et conformément à la Politique de communication du gouvernement du Canada. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi ou politique, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>The names, photographs, recordings and other personal information about individuals who work for the institution may be included in documentation posted on the institution’s intranet: e.g., within speeches, newsletters, etc. Information may be used or disclosed to provide statistical reports to management as well as for program evaluation.</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>PRN 939</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>NDP 939</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu915</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou915</t>
         </is>
@@ -3600,101 +3610,100 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>PSU 936</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>psu936</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>pou936</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Library Services</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Services de bibliothèque</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>This bank describes information about individuals who use the facilities, collections, and services of libraries of government institutions. Services may include loans, reference and research, and alerting and current awareness services, including consideration of client requests for new acquisitions. Personal information may include name, contact information, organization affiliation, research topic, other identification numbers, including user card number and expiration date and client barcode number.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information sur les personnes qui utilisent les installations, les collections et les services de bibliothèques des institutions fédérales. Les services peuvent comprendre les prêts, les références et la recherche, ainsi que les services d’avertissement et de mises au courant, dont l’évaluation des demandes des clients quant aux nouvelles acquisitions. Les renseignements personnels peuvent comprendre le nom, les coordonnées, l’affiliation de l’organisme, le sujet de recherche, d’autres numéros d’identification, y compris le numéro de carte de l’utilisateur et sa date d’expiration, ainsi que le numéro de code à barres du client.</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Full-and part-time, casual, and term employees of government institutions, agency employees, members of the general public, researchers, and employees of non-government institution libraries.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Personal information is used to support the delivery of library services of government institutions, such as identifying user preferences, researching topics, analyzing trends in information needs, processing inter-library loans, and controlling the circulation of material.</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés dans le but d’appuyer la prestation des services de bibliothèque des institutions fédérales, comme la détermination des préférences des utilisateurs, la recherche selon les sujets, l’analyse des tendances des besoins informationnels, le traitement des prêts entre bibliothèques, et le contrôle de la circulation des documents.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Information may be used or disclosed for program evaluation.</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>PRN 944</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>NDP 944</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu936</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou936</t>
         </is>
@@ -3708,109 +3717,110 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>PSU 937</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>POU 937</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>psu937</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>pou937</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Lobbying Act Requirements</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Exigences de la Loi sur le lobbying</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>This bank describes information collected by designated public office holders (e.g., current and former Deputy Heads, Assistant Deputy Ministers, senior members of the Canadian Forces, etc.) for the verification of lobbyist activities when requested by the Commissioner of Lobbying. Personal information may include name, contact information, financial information, biographical information, date, and time of the communication/lobbying activity, opinions and views of, or about, individuals, and subject matter.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information recueillie par les titulaires d’une charge publique désignée (p. ex., les administrateurs généraux actuels et les anciens administrateurs généraux, les sous-ministres adjoints, les cadres supérieurs des Forces canadiennes, etc.) au sujet de la vérification des activités des lobbyistes sur demande du commissaire au lobbying. Les renseignements personnels peuvent comprendre le nom, les coordonnées, de l’information financière, des renseignements biographiques, la date et de l’heure de l’activité de communication/lobbying, ainsi que les opinions et les points de vue des individus sur le sujet.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Designated public office holders and lobbyists as defined in the Lobbying Act.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Les titulaires d’une charge publique et les lobbyistes comme le définit la Loi sur le lobbying.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Information is collected pursuant to section 5 of the Lobbying Act to verify arranged meetings, telephone calls, and correspondence between public office holders and lobbyists. Lobbyists who have oral, arranged communications with designated public office holders must report these communications to the Commissioner of Lobbying; in turn, designated public officer holders must verify these communications if requested by the Commissioner of Lobbying.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Les renseignements sont recueillis en vertu de l’article 5 de la Loi sur le lobbying pour vérifier les réunions, les appels téléphoniques et la correspondance prévus entre les titulaires de charge publique et les lobbyistes. Les lobbyistes qui prévoient des échanges de vive voix avec des titulaires d’une charge publique désignée doivent rendent compte de ces échanges au commissaire au lobbying; les titulaires d’une charge publique doivent, quant à eux, vérifier ces échanges si le commissaire le demande.</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Information may be made accessible to the public via the website of the Office of the Commissioner of Lobbying of Canada (refer to Information-Specific Personal Information Bank Lobbyist Registry - OCL PPU 039 ). Information may be also be used or disclosed for program evaluation.  |  Links: Lobbyist Registry - OCL PPU 039 (https://lobbycanada.gc.ca/eic/site/012.nsf/eng/00843.html)</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de dossiers administratifs courants par une institution fédérale, y compris la destruction finale de ces dossiers, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>PRN 904</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>NDP 904</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu937</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou937</t>
         </is>
@@ -3824,105 +3834,105 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>PSU 919</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>psu919</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>pou919</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Members of Boards, Committees and Councils</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Membres de conseils d’administration, de comités et de conseils</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>This bank describes information used in the identification and selection of individuals to fill positions on institutional Boards, Committees and Councils. The personal information collected may include the following: full name, contact information, official language of choice, date of birth, country of birth, citizenship, gender, marital status, belonging to a minority, Social Insurance Number (SIN), unique identification number (e.g., unique employee number), terms and conditions of appointment including remuneration (e.g., salary, honoraria, per diem rate) and benefits, signature, physical limitations and any other relevant medical information, photographs or other image recordings, educational background, employment status, work history, volunteering history, professional affiliations, credit card and financial institution information, government security clearances, biographical information (including information about family members), conflict of interest declarations, letters of reference/recommendation, appointment date, and duration and resignation dates, if applicable.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels utilisés dans le processus d’identification et de sélection des personnes qui seront nommées aux conseils d’administration, comités et conseils de diverses institutions. Les renseignements personnels peuvent comprendre : le nom complet de la personne, ses coordonnées, sa langue officielle de préférence, sa date de naissance, son pays natal, sa citoyenneté, son sexe, sa situation de famille, son appartenance à un groupe minoritaire, son numéro d’assurance sociale (NAS), un numéro d’identification exclusif (p. ex., un numéro d’employé unique), les modalités de sa nomination, y compris sa rémunération (p. ex., traitement, honoraires, indemnité quotidienne) et ses avantages sociaux, sa signature, ses limitations physiques et toute autre information médicale pertinente, des photographies ou d’autres enregistrements visuels, sa scolarité, sa situation d’emploi, ses antécédents de travail, ses activités bénévoles, ses affiliations professionnelles, de l’information sur ses cartes de crédit et son établissement bancaire, sa cote de sécurité au gouvernement, des données biographiques (y compris des renseignements sur les membres de sa famille), toute déclaration de conflit d’intérêts, des lettres de référence/de recommandation, la date de nomination, la durée de la nomination et la date de démission, s’il y a lieu.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Candidates, as well as current and former members of Boards, Committees, and Councils, their family members, and individuals whose names have been provided as personal references.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Les candidats, ainsi que les membres actuels et anciens de conseils d’administration, de comités et de conseils, les membres de leur famille, ainsi que les personnes dont le nom a été donné à titre de référence personnelle.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>The personal information collected is used to support the identification and selection of individuals to serve on advisory, oversight or governance bodies. The information may be used to provide advice to the Minister or Head of the institution to fill existing and/or forthcoming vacancies and to maintain an inventory of potential candidates. The personal information is also used to manage the administration of expenses (e.g., travel) and compensation and benefits packages, conduct performance evaluations, maintain an inventory of current and former appointees, record potential conflicts of interest and any compliance action required, and to communicate with these individuals. The authority to collect personal information is found in a number of legislative authorities such as section 9 Department of Employment and Social Development Act and section 22 of the Museums Act. The Social Insurance Number is collected pursuant to the Income Tax Act. Please consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection by a specific government institution.</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Les renseignements personnels recueillis sont utilisés à l’appui de l’identification et de la sélection des personnes qui seront nommées membres d’organes de consultation, de surveillance ou de gouvernance. Ils pourront être utilisés pour conseiller le ministre ou le dirigeant de l’institution fédérale au moment de pourvoir des postes actuellement ou prochainement vacants et pour tenir un répertoire de candidats possibles. Les renseignements personnels servent aussi à gérer l’administration des dépenses (p. ex., les frais de voyage) et les régimes de rémunération et d’avantages sociaux, à évaluer le rendement, à tenir un répertoire des membres actuels et anciens, à enregistrer d’éventuels conflits d’intérêts et toute mesure de conformité nécessaire, ainsi qu’à communiquer avec ces personnes. Le pouvoir de collecter des renseignements personnels est prévu par de nombreuses autorités législatives, comme l’article 9 de la Loi sur le ministère de l’Emploi et du Développement social et l’article 22 de la Loi sur les musées. Le numéro d’assurance sociale est recueilli conformément à la Loi de l’impôt sur le revenu. Veuillez consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution fédérale afin de déterminer l’autorité législative pour la collecte par une institution fédérale donnée.</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>This information may be used in the preparation of reports for senior management and broader audiences (e.g., Annual Reports), planning and evaluation purposes, and communications materials (e.g., press releases, biographies, etc.) that may be disseminated in multiple formats, including the institution’s website. With consent of the individual, this information may be shared with other Government of Canada institutions for uses consistent with the mandate of the Board, Committee or Council on which personal information is collected to fill positions (Refer to Members of Boards, Committees and Councils – PSU 919 of the specific government institution). Information may be disclosed to the Canada Revenue Agency (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and, where applicable, the Province of Quebec for income tax purposes. Assistance of third party service providers may be used during the selection process.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution fédérale pour connaître la durée de conservation, par une institution fédérale, de certains types de documents administratifs communs, y compris leur destruction finale.</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Institution-Specific</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Propre à l’institution fédérale</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>PRN 938</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>NDP 938</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu919</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou919</t>
         </is>
@@ -3936,101 +3946,100 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>PSE 907</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>pse907</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>poe9071</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Occupational Health and Safety</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Santé et sécurité au travail</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>This bank describes information that is used in support of a government institution’s occupational health and safety activity, including the prevention of accidents and injuries or illnesses related to occupations, authorization of leave and benefits associated with work-related injury or illness, employee assistance services, fitness to return to work assessments, duty to accommodate, health and ergonomic assessments, health and safety complaints, injury compensation, and rehabilitation and retraining. Personal information may include name, contact information, employee identification number, employee personnel information, financial information, nature of complaint, medical information, opinions and views of, or about, individuals, and signature.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Ce fichier décrit l’information qui est utilisée dans le but d’appuyer une activité liée à la santé et à la sécurité du travail dans une institution fédérale, y compris la prévention des accidents et des blessures ou des maladies de nature professionnelle; une autorisation de congé payé liée à un accident du travail ou une maladie professionnelle; les services d’aide aux employés; les évaluations sur l’aptitude à retourner au travail; l’obligation de prendre des mesures d’adaptation; les évaluations de santé et de nature ergonomique; les plaintes relatives à la santé et à la sécurité; l’indemnisation des accidentés; la réadaptation et le recyclage. Les renseignements personnels peuvent comprendre le nom, les coordonnées, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, la nature de la plainte, les renseignements médicaux, les opinions et les points de vue sur, ou concernant, des individus, et la signature.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, including casual and contract employees; private sector health practitioners; health and safety professionals; attendants for persons requiring assistance; family members who are part of the same household and eligible for corporate rates for Wellness programs; and individuals designated as emergency contacts of employees</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Personal information is used to administer occupational safety and health activities in government institutions, which includes the promotion of a safe and healthy workplace for employees and others, provision of corporate Wellness programs, the prevention of accidents, occupational injuries and illnesses and, where applicable, the investigation of occurrences of such injuries and illnesses. Information may be collected pursuant to paragraph 7(1)(e) and subsection 11.1 of the Financial Administration Act; sections 114 and 240 of the Public Service Labour Relations Act; Part II of the Canada Labour Code and Part XVI of the Canada Occupational Health and Safety Regulations, the Government Employees Compensation Act, and the National Joint Council Directives.</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour l’administration des activités sur la santé et la sécurité au travail dans les institutions fédérales, ce qui comprend la promotion d’un milieu de travail sécuritaire et sain pour les employés et les autres personnes, la prestation de programmes de mieux-être au travail, la prévention des accidents, des blessures et des maladies professionnelles et, le cas échéant, la tenue d’enquêtes lorsque de telles blessures et maladies se produisent. Les renseignements peuvent être recueillis en vertu de l’alinéa 7(1)e) et du paragraphe 11.1 de la Loi sur la gestion des finances publiques; des articles 114 et 240 de la Loi sur les relations de travail dans la fonction publique; de la partie II du Code canadien du travail, et de la partie XVI du Règlement canadien sur la santé et la sécurité au travail; de la Loi sur l’indemnisation des agents de l’état, et des directives du Conseil national mixte.</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Information may be used or disclosed for the following reasons: to support decisions related to worker’s compensation and injury-on-duty leave; as a means of preventing injuries and illnesses and subsequent disabilities arising out of, or aggravated by, conditions of work; to establish that individuals subject to certain identified occupational risks are able to continue working without detriment to their health or safety or to that of others; and to establish the conditions under which certain individuals with identified illnesses or disabilities are able to continue to work under controlled conditions. Information may be shared with private sector health care providers. Information may be used to communicate with contacts of employees in emergency situations. Information concerning occupational health evaluations including related personal medical information is retained by Health Canada in the Corporate Services Branch under medical confidential status (refer to Central Personal Information Bank: Public Service Occupational Health Program - HC PCE 701 ). Information with respect to safety and health complaints and causes of accidents/injuries for accident prevention and health protection purposes is used to support the effective administration of each institution’s safety and health activity; such information is also disclosed to the institution’s work place health and safety committee. Information is also used to process payments and charge-backs with respect to injury compensation claims. Information related to injury compensation claims, including related correspondence and amounts paid, is retained by Employment and Social Development Canada and is shared with the institution of the affected employee and, where applicable, the relevant provincial or territorial workers’ compensation board. Employment and Social Development Canada holds information pertaining to employee compensation amounts, which are charged to institutions and distributed on a cost-recovery basis (refer to Personal Information Bank: Federal Workers Compensation - ESDC PPU 032 ). Information may also be shared with Employment and Social Development Canada, specifically, with safety officers for the purposes of accident and refusal to work investigations and the stipulation of corrective measures. Information may be shared with/described in other Standard Personal Information Banks pertaining to human resources activities including: Employee Personnel Record - PSE 901 ; Attendance and Leave - PSE 903 ; Employee Assistance - PSE 916 ; Pay and Benefits - PSE 904 ; and Grievances - PSE 910 . The investigation and settlement of vehicle accidents is also described in Standard Personal Information Bank Vehicle, Ship, Boat and Aircraft Accidents - PSE 908 . Information may also be used or disclosed for planning and program evaluation purposes.  |  Links: Public Service Occupational Health Program - HC PCE 701 (https://www.canada.ca/en/health-canada/corporate/about-health-canada/activities-responsibilities/access-information-privacy/info-source-federal-government-employee-information.html#a3.14); Federal Workers Compensation - ESDC PPU 032 (http://www.esdc.gc.ca/eng/transparency/ati/reports/infosource/index.shtml); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Attendance and Leave - PSE 903 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse903); Employee Assistance - PSE 916 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse916); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910); Vehicle, Ship, Boat and Aircraft Accidents - PSE 908 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse908)</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>PRN 922</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>NDP 922</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse907</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071</t>
         </is>
@@ -4044,117 +4053,120 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>PSE 906</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>pse906</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>poe906</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Official Languages</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Langues officielles</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>This bank contains course enrolment and attendance information; language training applications containing basic personal data, such as first official language, date of birth, and Personal Record Identifier for purposes of identification; language knowledge examination scores; training certificates and correspondence about the official languages qualifications of employees. The bank may also contain duplicate input forms for the Official Languages Information System. Language examination, exemption and training records are attached to the employee personnel record.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Ce fichier contient des renseignements sur les inscriptions aux cours et les présences; des demandes de formation linguistique comprenant des données personnelles de base utilisées à des fins d’identification, comme la principale langue officielle de l’employé, sa date de naissance et son Code d’identification de dossier personnel; les résultats des examens de connaissance linguistique; les certificats pour les formations et complété la correspondance concernant les qualifications de l’employé en matière de langues officielles. Le fichier peut également comprendre un double de la formule destinée au Système d’information sur les langues officielles. Les examens linguistiques, les dossiers concernant la formation et les exemptions sont joints au dossier personnel de l’employé.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>The purpose of the information described by this bank is to provide documentation for administration of official languages policies as they pertain to employees of federal government institutions, to document and support decisions pertaining to official languages qualifications and language testing and to document the language training needs and accomplishments of employees.</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Les renseignements décrits dans ce fichier ont pour but de fournir la documentation nécessaire à l’administration des politiques en matière de langues officielles régissant les employés des institutions fédérales. Ils visent à justifier et à étayer les décisions touchant les qualifications en matière de langues officielles et les épreuves linguistiques, ainsi qu’à justifier le besoin en formation linguistique et à confirmer les réalisations des employés.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>To support and document decisions concerning individual employees on staffing, entitlement to bilingual bonus where applicable, transfers and promotions; and to aid in determining the linguistic status of employees and auditing of the administration of official language programs. Information may be disclosed to federal government institutions, the Public Service Commission and Treasury Board of Canada Secretariat where applicable for recruitment and staffing purposes (refer to Institution-Specific Personal Information Banks: for the Public Service Commission of Canada: Executive Resourcing - PSC PCE 746 ; for Treasury Board of Canada Secretariat: Employment Equity Data Bank - TBS PCE 739 ).  |  Links: Executive Resourcing - PSC PCE 746 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp)</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>PRN 923</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>NDP 923</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse906</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe906</t>
         </is>
@@ -4168,113 +4180,115 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>PSU 938</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>psu938</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>pou938</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Outreach Activities</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Activités de sensibilisation</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>This bank describes information related to individuals who participate in outreach activities sponsored by government institutions. Such activities may involve consultations through various means, including hard-copy correspondence, e-mail, contests and competitions, success stories or the use of social media platforms including wikis, blogs, and other collaborative Internet technologies that are used or hosted by the institution. In some cases, individuals will be given prior notice that consultations will be recorded (audio or video). Types of activities may include surveys, symposia, conferences, forums, roundtables, seminars, and workshops. Personal information may include: name, contact information, biographical information, credit information, dietary restrictions and preferences, employee identification number, employment equity information, financial information, Internet Protocol (IP) addresses, medical information, and opinions and views of, or about, individuals.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés aux personnes qui participent aux activités de sensibilisation parrainées par des institutions fédérales. De telles activités peuvent comprendre des consultations par l’entremise de divers moyens, dont la correspondance épistolaire, les courriels, les jeux-questionnaires et les concours, les histoires de réussite ou l’utilisation de plateformes de médias sociaux, y compris les wikis, les blogues, ainsi que d’autres technologies Internet collaboratives qui sont utilisées ou hébergées par l’institution. Dans certains cas, les personnes recevront un avis les avisant que les consultations seront enregistrées sur bande audio ou vidéo. Les types d’activités peuvent comprendre les sondages, les colloques, les conférences, les forums, les tables rondes, les séminaires et les ateliers. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements sur la solvabilité, les restrictions et préférences alimentaires, le numéro d’identification d’employé, les renseignements sur l’équité en emploi, les renseignements financiers, les adresses du protocole Internet, les opinions et les points de vue sur, ou concernant, des individus.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Wherever possible, individuals seeking access to this bank should specify the title and date of the outreach activity. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Dans la mesure du possible, les personnes qui désirent avoir accès à leurs renseignements personnels doivent préciser le titre et la date de l’activité de sensibilisation. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, representatives of other levels of government, representatives of the academic and business communities, members of the general public (including parents and guardians where minors are concerned), and event speakers and facilitators.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>The information is used to enable individuals to participate in national and/or international outreach activities sponsored by government institutions. Such activities facilitate information exchanges in areas of common interest to institutions and their stakeholders and allow for the sharing of knowledge, expertise, and best practices. Personal information is collected pursuant to various federal laws and regulations. For the specific collection authority(ies), consult the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Ces renseignements sont utilisés afin de permettre aux personnes de participer aux activités nationales ou/et internationales de sensibilisation parrainées par les institutions fédérales. De telles activités facilitent les échanges d’information sur les champs d’intérêt communs des institutions et de leurs interlocuteurs, et permettent le partage des connaissances, de l’expertise et des pratiques exemplaires. Les renseignements personnels sont recueillis conformément aux diverses lois et règlements. Consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution pour déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>With notification, the proceedings of some outreach activities that are recorded may be made publicly available, including on the Internet. With consent, the information may be used to establish mailing lists to inform participants of future events or to contact individuals to seek views on issues of mutual interest. Information may be used to moderate public discussion on the social media platforms used by the institution. Information may be also be used or disclosed for program evaluation.</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Institution-specific</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>PRN 904</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>NDP 904</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu938</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou938</t>
         </is>
@@ -4288,101 +4302,100 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>PSE 914</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>pse914</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>poe914</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Parking</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Stationnement</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>This bank describes personal information related to parking permit applications and parking space permit holders of spaces on government institution-owned or leased property. Personal information may include name, work and home contact information, biographical information, employee identification number, employee personnel information, financial information, medical information (for those individuals who apply for parking for disability requirements), vehicle identification information, rating factors, and signature.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels liés aux demandes de permis de stationnement et aux détenteurs de permis de stationnement pour des propriétés louées par ou appartenant à des institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées à la maison et au travail, les renseignements biographiques, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, les renseignements médicaux (pour ceux qui demandent un stationnement pour les personnes handicapées), les renseignements d’identification du véhicule, les critères de tarification, et la signature.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Employees of the institution, passengers, contractors or other individuals, property owners or representatives.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Personal information is used for the administration of parking privileges and to authorize payroll deductions. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour administrer les droits au stationnement, et autoriser les retenues à la source. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Where government or other property is damaged, the accident may be reported to the Royal Canadian Mounted Police (refer to Central Personal Information Bank Protection of Personnel and Government Property - RCMP PPU 055) or to other policing authorities, or to the person(s) in charge or in control of the property. Information may be shared with Public Works and Government Services for the purpose of payroll deduction (refer to Central Personal Information Bank Public Service Compensation Systems - PWGSC PCE 705 ). Payroll deduction information may be shared with/described in Standard Personal Information Bank Pay and Benefits - PSE 904 . Information may also be used or disclosed for evaluation or reporting purposes.  |  Links: Public Service Compensation Systems - PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904)</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>PRN 901</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>NDP 901</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse914</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe914</t>
         </is>
@@ -4396,101 +4409,100 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>PSE 904</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>pse904</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>poe904</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Pay and Benefits</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Rémunération et avantages</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>This bank describes information related to the administration of pay and benefits within government institutions. Personal information may include name, contact information, biographical information, date of birth, date of death, employee identification number, employee personnel information, financial information, and Social Insurance Number (SIN).</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés à l’administration de la rémunération et des avantages sociaux au sein des institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, la date de naissance, la date du décès, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, et le numéro d’assurance sociale (NAS).</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Personal information is shared with Public Works and Government Services and is used to disburse salaries and allowances and to process deductions and orders for garnishment and diversion of funds. Personal information is collected under various Acts including the Financial Administration Act, the Government Employees Compensation Act, and the Public Service Labour Relations Act. The Social Insurance Number (SIN) is collected pursuant to the Income Tax Act, Canada Pension Plan, and the Employment Insurance Act, and for some institutions, the SIN is shared with Public Works and Government Services to create the Personal Record Identifier.</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont partagés avec Travaux publics et Services gouvernementaux Canada et sont utilisés pour verser les salaires et les allocations, et pour traiter les retenues et les ordonnances de saisie-arrêt de salaire et de distraction des fonds. Les renseignements personnels sont recueillis en vertu de diverses lois, y compris la Loi sur la gestion des finances publiques, la Loi sur l’indemnisation des agents de l’état, et la Loi sur les relations de travail dans la fonction publique. Le numéro d’assurance sociale est recueilli conformément à la Loi de l’impôt sur le revenu, du Régime de pensions du Canada, et de la Loi sur l’assurance-emploi; pour certaines institutions, le numéro d’assurance sociale est partagé avec Travaux publics et Services gouvernementaux Canada pour créer le code d’identification de dossier personnel.</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Information is shared with Public Works and Government Services Canada (refer to Public Service Compensation Systems -PWGSC PCE 705 and Public Service Pensions Data Bank - PWGSC PCE 702 ). Information, including the SIN, is disclosed to the Canada Revenue Agency (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and the Province of Quebec (if applicable) for taxation and pension purposes. Information may also be shared with the Department of Justice Canada to administer the Family Orders and Agreements Enforcement Assistance Act and the Garnishment, Attachment and Pension Diversion Act (refer to Family Orders and Agreements Enforcement Assistance - JUS PPU 125 and Garnishment Registry - JUS PPU 150 ). Information may be shared with third party service providers, for select institutions. Some information on pay and benefits may also be shared with/described in the Standard Personal Information Banks Employee Personnel File - PSE 901 , Grievances - PSE 910 , and Discipline - PSE 911 . Information may also be used or disclosed for program evaluation.  |  Links: Public Service Compensation Systems -PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Public Service Pensions Data Bank - PWGSC PCE 702 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Family Orders and Agreements Enforcement Assistance - JUS PPU 125 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/index.html); Garnishment Registry - JUS PPU 150 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/p3.html); Employee Personnel File - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>PRN 941</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>NDP 941</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe904</t>
         </is>
@@ -4504,105 +4516,105 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>PSU 917</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>POU 917</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>psu917</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>pou917</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Personnel Security Screening</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Filtrage de sécurité du personnel</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>This bank describes personal information created, collected, used, disclosed and/or retained in relation to the security screening of individuals working or applying for work with a government institution. Personal information may include: name(s), date of birth, date of death, contact information, biographical information, biometric information (e.g., fingerprints, digital photographs, voice, polygraph examination), opinions or assessments of an individual’s character (e.g., loyalty, trustworthiness), citizenship status, credit information, criminal checks and history, law enforcement record checks, educational information, associations and memberships, employee identification numbers, employee personnel information, financial information, unique identifiers, descriptions or images of physical attributes, place of birth, signature, military service information, views and opinions of, or about, individuals, open source intelligence, security assessment information.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Cette banque décrit les renseignements personnels créés, recueillis, utilisés, divulgués et/ou conservés relativement au filtrage de sécurité des personnes qui travaillent auprès d’une institution fédérale ou qui y postule un poste. Les renseignements personnels peuvent comprendre les suivants : noms, date de naissance, date de décès, coordonnées, informations biographiques, informations biométriques (p. ex., empreintes digitales, photos numériques, voix, test polygraphique), opinions ou évaluation du caractère d’une personne (p. ex., loyauté fiabilité), statut de citoyen, informations sur le crédit, vérifications judiciaires et antécédents criminels, vérifications des dossiers sur l’exécution de la loi, informations sur les études, associations et affiliations, numéro d’identification de l’employé, renseignements personnels de l’employé, informations financières, identificateurs uniques, descriptions ou images des attributs physiques, date de naissance, signature, informations sur le service militaire, points de vue et opinions de la personne ou à son sujet, renseignement de sources ouvertes, informations sur l’évaluation de sécurité.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>(1) Information may be stored in either hard copy format or electronically (e.g. in databases). (2) Some institutions have developed institution-specific security screening personal information banks. Individuals seeking access to their information in PSU 917 may also want to request that other institutional PIBs related to security screening be included in the access to information request if they have worked in or for the following departments which maintain separate PIBs: Public Services and Procurement Canada (Industry Personnel Clearance and Reliability Records – PWGSC PPU 015) ; National Defence / Canadian Armed Forces (Personnel Security Investigation File – DND PPU 834) ; Privy Council Office (Security Clearance and Assessments Bank – PCO PPE 801) ; Royal Canadian Mounted Police (Security Reliability Screening Records – RCMP PPU 065) ; and Canadian Security Intelligence Service (Employee Security – SIS PPE 815) .  |  Links: Public Services and Procurement Canada (Industry Personnel Clearance and Reliability Records – PWGSC PPU 015) (https://www.tpsgc-pwgsc.gc.ca/aiprp-atip/infosource2014-eng.html); National Defence / Canadian Armed Forces (Personnel Security Investigation File – DND PPU 834) (https://www.forces.gc.ca/en/transparency-access-info-privacy/info-source-toc.page); Privy Council Office (Security Clearance and Assessments Bank – PCO PPE 801) (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Royal Canadian Mounted Police (Security Reliability Screening Records – RCMP PPU 065) (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/pib-frp-eng.htm); Canadian Security Intelligence Service (Employee Security – SIS PPE 815) (https://www.csis.gc.ca/tp/nfsrc-en.php)</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Job applicants, all current and former employees (students, agency and casual employees, persons on loan, assignment or secondment, exempt staff of ministers, ministers of state and parliamentary secretaries, locally engaged staff), volunteers, contractors, foreign and domestic visitors, immediate relatives, current and former spouse/common law partner, associates, cohabitants, individuals who give character references (including neighbours), current/former employers, parents or guardians of job applicants and employees under the age of 18.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Postulants, employés actuels et anciens (étudiants, employés d’un organisme et employés occasionnels, personnes prêtées, affectation ou détachement, sauf les membres du personnel des ministres, des ministres d’État et des secrétaires parlementaires, le personnel embauché localement), bénévoles, entrepreneurs, visiteurs étrangers et nationaux, proches parents, époux ou conjoints de fait actuels et anciens, associés, cohabitants, personnes qui donnent des références morales (y compris les voisins), employeurs actuels et anciens, parents ou gardiens des candidats à un emploi et employés de moins de 18 ans.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Personal information described in this bank is used to support decisions for granting, denying, revoking, or reviewing for cause the reliability status, security clearance, site access status or site access clearance of individuals working or applying to work through appointment, assignment or contract or other individuals with whom government may share or provide access to sensitive or information or assets, or access to facilities. For most institutions, personal information is collected pursuant to section 7 of the Financial Administration Act and as required under the Standard on Security Screening. That authority carries with it the authority to perform security screenings so as to ensure that individuals being appointed to the public service – and who have access to government information and assets – are reliable and loyal. Institutions may have additional legislative authorities under which security screening is to be performed. For those institutions not subject to the Financial Administration Act or the Standard , consult the institution's Access to Information Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Les renseignements personnels décrits dans ce fichier servent à appuyer les décisions prises pour accorder, refuser ou effectuer un examen justifié de la cote de fiabilité, de la cote de sécurité ou de l’accès au site de personnes travaillant ou postulant par le biais d’une nomination, d’une affectation ou d’un contrat ou d’autres personnes avec qui le gouvernement peut échanger des informations ou des biens de nature délicate, leur donner accès à ceux-ci ou à des installations. Pour la plupart des institutions, les renseignements personnels sont recueillis en vertu de l’article 7 de la Loi sur l’emploi dans la fonction publique et, au besoin, en vertu de la Norme sur le filtrage de sécurité. Ce pouvoir est accompagné de celui d’effectuer un filtrage de sécurité afin de faire en sorte que les personnes nommées dans la fonction publique – et qui ont accès aux informations et aux biens du gouvernement – soient fiables et loyales. Les institutions peuvent détenir d’autres pouvoirs prévus par la loi en vertu desquels un filtrage de sécurité doit être effectué. Pour les institutions non assujetties à la Loi sur l’emploi dans la fonction publique ou à la Norme, veuillez consulter le coordinateur de l’accès à l’information de l’institution afin de déterminer l’autorisation de collecte.</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Where required, personal information may be shared in accordance with the institution's enabling legislation and within the parameters of the Privacy Act, with the Royal Canadian Mounted Police ( Canadian Criminal Real Time Identification Services – RCMP OPS 1214 and Personnel Security Records – RCMP ADM 445 ) and the Canadian Security Intelligence Service ( Security Assessments/Advice Records – CSIS PPU 005 ) to conduct security screening verifications, inquiries and/or assessments in accordance with the Policy on Government Security. Information may be shared with the Canadian Human Rights Commission ( Human Rights Litigation Records – CHRC DRP 020 , Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 ), the Public Service Labour Relations and Employment Board ( Complaint/Grievance Mediation Records – PSLRB ROP 579 ), Justice Canada ( Litigation Services Records – JUS 3.0.5 ) or the Security Intelligence Review Committee ( Complaints Records – SIR COM 001 ) when an individual challenges a decision to deny, suspend or revoke a the required security status or security clearance. Information may be disclosed to the Privy Council Office ( Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 ) should the individual pose a potential risk to national security or is part of a national security-related investigation. The security screening status of an individual may be shared internally within institutions with human resource officials to update the individual's personnel file ( Employee Personnel Record – PSE 901 , Governor in Council Appointments – PSU 918 , Members of Boards Committees and Councils – PSU 919 ). Information may be shared within or between government institutions for staffing purposes ( Staffing – PSE 902 ). Information may be shared within institutions with departmental security officials for issuance of access cards and badges ( Physical Access Controls PSU 907 ). Information may be shared within institutions with departmental security officials in cases of adverse information for investigation ( Security – PRN 931 or Security Incidents and Privacy Breaches – PSU 939 ). Biographical information, including name, date of birth, employment and/or educational history, may be shared with individuals or entities outside the government institution to confirm identity and conduct required inquiries or verifications including: authorized credit reporting agencies, personal and/or professional referees, and educational institutions and/or professional organizations. Information, including the results of security screening checks, may be disclosed to an individual’s manager, labour relations advisors, and/or an institutional security screening advisory board, on a need to know basis, when a decision to deny, revoke or suspend pending an investigation is being considered. Information, including completed security screening forms, the results of security screening checks and decisions made by a department may be shared between institutional security officials to enable transferability of security screening and to help ensure that individuals are not engaged by another government institution without regard to the circumstances leading to any previous denial or revocation which may have taken place in another institution. Select anonymized information may be used or disclosed for program evaluation.  |  Links: Canadian Criminal Real Time Identification Services – RCMP OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Personnel Security Records – RCMP ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Security Assessments/Advice Records – CSIS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-en.php); Human Rights Litigation Records – CHRC DRP 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Complaint/Grievance Mediation Records – PSLRB ROP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_e.asp); Litigation Services Records – JUS 3.0.5 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/p3.html); Complaints Records – SIR COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-eng.html); Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Employee Personnel Record – PSE 901 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Governor in Council Appointments – PSU 918 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Members of Boards Committees and Councils – PSU 919 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Staffing – PSE 902 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Physical Access Controls PSU 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu907); Security – PRN 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-classes-records.html); Security Incidents and Privacy Breaches – PSU 939 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp)</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>Au besoin, les renseignements personnels peuvent être communiqués conformément à la loi habilitante de l'institution et dans les paramètres de la Loi sur la protection des renseignements personnels, à la Gendarmerie royale du Canada ( Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 et Fichiers sur la sécurité du personnel GRC ADM 445 ) et au Service canadien du renseignement de sécurité ( Évaluations de sécurité/Avis – SCRS PPU 005 ) pour qu’ils effectuent des vérifications, des enquêtes et/ou des évaluations de filtrage de sécurité, conformément à la Politique sur la sécurité du gouvernement. Les informations peuvent être communiquées à la Commission canadienne des droits de la personne ( Contentieux en matière de droits de la personne – CCDP REG 020 , Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 ), Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 ) , à la Commission des relations de travail et de l’emploi dans la fonction publique, au ministère de la Justice Canada ( Services de contentieux – JUS 3.0.5 ) ou au Comité de surveillance des activités de renseignement de sécurité ( Plaintes – SCA COM 001 ) lorsqu’une personne conteste une décision visant à refuser, à suspendre ou à révoquer une autorisation de sécurité ou une autorisation d’accès aux sites ou au Bureau du Conseil privé ( Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 ) si la personne pose un risque potentiel à la sécurité nationale ou fait l’objet d’une enquête liée à la sécurité nationale. La cote de filtrage de sécurité d’une personne peut être communiquée à l’interne au sein des institutions aux responsables des ressources humaines afin de mettre à jour le dossier personnel de la personne concernée ( Dossier personnel d’un employé – POE 901, Nominations par le Gouverneur en conseil – POU 918 , Membres de conseils d’administration, de comités et de conseils – POU 919 ). Les informations peuvent être communiquées au sein d’une institution fédérale et entre elles aux fins de dotation ( Dotation – POE 902 ). Les informations peuvent être communiquées au sein des institutions aux responsables de la sécurité ministérielle pour la délivrance de cartes d’accès et de laissez-passer ( Contrôles d’accès physique – POU 907 ). Les informations peuvent être communiquées pour enquête au sein des institutions aux responsables de la sécurité ministérielle dans les cas d’informations préjudiciables ( Sécurité – NDP 931 ou Incidents de sécurité et atteintes à la vie privée – POU 939 ). Les informations peuvent être communiquées à des entités de l’extérieur de l’institution fédérale, y compris les bureaux de crédit pour qu’elles réalisent des enquêtes sur la situation financière. Les renseignements, y compris les résultats du filtrage de sécurité, peuvent être communiqués au gestionnaire d’une personne, aux conseillers en relations de travail, et/ou au conseil consultatif du filtrage de sécurité institutionnel, en fonction du besoin de savoir, lorsqu’une décision de refuser, de révoquer ou de suspendre en attente d’une enquête fait l’objet d’un examen. Les renseignements, y compris les formulaires d’enquête de sécurité dûment remplis, les résultats des vérifications du filtrage de sécurité et les décisions prises par un ministère peuvent être communiqués entre les responsables de sécurité institutionnels afin de permettre la transférabilité du filtrage de sécurité et d’aider à veiller à ce que les personnes ne soient pas engagées par une institution fédérale ou un ministère compte non tenu des circonstances menant à une révocation ou à un refus antérieur qui pourrait avoir eu lieu dans une autre institution. Certaines informations rendues anonymes peuvent être utilisées ou divulguées pour l’évaluation d’un programme.  |  Links: Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Fichiers sur la sécurité du personnel GRC ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Évaluations de sécurité/Avis – SCRS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-fr.php); Contentieux en matière de droits de la personne – CCDP REG 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_f.asp); Services de contentieux – JUS 3.0.5 (http://www.justice.gc.ca/fra/trans/aiprp-atip/infosource/p3.html); Plaintes – SCA COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-fra.html); Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=fra&amp;page=information&amp;sub=publications&amp;doc=info-source/index-fra.htm); Dossier personnel d’un employé – POE 901, Nominations par le Gouverneur en conseil – POU 918 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Membres de conseils d’administration, de comités et de conseils – POU 919 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Contrôles d’accès physique – POU 907 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907); Sécurité – NDP 931 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/categories-documents-ordinaires.html); Incidents de sécurité et atteintes à la vie privée – POU 939 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html)</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>For most government institutions, records will be retained two years following the individual’s departure from the federal public service, or last administrative action, and then destroyed. Record will be retained for ten years in cases of denial or revocation of security status or clearance and then destroyed. For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution's Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Pour la plupart des institutions fédérales, les dossiers seront conservés pendant deux ans suivant le départ de la fonction publique fédérale de la personne ou le dernier changement administratif, après quoi ils seront détruits. Le dossier sera conservé pendant 10 ans dans les cas de refus ou de révocation de la cote ou de l’autorisation de sécurité, puis sera détruit. Pour connaître la durée de conservation de certains types de documents administratifs courants par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu917</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou917</t>
         </is>
@@ -4616,113 +4628,115 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>PSU 907</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>psu907</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>poe907</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Physical Access Controls</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Contrôles d’accès physique</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>This bank describes information used in support of physical security measures in the form of identification cards, employee and visitor access badges, and video surveillance recordings generated by cameras located on the perimeters of, or within institutionally operated buildings and facilities. Additionally, in support of employee and visitor access control, the records related to these subjects contain the actual access logs/registers used to issue temporary employee passes and temporary visitor passes. Personal information collected may include recorded visual images, photographs, data logs, signatures, surnames, given names, telephone numbers, access badge numbers, temporary pass control numbers and visitor company/organization information related to the issuance of temporary visitor passes.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements qui servent à la prise de mesures de sécurité physique revêtant la forme de cartes d’identification et de laissez-passer et qui ont trait aux enregistrements de surveillance vidéo situés aux périmètres et à l’intérieur d’immeubles et d’installations. De plus, à l’appui du contrôle d’accès des visiteurs et des employés, les documents connexes contiennent les registres de contrôle d’accès réels qui servent à émettre des laissez-passer pour les employés temporaires et des laissez-passer pour visiteurs. Les renseignements personnels recueillis peuvent comprendre des images enregistrées, des photos, des registres de données, des signatures, des noms et prénoms, des numéros de téléphone, des numéros de cartes d’identification, des numéros de contrôle de laissez-passer temporaires et de l’information sur l’organisation/l’entreprise que représente le visiteur, le tout lié à l’émission de laissez-passer pour visiteurs.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>This personal information bank was formerly two separate personal information banks: Security Video Surveillance and Temporary Visitor Access Control Logs and Access Badges PSU 907 and Identification and Access Cards PSE 917.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Ce fichier de renseignements personnels correspondait auparavant à deux fichiers de renseignements personnels distincts : Surveillance vidéo, registres de contrôle d’accès des visiteurs et laissez-passer POU 907 et Cartes d'identification et laissez-passer POE 917).</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Employees, and those on assignment or contract and visitors who require access to a government institution or any other person within proximity of video surveillance recording capabilities.</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Les employés, les employés en affectation et les contractuels, et les visiteurs qui doivent avoir accès à une institution fédérale ou toute autre personne se trouvant à proximité du champ d’enregistrement de la caméra de surveillance.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>The personal information is used to enhance the security of government institutions facilities and of individuals and assets present in such facilities. Video surveillance is sometimes conducted in real time or recordings can be used to investigate past occurrences, security incidents or emergency situations. Access logs/registers, access passes and any other records related to employee and visitor access control may also be used to monitor or investigate current or past security incidents. For many institutions, personal information is collected under the authority of various Acts, including the Financial Administration Act (FAA) and as required under the Policy on Government Security, Public Service Employment Act (PSEA), Criminal Code, and the Defence Production Act (DPA). For those institutions not subject to the FAA, PSEA, DPA, or the Policy on Government Security, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Ces renseignements personnels sont utilisés afin d’accroître la sécurité des installations des institutions fédérales, des personnes et des biens présents à l’intérieur de ces installations. La surveillance vidéo est parfois effectuée en temps réel ou les enregistrements peuvent servir à enquêter sur des événements passés, des incidents de sécurité ou des situations d’urgence. Les registres de contrôle d’accès, les laissez-passer et tout autre document lié au contrôle d’accès des visiteurs et des employés peuvent également être utilisés pour surveiller des incidents de sécurité actuels ou passés ou pour faire enquête. Pour un bon nombre d’institutions, les renseignements personnels sont recueillis en vertu de diverses lois, notamment la Loi sur la gestion des finances publiques (LGFP) et conformément à la Politique du gouvernement sur la sécurité, à la Loi sur l’emploi dans la fonction publique (LEFP), au Code criminel du Canada et à la Loi sur la production de défense (LPD). En ce qui concerne les institutions qui ne sont pas assujetties à la LGFP, à la LEFP, à la LPD et à la Politique sur la sécurité du gouvernement, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>The  information may be used or disclosed to assist security officials in the  monitoring of activities and/or the issuance of access passes. Information may  be used for identification purposes in support of personnel security screening.  Information may be used to support compliance with other relevant Treasury Board policy instruments and policy directions. Additionally, records and recordings may record entry  and exit times from facilities and may be used in the event of security-related  incidents such as thefts or emergency situations. In such cases, this  information may be shared with appropriate law enforcement agencies, emergency  workers, appropriate staff relations officers, or investigative bodies for  further investigations, charges or disciplinary actions (refer to Security  Incidents and Privacy Breaches PSU 939 and Discipline  PSE 911 ). Video information that reveals evidence of illegal activity,  employee misconduct or accidents may be disclosed to appropriate staff  relations, facility owners, enforcement or investigative bodies for further  investigations, charges or disciplinary actions.  |  Links: Security  Incidents and Privacy Breaches PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#psu939); Discipline  PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de dossiers administratifs courants par une institution fédérale, y compris la destruction finale de ces dossiers, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>PRN 931</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>NDP 931</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu907</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907</t>
         </is>
@@ -4736,101 +4750,100 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>PSU 912</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>psu912</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>pou912</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Professional Services Contracts</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Marchés de services professionnels</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>This bank describes information contained in agreements between government institutions and a person or firm to provide goods, perform services, to construct works or to lease real property. Personal information may include name, contact information (including business name), biographical information, educational information, financial information, evaluations/assessments, Social Insurance Number (SIN), other identification number (e.g. Business Number) and signature.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements contenus dans les ententes conclues entre les institutions fédérales, et une personne ou une société, afin de fournir des biens ou des services, de construire des ouvrages ou de louer des biens réels. Les renseignements personnels peuvent comprendre le nom, les coordonnées (y compris le nom commercial), les renseignements biographiques, les renseignements sur les études, les renseignements financiers, les évaluations/analyses, le numéro d’assurance sociale (NAS), un autre numéro d’identification (p. ex., numéro d’entreprise), et la signature.</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Individuals representing themselves or employed through private companies (including temporary help services) who have submitted responses to Requests for Proposals and who have been engaged through contracts or standing offers with government institutions and individuals who are provided as professional references.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Personal information is used to manage the contracting process, which includes the request for and receipt of proposals, evaluation of bids, selection of contractor, preparation, negotiation, execution, and award of contract, the disbursement of funds for services, deliverables, or both as specified within the contract, and post-contract evaluation. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority. The SIN is collected pursuant to the Income Tax Act.</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour gérer le processus de passation des marchés, qui comprend la demande et la réception des propositions, l’évaluation des soumissions, la sélection de l’entrepreneur, la préparation, la négociation, l’exécution, et l’attribution du marché, le décaissement de fonds pour les services, les produits livrables, ou les deux selon les spécifications du marché, ainsi que l’évaluation de l’exécution du marché. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à cette Loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte. Le numéro d’assurance sociale est recueilli conformément à la Loi de l’impôt sur le revenu.</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>Information is used to maintain an inventory of potential contractors. Information may also be used to recover overpayments and debts owed to the Crown and, where applicable, to enable execution of orders of garnishment, attachment, or diversion of funds in accordance with the Garnishment, Attachment and Pension Diversion Act and related regulations. Information may be used to confirm the identity of contractors (where required) for access to governmental and institutional websites and databases and for the loan of equipment and/or supplies. Information, including the Social Insurance Number and Business Number, is disclosed to the Canada Revenue Agency in T4A-NR Supplementary and T1204 slips (refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 ) and the Province of Quebec (if applicable) for tax purposes. The information may be shared with/described in Standard Personal Information Banks Accounts Payable - PSU 931 and Accounts Receivable - PSU 932 for payment administration. Selected information on contracts for $10,000 or more, including the fact that a contractor is a former public servant in receipt of a Public Service Superannuation Act pension, may be made available on institutions’ websites, in compliance with proactive disclosure procedures. Information may also be used or disclosed for evaluation or reporting purposes.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable - PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>99/004</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>PRN 912</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>NDP 912</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu912</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou912</t>
         </is>
@@ -4844,113 +4857,115 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>PSU 914</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>psu914</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>pou914</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Public Communications</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Communications publiques</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>This bank describes information used to communicate with individuals external to the institution and may include general inquiries (received by e-mail, telephone, mail) and responses, the distribution of public awareness and communications material, the dissemination of reports, publications, and other documentation including the release of previously released access to information packages (informal access requests), success stories, public opinion research, and information posted to social media platforms including wikis, blogs, and other collaborative Internet technologies used or hosted by the institution . Personal information may include name, contact information, user names and passwords, employee personnel information, biographical information, photographs, video and audio recordings, views and opinions of, or about, individuals, and Internet Protocol (IP) routing addresses.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements utilisés pour communiquer avec les personnes de l’extérieur de l’institution, y compris les demandes de renseignements généraux (reçues par courriel, par téléphone et par courrier) et les réponses, le matériel de sensibilisation et de communication publiques, les rapports, publications, et autre documentation, y compris la diffusion de trousses d’accès à l’information déjà publiées (demandes d’accès informelles) , les histoires de réussite, la recherche sur l’opinion publique, et l’information publiée sur les plateformes de médias sociaux, y compris les wikis, les blogues, ainsi que d’autres technologies d’Internet collaboratives qui sont utilisées ou hébergées par l’institution.</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>This information may be stored in either hard copy format or electronically (e.g., in databases or on Web sites, including social media applications, etc.). Although Internet Protocol (IP) addresses are not specifically requested by an institution, they may be captured electronically when an email is received. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Ces renseignements peuvent être stockés sous forme papier ou électronique (p. ex., dans des bases de données ou dans des sites Web, y compris les applications de médias sociaux, etc.). Bien qu’une institution ne demande pas les adresses du protocole Internet (PI) expressément, elles peuvent être saisies de manière électronique à la réception d’un courriel. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Members of the public, representatives of private sector organizations and other government institutions (i.e., municipal, provincial/territorial, and international), employees and other representatives of government institutions, who have requested information from, or submitted information to, a government institution; parents and guardians of minors; employees and other individuals with access to institutional networks, including individuals who have prepared information for dissemination, such as publication on the institution’s extranet or internet sites or who act as contact points within the institution.</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Personal information is used to disseminate information about the functions, programs, and activities of the institution, including about employees of the institution. For many institutions, personal information is collected under the authority of the Financial Administration Act (FAA), and in accordance with the Communications Policy of the Government of Canada. For those institutions not subject to the FAA or the Communications Policy of the Government of Canada, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour disséminer l’information sur les fonctions, les programmes et les activités de l’institution, y compris sur les employés de l’institution. Pour un bon nombre d’institutions, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques, (LGFP) et conformément à la Politique de communication du gouvernement du Canada. En ce qui concerne les institutions qui ne sont pas assujetties à la LGFP ou à la Politique de communication du gouvernement du Canada, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>The names, photographs, recordings and other personal information about individuals who work for the institution may be included in documentation posted on the institution’s extranet or Internet sites; e.g., within speeches, newsletters, etc. With consent of the individual, information may be shared with other areas of the institution for program-specific mailing/distribution lists and/or telephone lists. Information may be used to moderate public discussion on the social media platforms used by the institution. Responses to enquiries and any other relevant information are accounted for by the institution-specific personal information bank related to the program area that sent the response. Requests for information may be transferred when the requested information, e.g., inquiry or complaint, falls under the responsibility of another institution, refer to Executive Correspondence - PSU 902 . Some information may also be posted on government institutions’ websites for proactive disclosure purposes. Information may also be used or disclosed to provide statistical reports to management as well as for program evaluation.  |  Links: Executive Correspondence - PSU 902 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu902)</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de dossiers administratifs courants par une institution fédérale, y compris la destruction finale de ces dossiers, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Institution-specific.</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Propre à l’institution</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>PRN 939</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>NDP 939</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu914</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou914</t>
         </is>
@@ -4964,105 +4979,105 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>PSU 948</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>psu914a</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>pou948</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Real Property Management</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Gestion des biens immobiliers</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>This bank describes information related to the management of federal real property or other real property used or acquired by a government institution. Real property refers to any right, interest or benefit of land, which includes: mines, minerals and improvements on, above or below the surface of the land. Personal information may include name, biographical information, contact information, size of family, credit history, rental / lease terms and conditions, financial information, information with respect to property transactions, including appraisals, and description of property, including photographs.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Ce fichier contient les renseignements liés à la gestion des biens immobiliers fédéraux et autres biens immobiliers utilisés ou acquis par une institution fédérale. Les biens immobiliers font référence à tout droit, intérêt ou profit dans des terres, y compris les mines, les minéraux et les améliorations qui leur sont apportées, sur ou sous terre. Les renseignements personnels peuvent comprendre le nom, les renseignements biographiques, les coordonnées, la taille de la famille, les antécédents en matière de crédit, les modalités relativement à la location, les renseignements financiers, les renseignements concernant les transactions liées à la propriété, y compris les évaluations, et une description de la propriété, y compris des photos.</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Former or current tenants or applicants for tenancy of federal real property, real property owners, licensees, lessees, and property appraisers.</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Locataires anciens ou actuels, ou personnes qui présentent une demande de location d’un bien immobilier fédéral, propriétaires d’un bien immobilier, détenteurs de permis, preneurs à bail et estimateurs de biens.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Personal information is used to administer real property activities, which are related to the planning, acquisition, use and disposal of real property. Personal information is collected pursuant to a number of acts, principally, the Department of Public Works and Government Services Act, Federal Real Property and Federal Immovables Act, Federal Real Property Regulations, Department of Canadian Heritage Act, National Capital Act, Financial Administration Act, Historic Sites and Monuments Act, Department of Natural Resources Act, and Expropriation Act.</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés dans le cadre de l’administration des activités liées aux biens immobiliers, notamment la planification, l’acquisition, l’utilisation et l’aliénation de biens immobiliers. Les renseignements personnels sont recueillis aux termes de diverses lois, essentiellement la Loi sur le ministère des Travaux publics et des Services gouvernementaux, la Loi sur les immeubles fédéraux et les biens réels fédéraux, le Règlement concernant les immeubles fédéraux, la Loi sur le ministère du Patrimoine canadien, la Loi sur la capitale nationale, la Loi sur la gestion des finances publiques, la Loi sur les lieux et monuments historiques, la Loi sur le ministère des Ressources naturelles et la Loi sur l’expropriation.</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Information may be used or disclosed for the following purposes: to collect debts owed by tenants as a result of their tenancy; for credit checks; for property tax payments, that is, information may be disclosed to municipalities in which the properties are located for tax assessments and administration of the payments-in-lieu of taxes program and for evaluation or reporting to senior management. Information may be shared with or described in the Standard Personal Information Banks Accounts Payable – PSU 931 , and Accounts Receivable – PSU 932 .  |  Links: Accounts Payable – PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable – PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>To be determined</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>À déterminer</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>PRN 948</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>NDP 948</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu914a</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou948</t>
         </is>
@@ -5076,117 +5091,120 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>PSE 920</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>pse920</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>poe920</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Recognition Program</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Programme de reconnaissance</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>This bank describes information that is used to formally recognize the achievement of and give awards to employees. The personal information may include: name, contact information, biographical information, educational information, employee identification number, employee personnel information, photography, signature, opinion or views of or about individuals.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements utilisés en vue de reconnaître officiellement les réalisations des employés et de leur attribuer des primes. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements sur l’éducation, le numéro d’identification de l’employé, les renseignements personnels de l’employé, des photos, la signature, et les opinions et points de vue sur ou concernant des individus.</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Bank formerly called Recognition Policy. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Le fichier portait auparavant le titre Politique de reconnaissance. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Employees of the government institution who have been nominated for awards.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Employées de l’institution fédérale qui ont été proposés pour des primes.</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>The personal information is used to identify employees who have been nominated for awards in accordance with a recognition program. The information is also used to disburse funds or distribute gifts. Personal information is collected pursuant to various federal laws and regulations. For the specific legal authority for the collection, consult the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Les renseignements personnels servent à identifier les employés qui ont été proposés en vue de recevoir une prime dans le cadre d’un programme de reconnaissance. Les renseignements sont aussi utilisés pour verser les fonds et distribuer les marques de reconnaissance. Les renseignements personnels sont recueillis conformément aux divers lois et règlements. Il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>The information may be used or disclosed for the following purposes: reporting to senior management, evaluation and audit. Some elements of the information may be published on the Internet, intranet or other medium. Information may be shared with PSE 904 Pay and Benefit in cases where awards qualify as income. Information may be shared with PSE 901 Employee Personnel Record.</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>PRN 940</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>NDP 940</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse920</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe920</t>
         </is>
@@ -5200,101 +5218,100 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>PSU 910</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>psu910</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>pou910</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Relocation</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Réinstallation</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>This information is used to document the processes involved in the relocation of employees and their families. The personal information collected includes: the individuals’ name and job title, organization name, work telephone, work address, job classification and level, Personal Record Identifier, name of delegated institutional officer or manager, signatures, name of spouse or common-law partner, names of children and/or extended family members, special medical needs that may need to be accommodated, monthly statement of credit card expenses, personal declarations of expenses when receipts are not obtainable or have been inadvertently destroyed, mortgage or rental cost information, legal fees and real estate fees.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Ces renseignements sont utilisés pour consigner des données sur les processus liés à la réinstallation d’employés et de leur famille. Les renseignements personnels recueillis comprennent le nom de la personne, le titre de son poste, le nom de son organisation, son numéro de téléphone au bureau et l’adresse du bureau, la classification et le niveau de son poste, son code d’identification de dossier personnel, le nom du fonctionnaire ou du gestionnaire de l’institution à qui les pouvoirs ont été délégués, des signatures, le nom de son conjoint ou de son conjoint de fait, le nom de ses enfants et de membres de sa famille élargie, ses besoins spéciaux sur le plan médical dont on pourrait avoir à tenir compte, ses relevés mensuels de cartes de crédit, ses déclarations personnelles de dépenses lorsqu’il n’est pas possible d’obtenir des reçus ou que les reçus ont été détruits par inadvertance, les coûts liés à son hypothèque ou à son loyer, les frais juridiques et les frais immobiliers.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Employees who relocate and their spouses or common-law partners, their children and/or extended family members. Also includes individuals representing third party suppliers, such as moving and storage companies.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Les employés réinstallés, leur conjoint ou conjoint de fait, leurs enfants et les membres de leur famille élargie. Également les personnes représentant des tiers fournisseurs comme les entreprises de déménagement et d’entreposage.</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>The purpose of this information is to document and administer the relocation of individuals and their family members. This includes information related to relocation planning, selection of new accommodations, shipment of personal and household effects, and move authorizations and claims.</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Ces renseignements permettent de consigner et de gérer des données sur la réinstallation de personnes et de membres de leur famille. Cela comprend les renseignements concernant la planification de la réinstallation, le choix d’un nouveau logement, l’envoi des effets personnels et ménagers, les autorisations liées au déménagement et les demandes de remboursement des frais de réinstallation.</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>Non-personal information may be used to provide reports on employee relocations to management. The information may also be used for research, planning, audit and evaluation purposes.</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>98/001 and 99/004</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>PRN 936</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>NDP 936</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu910</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou910</t>
         </is>
@@ -5308,125 +5325,130 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>PSU 939</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>POU 939</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>psu939</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>pou939</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Security Incidents and Privacy Breaches</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Incidents de sécurité et atteintes à la vie privée</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>This bank describes information related to physical, administrative, and technical security, which may include: security complaints and breaches, privacy breaches, threat and risk assessments, workplace harassment and violence, theft, fraud, vandalism, accidental damages, emergency and increased threat situations, or threats to the national interest of Canada. Personal information may include: name: contact information, physical attributes, employee identification number, employee personnel information, criminal charges/investigation information, financial information, opinions and views of, or about, individuals, and signature.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés à la sécurité physique, administrative et technique, notamment les plaintes concernant la sécurité et les infractions à la sécurité, les atteintes à la vie privée, les évaluations des menaces et des risques, le harcèlement et la violence en milieu de travail, le vol, la fraude, le vandalisme, les dommages accidentels, les situations d’urgence et de menace accrue, et les menaces à l’intérêt national du Canada.</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Individuals seeking access to this bank should provide the type of incident, the location, and approximate date of the incident. Description last updated: July 2025.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Les personnes qui désirent avoir accès au présent fichier doivent fournir le type d’incident, l’endroit et la date approximative de l’incident. Le présent fichier de renseignements personnels ordinaire a été mis à jour en juillet 2025.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Employees of government institutions and other individuals involved in security incidents.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Les employés des institutions fédérales et les autres personnes visées par des incidents de sécurité.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Personal information is collected to report and investigate security incidents and to ensure that vulnerabilities are identified and the risk of future occurrences reduced. For many institutions, personal information is collected under the authority of various Acts, including the Financial Administration Act (FAA) and as required under the Policy on Government Security, Public Service Employment Act (PSEA), Criminal Code, and the Defence Production Act (DPA). For those institutions not subject to the FAA, PSEA, DPA, or the Policy on Government Security, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont recueillis pour signaler des incidents de sécurité, faire enquête et s’assurer que les vulnérabilités ont été cernées et que le risque de récidive est réduit.</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>Information may be disclosed to entities such as: the institutional security office, the institutional information technology security office, institutional ATIP office, institutional legal services, and the appropriate lead security agency which may include: the appropriate law enforcement authority for incidents suspected to be criminal offences; the Privy Council Office for incidents involving the compromise of Cabinet confidences; the Canadian Security Intelligence Service for incidents involving threats to the national interest; the Office of Critical Infrastructure Protection and Emergency Preparedness for incidents and threats affecting the availability of critical assets and services; the health and safety committee and to the Head of Compliance and Enforcement designated under the Canada Labour Code for incidents which can be considered as a “hazardous occurrence” or involve employee injury; and the Treasury Board of Canada Secretariat for incidents that have an impact on government operations or that could require revisions to operational standards or technical documentation. In the case of privacy breaches, information may also be disclosed to the Office of the Privacy Commissioner of Canada. Information may also be shared with human resources officials and managers, as required, to determine appropriate action and to support decisions regarding discipline or investigations. In this case, information may also be described in the following employee-related Standard Personal Information Banks: Discipline - PSE 911 , Employee Personnel Record – PSE 901 , and Personnel Security Screening - PSU 917 . The information may also be used or disclosed for program evaluation.  |  Links: Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911); Employee Personnel Record – PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Personnel Security Screening - PSU 917 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu917)</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>Les renseignements peuvent être communiqués à diverses entités, notamment le bureau de la sécurité de l’institution, le bureau de la sécurité de la technologie de l’information de l’institution, le bureau de l’accès à l’information et de la protection des renseignements personnels de l’institution, les services juridiques de l’institution, le principal organisme de sécurité compétent, ce qui peut comprendre l’autorité d’application de la loi compétente pour les incidents soupçonnés d’être des infractions criminelles, le Bureau du Conseil privé pour les incidents compromettant des documents confidentiels du Cabinet, le Service canadien du renseignement de sécurité pour les incidents comportant des menaces envers la sécurité du Canada, le Bureau de la protection des infrastructures essentielles et de la protection civile pour les incidents et les menaces touchant la disponibilité de biens et services essentiels, le comité de santé et de sécurité et chef de la conformité et de l’application désigné en vertu du Code canadien du travail pour les incidents pouvant être considérés comme des « situations comportant des risques » ou pouvant causer des blessures à des employés, et le Secrétariat du Conseil du Trésor du Canada pour les incidents qui ont une incidence sur les opérations du gouvernement ou qui pourraient nécessiter la révision de normes opérationnelles ou de documents techniques.</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>98/001</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>PRN 931</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>NDP 931</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou939</t>
         </is>
@@ -5440,109 +5462,110 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>PSE 902</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>pse902</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>poe9021</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Staffing</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Dotation</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>This bank describes information about recruitment and staffing activities, which includes solicited and unsolicited applications for employment, position reclassifications, secondments, deployments, and other work assignments or arrangements within government institutions. Personal information may include name, contact information, assessment/test results, biographical information, citizenship status, date and place of birth, educational information, employee identification number, employment equity information, employee personnel information, financial information, official language proficiency, medical information, opinions and views of, or about, individuals, and signatures.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements liés aux activités de recrutement et de dotation, y compris les demandes d’emploi sollicitées et non sollicitées, et les reclassifications de postes, les détachements, les mutations ou autres affectations ou modalités de travail au sein des institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les résultats des analyses/tests, les renseignements biographiques, le statut de citoyen, la date et le lieu de naissance, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, les renseignements qui figurent au dossier de l’employé, les renseignements financiers, la compétence dans les langues officielles, les renseignements médicaux, les opinions et les points de vue sur, ou concernant, des individus, et les signatures.</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Individuals requesting information described by this bank should provide a competition number, if applicable.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Les personnes qui demandent des renseignements décrits dans ce fichier doivent fournir un numéro de concours, s’il y a lieu.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Employees of the institution and other individuals who apply for employment in the institution including through recruitment initiatives, as well as individuals who provide references or are supervisors of applicants.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Personal information is used to administer recruitment and staffing activities in government institutions, which includes maintaining an inventory of potential candidates for future staffing actions. For most government institutions, personal information is collected pursuant to the Public Service Employment Act, the Employment Equity Act, and the Canadian Human Rights Act (section 16). For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour administrer les activités de recrutement et de dotation dans les institutions fédérales, ce qui comprend la tenue à jour d’un inventaire de candidats éventuels pour de futures mesures de dotation. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis en vertu de la Loi sur l’emploi dans la fonction publique, la Loi sur l’équité en matière d’emploi, et la Loi canadienne sur les droits de la personne (article 16). En ce qui concerne les institutions qui ne sont pas assujetties à ces lois, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>Information may be disclosed to the Public Service Commission, Treasury Board Secretariat and other government institutions for recruitment, employment equity, and staffing purposes, including complaints (refer to Institution-Specific Personal Information Banks: for the Public Service Commission of Canada: Applicant Inventories and Referrals - PSC PPU 015 ; Assessment by the Personnel Psychology Centre - PSC PCU 025 , Second Language Evaluation (SLE) Test Results - PSC PPU 030 , Executive Resourcing - PSC PCE 746 , Analytical Environment - PSC PCE 761 , and Investigations, Mediation and Conciliation - PSC PPU 010 ; for Treasury Board of Canada Secretariat: Employment Equity Data Bank - TBS PCE 739 and Workforce Adjustment Monitoring (WFAM) System - TBS PCE 804 ). Information relating to staffing complaints may be shared with the Public Service Commission (refer to Institution-Specific Personal Information Bank Investigations, Mediation and Conciliation - PSC PPU 010 ) and the Federal Public Service Staffing Tribunal with Public Sector Labour Relations and Employment Board, when required. On request, selected information may be disclosed to a participant in a staffing process. Information may also be shared with third party service providers to manage recruitment initiatives. Information may also be used or disclosed for human resources planning and studies (refer to Standard Personal Information Bank Human Resources Planning - PSU 935 ) and staffing decisions may also be described in Standard Personal Information Bank Employee Personnel Record - PSE 901 . Voluntary self identification information relating to employment equity programs and services is also described in Standard Personal Information Bank Employment Equity and Diversity - PSE 918 . Selected information about reclassifications may be proactively disclosed on government institutions’ websites. Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Applicant Inventories and Referrals - PSC PPU 015 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Assessment by the Personnel Psychology Centre - PSC PCU 025 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Second Language Evaluation (SLE) Test Results - PSC PPU 030 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Executive Resourcing - PSC PCE 746 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Analytical Environment - PSC PCE 761 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Investigations, Mediation and Conciliation - PSC PPU 010 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp); Workforce Adjustment Monitoring (WFAM) System - TBS PCE 804 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg00-eng.asp); Investigations, Mediation and Conciliation - PSC PPU 010 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Human Resources Planning - PSU 935 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Employment Equity and Diversity - PSE 918 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse918)</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>PRN 919, PRN 920</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>NDP 919, NDP 920</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse902</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021</t>
         </is>
@@ -5556,101 +5579,100 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>PSE 905</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>pse905</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>poe905</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Training and Development</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Formation et perfectionnement</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>This bank describes personal information collected to support an institution’s training and development programs (e.g., mentoring, career orientation, developmental work assignments or arrangements, etc.). Personal information may include name, contact information, educational information, employee identification number, employment equity information, employee personnel information, financial information, biographical information, and assessment and training results.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements personnels recueillis à l’appui du programme de formation et de perfectionnement d’une institution (p. ex., les programmes de mentorat et d’orientation des carrières, les affectations et les modalités de travail de perfectionnement, etc.). Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, les renseignements personnels de l’employé, les renseignements financiers, les renseignements biographiques, ainsi que les résultats de l’analyse et de la formation.</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Individuals who are employed by government institutions who register for training or development courses or programs.</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Personal information is used to register and pay for approved training and development activities. Where applicable, government institutions may receive information from the Canada School of Public Service or other course providers about registration costs and training results. For most government institutions, personal information is collected under the authority of the Public Service Staff Relations Act and the Public Service Employment Act. For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour s’inscrire à des activités de formation et de perfectionnement approuvées et pour les payer. Là où il y a lieu, les institutions fédérales peuvent recevoir des renseignements de l’école de la fonction publique du Canada ou des autres prestataires de cours sur les coûts d’inscription et les résultats de la formation. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis en vertu de la Loi sur les relations de travail dans la fonction publique, et de la Loi sur l’emploi dans la fonction publique. En ce qui concerne les institutions qui ne sont pas assujetties à ces lois, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>Information may be used to link voluntary self-identification data to information contained in other banks (refer to Standard Personal Information Bank Employment Equity and Diversity - PSE 918) for the purpose of implementing and evaluating government policies relating to employment equity and diversity. Some information may also be shared with/described in the Standard Personal Information Banks Accounts Receivable - PSU 932 , Employee Performance Management Program – PSE 912 and Employee Personnel Record - PSE 901 . Information may also be used or disclosed for program evaluation.  |  Links: Accounts Receivable - PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932); Employee Performance Management Program – PSE 912 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse912); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901)</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>PRN 927</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>NDP 927</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe905</t>
         </is>
@@ -5664,97 +5686,95 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Public Standard Bank</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>PSU 909</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>psu909</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>pou909</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Voyages</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>This bank describes information about employees who travel on official institutional business. Personal information may include name, contact information, biographical information, employee identification number, employee personnel information, financial information and passport/visa information, travel history, travel claims, accommodations, meals, or preferences. Travellers may also be requested to provide date of birth and gender when booking travel arrangements.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Ce fichier décrit les renseignements sur les employés qui se déplacent pour des activités officielles de leur institution. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers et sur le passeport/visa, les antécédents de voyage, les demandes d’indemnité de voyages, le logement, les repas et les préférences. Les employés en voyages peuvent également être tenus de fournir la date de naissance et le sexe lorsqu’ils font des préparatifs de voyages.</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Employees of government institutions, Ministers, Parliamentary Secretary, exempt staff, and other individuals (may include term or casual employees, temporary staff, volunteers, students, consultants and contractors, or witnesses) who travel on official institutional business, their spouses or common-law partners and dependants.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Personal information is used to process travel requirements for individuals who travel on behalf of the institution. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour répondre aux besoins de déplacement des individus qui voyagent au nom de leur institution. Pour la plupart des institutions fédérales, les renseignements personnels sont recueillis en vertu de la Loi sur la gestion des finances publiques. En ce qui concerne les institutions qui ne sont pas assujetties à la loi, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>Travel expenses incurred by the Minister, Parliamentary Secretary, exempt staff, and by senior level employees (i.e., Deputy Minister, Associate Deputy Minister, Assistant Deputy Minister, or equivalent) may be proactively disclosed on government institutions’ websites. Some institutions may share information with Public Works and Government Services Canada to establish the Traveller Profile (refer to Central Personal Information Bank Shared Travel Services Initiative (STSI) Traveller Profile - PWGSC PCE 706 ). In some instances, information may also be shared with the Department of Foreign Affairs and International Trade Canada (e.g., official delegations to events in foreign countries). Information may also be shared with/described in Standard Personal Information Banks Accounts Payable - PSU 931 and Accounts Receivable – PSU 93 2. Information may be used or disclosed for program evaluation and reporting purposes.  |  Links: Shared Travel Services Initiative (STSI) Traveller Profile - PWGSC PCE 706 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/index-eng.html); Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable – PSU 93 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>98/001 and 99/004</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>PRN 934, PRN 935</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>NDP 934, NDP 935</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu909</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou909</t>
         </is>
@@ -5768,109 +5788,110 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>PSE 915</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>pse915</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>poe915</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Values and Ethics Codes for the Public Sector and Organizational code(s) of Conduct</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Codes de valeurs et d’éthique du secteur public et Code(s) de conduite organisationnel(s)</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>This bank describes information related to the responsibilities of public servants in government institutions included in the public sector as defined in section 2 of the Public Servants Disclosure Protection Act (PSDPA) as set forth in the Values and Ethics Code for the Public Sector, applicable organizational code(s) of conduct, as well as conflict of interest and post-employment measures. Personal information may include name, contact information, financial information, credit information, biographical information, employee identification number, employee personnel information, views and opinions of, or about, individuals, signature and other personal information which may be contained in a conflict of interest statement.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Ce fichier décrit des renseignements personnels relatifs aux responsabilités des fonctionnaires d’institutions fédérale appartenant à au secteur public au sens de l’article 2 de la Loi sur la protection des fonctionnaires divulgateurs d’actes répréhensibles (LPFDAR) et énoncées dans le Code de valeurs et d’éthique du secteur public, des code(s) de conduite organisationnels applicable, ainsi que les mesures régissant les conflits d’intérêt et l’après-mandat. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements financiers, les renseignements de solvabilité, les renseignements biographiques, le numéro d’identification d’employé, les renseignements personnels de l’employé, les opinions et les points de vue sur, ou concernant, des individus, la signature et d’autres renseignements personnels pouvant figurer dans une déclaration de conflits d’intérêts.</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Public servants of government institutions included in the core public administration for which Treasury Board is the employer and who are members of a collective bargaining group that has yet to transition to the Values and Ethics Code for the Public Sector in their collective agreements remain subject to the Values and Ethics Code for the Public Service in regards to conflict of interest measures and post-employment measures. Those who have transitioned to the Values and Ethics Code for the Public Sector are subject to the Policy on Conflict of Interest and Post-Employment. Bank formerly called: Values and Ethics Code for the Public Service. Description last updated: December 2013.</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Les fonctionnaires d’institutions fédérales faisant partie de l’administration publique centrale dont le Conseil du Trésor est l’employeur et qui sont membres d’une unité de négociation qui n’a pas encore adopté, dans sa convention collective, le Code de valeurs et d’éthique du secteur public, sont néanmoins assujettis au Code de valeurs et d’éthique du secteur public pour ce qui est des mesures relatives aux conflits d’intérêts et à l’après-mandat. Les fonctionnaires qui sont passés au Code de valeurs et d’éthique de la fonction publique sont assujettis à la Politique sur les conflits d’intérêts et l’après-mandat. Dernière mise à jour de la description : décembre 2013.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, family members, and other individuals with whom the employee may have a business interest.</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Personal information is used to provide direction and authorizations, support decision on transfers, discipline and termination of employment, if conflict of interest exists, resolve situations of perceived, potential and actual conflicts of interest in current and post-employment This includes conflicts of interest in relation to 1) assets and liabilities, 2) gifts, hospitality and other benefits, 3) outside employment or activities, 4) preferential treatment and 5) solicitation. Personal information is also used in assessing the need for the establishment of a blind trust or for approving reimbursement for costs associated with such a divestment. Personal information is collected pursuant to section 5 and 6 of the PSDPA. Personal information is collected pursuant to sections 7 and 11.1 (1)(j) of the Financial Administration Act (FAA) for setting terms and conditions of employment. For those institutions not subject to the PSDPA or the FAA, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Les renseignements personnels sont utilisés pour fournir des orientations et des autorisations, appuyer des décisions concernant des mutations, des mesures disciplinaires et des licenciements, et régler des situations de conflits d’intérêt perçus, possibles ou réels durant le mandat ou l’après-mandat de l’employé, ce qui englobe les conflits d’intérêts concernant : 1) actifs et passifs, 2) cadeaux, marques d’hospitalité et autres avantages, 3) activités ou emplois extérieurs, 4) traitement de faveur, et 5) sollicitation. Les renseignements personnels servent aussi aux fins de l’évaluation du besoin d’établir une fiducie sans droit de regard ou de l’approbation du remboursement de coûts liés à un tel dessaisissement. Les renseignements personnels sont recueillis en vertu des articles 5 et 6 de la LPFDAR. Les renseignements personnels sont recueillis en vertu des articles 7 et 11.1 (1)j) de la Loi sur la gestion des finances publiques (LGFP) aux fins d’établir les conditions de travail. En ce qui concerne les institutions qui ne sont pas assujetties à la LPFDAR ou la LGFP, il faut consulter le coordonnateur de l’accès à l’information et de la protection des renseignements personnels de l’institution afin de déterminer l’autorité législative pour la collecte.</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>In some cases, information may be disclosed to the Office of the Chief Human Resources Officer, Treasury Board Secretariat for the purpose of obtaining advice on possible conflicts of interest. In cases where an allegation of wrongdoing is made, information may be disclosed either to the Office of the Public Sector Integrity Commissioner of Canada, which may make recommendations where warranted to Deputy Heads of institutions, refer to Case Review and Investigation Files – PSIO PPU 005 or to the senior officer responsible for receiving and dealing with disclosures of wrongdoing in the government institution, refer to Disclosure of Wrongdoing in the Workplace – PSU 906 . Information may be shared with human resources officials where a conflict of interest results in discipline or termination of employment, refer to Discipline – PSE 911 . Information may also be used or disclosed for program evaluation, policy analysis, research, audit or statistical purposes.  |  Links: Case Review and Investigation Files – PSIO PPU 005 (http://www.psic.gc.ca/eng/about-us/publications#ATIP); Disclosure of Wrongdoing in the Workplace – PSU 906 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu906); Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>PRN 920, PRN 926</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse915</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe915</t>
         </is>
@@ -5884,101 +5905,100 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>PSE 908</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>pse908</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>poe908</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Vehicle, Ship, Boat and Aircraft Accidents</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Accidents d’automobile, de bateau, d’embarcation et d’avion</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>The records containing information described in this bank may contain reports on accidents; claims of damages; legal decisions; settlement transactions and correspondence concerning accidents involving government-owned and leased vehicles, ships, boats and aircraft as well as privately-owned vehicles, ships, boats and aircraft used on official business. Records concerning occupational health and safety, as well as authorization of leave and benefits associated with work-related injury or illness are described in Standard Personal Information Bank Occupational Health and Safety - PSE 907 .  |  Links: Occupational Health and Safety - PSE 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse907)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Les dossiers contenant des renseignements décrits dans ce fichier peuvent comprendre des rapports sur les accidents; des réclamations pour les dommages subis; des décisions du tribunal; des règlements des transactions et la correspondance concernant des accidents survenus à des véhicules, des bateaux, des embarcations et des avions loués ou appartenant à l’état, ainsi qu’à des véhicules, bateaux, embarcations et avions privés utilisés à des fins professionnelles. Les dossiers de santé et sécurité au travail ainsi que les dossiers d’autorisation de congés et de prestations liés à une blessure au travail ou à une maladie professionnelle sont décrits dans le fichier de renseignements personnels ordinaire, Santé et sécurité au travail – POE 907.  |  Links: Santé et sécurité au travail – POE 907. (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Employés de l’institution.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>The purpose of these records is to maintain information regarding vehicle, ship, boat and aircraft accidents involving employees of a government institution.</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Ces dossiers ont pour but de conserver les renseignements se rapportant aux accidents d’automobile, de bateau, d’embarcation et d’avion survenus à des employés du gouvernement.</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>To determine liability for such accidents and to approve damage settlements.</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>PRN 922, PRN 945</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse908</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe908</t>
         </is>
@@ -5992,105 +6012,105 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Employee Standard Bank</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>PSE 930</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>pse930</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>poe930</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Workplace Day Care</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Garderie en milieu de travail</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>The records containing information described in this standard bank may contain information collected from employee surveys conducted by government institutions for the purpose of estimating employee demand for workplace day care and from workplace day care centre records for evaluating the workplace day care policy. Such information may include employee or user personal data, data on their children, anticipated demand for day care and probability and reasons for enrolling a child in an institutionally sponsored workplace day care centre.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Les dossiers contenant les renseignements décrits dans ce fichier peuvent renfermer des renseignements recueillis à partir d’enquêtes menées par des institutions fédérales auprès de leurs employés pour évaluer la demande de garderies en milieu de travail, à partir des dossiers des garderies en milieu de travail. Ces renseignements ont été compilés dans le but de déterminer l’aide financière permanente sur laquelle pourront compter les garderies pour ce qui est de la location des locaux, et d’évaluer la politique sur les garderies. Ils peuvent comprendre des données personnelles sur l’employé ou l’utilisateur, ou encore sur ses enfants, et peuvent porter sur la demande prévue en services de garderie, la probabilité qu’un employé inscrive un enfant dans une garderie parrainée par l’institution et les raisons qui pourraient l’inciter à l’y inscrire.</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>All federal employees included in Schedules I and IV of the Financial Administration Act.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Tous les employés fédéraux énumérés aux annexes I et IV de la Loi sur la gestion des finances publiques.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>These records are to be used to determine whether sufficient employer interest and demand exist to merit further consideration (viability study) by the government institution of the possibility of establishing a workplace day care centre. They will be used to determine the level of ongoing federal rental support for the workplace day care centre. This information will also be used for the purposes of evaluating the day care centre policy.</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Ces dossiers doivent servir à déterminer si l’intérêt de l’employeur et la demande sont suffisants pour qu’une institution fédérale envisage réellement (étude de viabilité) la possibilité d’établir une garderie en milieu de travail. Ils permettront de déterminer le niveau d’aide que le gouvernement fédéral est prêt à accorder à la garderie en ce qui concerne la location des locaux. Ils serviront également à évaluer la politique sur les garderies.</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>The information in these records will be used for administrative and statistical purposes associated with the establishment of a day care centre. It will also be used for the evaluation and monitoring of the federal public service workplace day care policy. The information may be disclosed to Treasury Board, the government institution, an authorized committee of the government institution, a custodian government institution and the Board of Directors of the Day Care Centre. Together with the linked information from the files identified below, this information will form the basis for tabulations of the extent and type of employee day care users.</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Pour connaître la durée de conservation de certains types de documents administratifs communs par une institution fédérale, y compris la destruction finale de ces documents, veuillez communiquer avec le coordonnateur de l’accès à l’information et de la protection des renseignements personnels.</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>98/005</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>PRN 949</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>NDP 949</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse930</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe930</t>
         </is>
@@ -6103,50 +6123,32 @@
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Categories of Personal Information</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Catégories de renseignements personnels</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#categories</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#categories</t>
         </is>

--- a/spib_en_fr.xlsx
+++ b/spib_en_fr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,7 @@
           <t>PSU 901</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>psu901</t>
@@ -639,6 +640,7 @@
           <t>Information may be shared with other government institutions during consultations required to process and respond to formal requests made under the Acts. Information may be shared with the Office of the Privacy Commissioner during investigations, refer to Privacy Complaints and Investigations – OPC PPU 005 and Privacy Commissioner Ad Hoc – Complaints and Investigations – OPC PPU 008 . Information may be shared with the Office of the Information Commissioner during investigations, refer to Complaint Investigations – OIC PPU 3100 and Ad Hoc Information Commissioner Complaint Investigations – OIC PPU 123 . Personal information may be shared with a government institution providing internal support services in accordance with section 29.2 of the Financial Administration Act. For information about the internal support services used, please contact the institution’s Access to Information and Privacy Coordinator. The information may be used for planning and evaluation purposes. Depersonalized and aggregated information is used to report to Parliament on the administration of the Access to Information Act and the Privacy Act.  |  Links: Privacy Complaints and Investigations – OPC PPU 005 (https://www.priv.gc.ca/au-ans/atip-aiprp/infosource_e.asp); Privacy Commissioner Ad Hoc – Complaints and Investigations – OPC PPU 008 (https://www.priv.gc.ca/au-ans/atip-aiprp/infosource_e.asp); Complaint Investigations – OIC PPU 3100 (http://www.oic-ci.gc.ca/eng/info-source.aspx); Ad Hoc Information Commissioner Complaint Investigations – OIC PPU 123 (http://www.oic-ci.gc.ca/eng/info-source.aspx)</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -696,6 +698,7 @@
           <t>PSU 931</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>psu931</t>
@@ -766,6 +769,7 @@
           <t>Information may be shared with Public Works and Government Services Canada (Receiver General for Canada) for payment purposes refer to Receiver General Payments - PWGSC PCU 712. Where applicable, information may be shared with the Bank of Canada and financial institutions of foreign countries for transactions purposes. In some cases, the SIN and other information is shared with the Canada Revenue Agency and the Province of Quebec, and is used for data matching purposes, including income verification, refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 . Information may be used or disclosed for financial reporting and program evaluation.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -823,6 +827,7 @@
           <t>PSU 932</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>psu932</t>
@@ -893,6 +898,7 @@
           <t>Information may be shared with Public Works and Government Services Canada (Receiver General for Canada) to process payments to the government institution; refer to Receiver General Payments - PWGSC PCU 712. Information may be shared with the government institution’s own financial institution. Information may be shared with financial institutions of foreign countries for transactions purposes. Information may also be shared with collection agencies for debt recovery purposes. In some cases, the SIN and other information is shared with the Canada Revenue Agency and the Province of Quebec, and is used for data matching purposes, including income verification, refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 . Information may be used or disclosed for financial reporting and program evaluation.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -950,6 +956,7 @@
           <t>PSU 940</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>psu940</t>
@@ -980,6 +987,9 @@
           <t>Le fichier décrit l’information utilisée à l’appui d’un programme de cartes d’achats d’une institution. Les cartes d’achat sont utilisées pour acquérir et payer des biens et des services, mais ne servent pas pour les dépenses liées aux voyages ou pour les dépenses liées à l’opération et à l’entretien de véhicules. Les renseignements personnels peuvent comprendre le nom du détenteur d’une carte, les coordonnées, la langue, le numéro d’identification d’employé, le numéro de la carte, la date d’expiration, la limite de crédit, et les renseignements relatifs aux vérifications ou à la conformité aux règles, et aux enquêtes.</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Individuals who apply for an acquisition card and those who are issued such cards.</t>
@@ -1005,6 +1015,7 @@
           <t>Information may be shared with Public Works and Government Services Canada to monitor the operation of the acquisition card program and to take corrective action when required. Information may also be shared with the private sector card issuer, namely, financial institutions. The information may be also be used or disclosed for program evaluation, enforcement (refer to Security Incidents and Privacy Breaches - PSU 939 and Discipline - PSE 911 ), and for reporting to Senior Management.  |  Links: Security Incidents and Privacy Breaches - PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1062,6 +1073,7 @@
           <t>PSU 911</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>psu911</t>
@@ -1092,6 +1104,9 @@
           <t>Ce fichier décrit des renseignements personnels sur les personnes ayant présenté des demandes d’emploi ou fourni les curricula vitae (réclamés ou non) et une correspondance connexe. Les renseignements personnels fournis par une personne dans les formulaires de demande, les curricula vitae et la correspondance peuvent comprendre son nom, ses coordonnées, sa situation et ses antécédents professionnels, ses études, son état matrimonial, sa date de naissance, son sexe, sa connaissance des langues officielles, sa situation au regard de l’équité en emploi, ses handicaps physiques, sa citoyenneté, son code d’identification de dossier personnel, son Numéro de service client, ses relevés de notes, ses lettres de recommandation et d’autres renseignements personnels.</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Public service employees and non-public service employees seeking employment with the institution; individuals whose names have been provided as employment references, personal references, or both; and individuals referring another individual for a position.</t>
@@ -1117,6 +1132,7 @@
           <t>Relevant information would be transferred to an employee personnel record (refer to Standard Personal Information Bank Employee Personnel Record - PSE 901 ) if the individual accepts an offer of employment. This information may also be used for planning and evaluation purposes. The information may also be transferred to another institution, if the other institution is deemed to be more appropriate for potential employment opportunities for the individual. The data collected and maintained may be used for statistical purposes, training requirements, and other development opportunities. The personal information about individuals self-identified in employment equity groups may be used for statistical purposes by the institution and may be shared with the Public Service Commission of Canada, Treasury Board of Canada Secretariat, and the Canada Public Service Agency for the same purpose.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901)</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1174,6 +1190,7 @@
           <t>PSE 903</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>pse903</t>
@@ -1204,6 +1221,9 @@
           <t>Les dossiers contenant les renseignements décrits dans ce fichier peuvent comprendre des rapports sur les absences et les demandes de congé, ainsi que les certificats médicaux produits pour des congés de maladie. Sur tous ces documents, on doit inscrire le Code d’identification de dossier personnel et on doit également joindre la correspondance connexe aux présences et congés. Le dossier annuel portant sur les congés et les présences peut être joint au dossier personnel d’un employé. Certains renseignements relatifs aux congés et aux présences sont présentés sous forme de modules automatisés enregistrés dans des bases de données sur le personnel de l’organisme ou du ministère (systèmes présence/temps, congés et absences.</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
@@ -1229,6 +1249,7 @@
           <t>To record attendance  and authorize leave. To support decisions on pay and benefits, such as those  concerning leave and termination of employment, to evaluate use of leave and  rates of absenteeism and to verify policy compliance. This information may be  shared for disciplinary purposes (refer to PSE  901 Employee Personnel Record and PSE  911 Discipline ).  |  Links: PSE  901 Employee Personnel Record (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse901); PSE  911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1256,7 +1277,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>NDP 941</t>
+          <t>NDP 941, NDP 924</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1281,6 +1302,8 @@
           <t>Public Standard Bank</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>psu904</t>
@@ -1301,6 +1324,8 @@
           <t>Systèmes automatisés de gestion des documents, des dossiers et de l’information</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>This standard personal information bank was terminated since all personal information retained in the systems is accounted for in personal information banks or classes of personal information of the programs or activities for which it was collected. Description terminated: December 2013.</t>
@@ -1316,6 +1341,18 @@
           <t>2013-12-01</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu904</t>
@@ -1343,6 +1380,7 @@
           <t>PSU 903</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>psu903</t>
@@ -1373,11 +1411,15 @@
           <t>Ce fichier décrit les renseignements qui sont utilisés à l’appui des fonctions de gestion de la continuité des opérations, qui comprennent l’élaboration et l’exécution, dans les délais prévus, des plans, des mesures et des procédures afin de minimiser l’interruption des services et de la disponibilité des immobilisations en cas d’urgence ou d’interruption de service. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements personnels de l’employé, et les renseignements médicaux. Les renseignements personnels peuvent aussi comprendre les noms et les coordonnées des personnes désignées par les employés comme personnes avec qui communiquer en cas d’urgence.</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Employees of the government institution; Ministers and exempt staff and other personnel of offices of Ministers or Ministers of State; emergency contacts identified by employees; private sector emergency response officials and service providers; and other federal, provincial or municipal officials who may need to be contacted in the event of an emergency or disruption of services.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Personal information is used to plan and respond in a timely and effective manner to an emergency or to a disruption of service, to establish a list of employees, appropriate officials and their contact information. The list may be used to contact such individuals in the event of an emergency or the execution of the Business Continuity Plan. Some institutions may also require that supervisors maintain a list of direct reports, home telephone numbers and the emergency contacts identified by the direct reports. For most government institutions, personal information is collected pursuant to the Financial Administration Act (as required under the Policy on Government Security) and the Emergency Management Act. For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
@@ -1393,6 +1435,7 @@
           <t>Information may be shared with other federal, provincial, and municipal institutions, police, fire and other emergency response agencies as required. Some information may be shared with/described in the Standard Personal Information Banks Employee Personnel Record - PSE 901 and Occupational Health and Safety - PSE 907 . Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Occupational Health and Safety - PSE 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse907)</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1450,6 +1493,7 @@
           <t>PSU 933</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>psu933</t>
@@ -1480,11 +1524,15 @@
           <t>Ce fichier décrit les renseignements liés aux plaintes déposées en vertu de la partie III de la Loi canadienne sur les droits de la personne. Les plaintes, conformément à la partie III de la Loi canadienne sur les droits de la personne, peuvent être déposées contre une organisation réglementée par le gouvernement fédéral et se rapporter à des allégations de pratiques discriminatoires fondées sur tout motif illicite. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les vérifications de casier judiciaire/antécédents criminels, les renseignements sur les études, le numéro d’identification d’employé, les renseignements personnels de l’employé, des renseignements sur l’équité en emploi, la nature de la plainte, les opinions et les points de vue sur, ou concernant, des individus, d’autres numéros d’identification, les renseignements médicaux, les signes distinctifs, et la signature.</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Individuals and representatives of individuals or groups who make a complaint, respondents, and witnesses.</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Personal information is collected pursuant to Part III of the Canadian Human Rights Act and is used to record, enquire into and resolve complaints of discrimination.</t>
@@ -1500,6 +1548,7 @@
           <t>Information may be shared with the Department of Justice Canada to provide evidence for the hearing of a complaint by the Canadian Human Rights Tribunal, the Federal Court of Canada, the Appeal Court and/or the Supreme Court of Canada. Information may be also be used or disclosed for program evaluation.</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1557,6 +1606,7 @@
           <t>PSE 911</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>pse911</t>
@@ -1587,11 +1637,15 @@
           <t>Ce fichier décrit les renseignements personnels reliés à la demande de normes disciplinaires dans la fonction publique fédérale et les pénalités connexes, y compris le licenciement, la suspension, la rétrogradation à un poste situé dans une échelle de traitement comportant un plafond inférieur et les sanctions pécuniaires qui peuvent être appliquées en raison de manquements à la discipline ou de mauvaise conduite dans les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, la date de naissance, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, les avis juridiques, les renseignements médicaux, la nature de la mauvaise conduite et la mesure disciplinaire, les opinions et les points de vue sur, ou concernant, des individus, et la signature.</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Employees and former employees of the institution who are/were the subject of the alleged misconduct, interviewees, medical practitioners, representatives or bargaining agents, and witnesses.</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Personal information is used to investigate alleged misconduct in government institutions and to determine the need for, and nature of, disciplinary actions. Information is also collected to support decisions on pay and benefits, attendance and leave, transfer, demotion and termination of employment. For many institutions, personal information is collected pursuant to paragraph 12(1)(c) of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
@@ -1607,6 +1661,7 @@
           <t>Some discipline measures may also be described in Standard Personal Information Bank Employee Personnel Record - PSE 901 . Information concerning grievances is described in Standard Personal Information Bank Grievances - PSE 910 . Where applicable, information may be shared with the following entities: 1) the Treasury Board of Canada Secretariat in cases of terminations / demotions, interpretation / application of cases involving important jurisprudential issues, and other special instances; 2) professional regulatory bodies, as required; and 3) law enforcement agencies in the event of an alleged criminal offence. Information may also be used or disclosed for program evaluation.  |  Links: Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910)</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>(1) For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator. (2) Documentation concerning a specific employee including documentation related to disciplinary action - the time limit for disposal is that specified in applicable collective agreements or a minimum of two years following the date of disciplinary action, provided no further disciplinary action has been recorded in the meantime. (3) In cases where a disciplinary action has been rescinded, the onus is on the institution to ensure that the documentation of the action concerned is immediately destroyed.</t>
@@ -1664,6 +1719,7 @@
           <t>PSU 906</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>psu906</t>
@@ -1714,6 +1770,7 @@
           <t>Individuals who report an alleged wrongdoing in the public sector as well as individuals who are alleged to have committed wrongdoing, witnesses, representatives of individuals such as union representatives and legal counsel, investigators and any other party affected by the allegation(s).</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Personal information is used to assess, investigate, report and resolve alleged wrongdoing in the public sector. When warranted, personal information may also be used to temporarily assign other duties to a public servant and provide notice of actions taken, or proposed to be taken, to the Public Sector Integrity Commissioner on recommendations made by the Commissioner. Personal information is collected pursuant to sections 12 to 14, 22(g), 22(h), 26 and 27 of the PSDPA.</t>
@@ -1729,6 +1786,7 @@
           <t>The information may be used or disclosed for evaluation and reporting to senior management. In limited circumstances under applicable laws, reporting purposes may include reporting to the Minister, or governing council, responsible for the government institution and publicly reporting on the wrongdoing. Depersonalized and aggregated information may be shared with the Treasury Board Secretariat (Office of the Chief Human Resources Officer) for reporting purposes. Information may be shared with internal security officials, refer to Security Incidents and Privacy Breaches- PSU 939 , or other authorities having the powers to investigate under federal, provincial and municipal statutes if the investigation reveals potential fraud or other criminal wrongdoing. Information may be shared with the government institution’s labour relations division when the chief executive officer of the government institution decides to apply disciplinary measures to public servants who perpetrated wrongdoings, refer to Discipline – PSE 911 .  |  Links: Security Incidents and Privacy Breaches- PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939); Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1786,6 +1844,7 @@
           <t>PSU 913</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>psu913</t>
@@ -1821,6 +1880,7 @@
           <t>The head of a government institution is not required, in accordance to sub-section 9(2) Privacy Act, to account for the disclosure of the information under section 8(2)(e) in the personal information bank from which the personal information was requested. Description last updated: December 2013.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>2013-12-01</t>
@@ -1841,11 +1901,13 @@
           <t>The personal information is used to document requests received from investigative bodies pursuant to paragraph 8(2)(e) of the Privacy Act and the responses to such requests. Personal information is collected pursuant to section 8(4) of the Privacy Act and section 7 of the Privacy Regulations.</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>The information may be used or disclosed for statistical and audit purposes. Information may be shared with government institutions who are investigative bodies listed in Schedule 2 of the Privacy Regulations. Investigative bodies that receive personal information as a result of disclosures pursuant to paragraph 8(2)(e) of the Privacy Act may subsequently share such personal information with other federal investigative bodies or law enforcement agencies, for the purpose of the administration or enforcement of a law and/or the detection, prevention, or suppression of crime.</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -1903,6 +1965,7 @@
           <t>PSU 905</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>psu905</t>
@@ -1933,6 +1996,9 @@
           <t>Les dossiers contenant les renseignements décrits dans ce fichier se rapportent à l’utilisation des réseaux électroniques des institutions fédérales. Des journaux contenant le détail sur l’utilisation des réseaux sont compilés et revus par les agents appropriés de l’institution lorsqu’il y a lieu de soupçonner la non-conformité aux politiques ou qu’un réseau électronique d’une institution fédérale est soumis à un usage détourné, au sens donné à ce terme dans les politiques en la matière de l’institution intéressée ou de la Politique d’utilisation des réseaux  électroniques, ou autres instruments de politiques et orientations pertinents du Conseil du Trésor. Ces dossiers peuvent comprendre par exemple des journaux de réseau qui  établissent des liens entre le poste de travail d’un employé et une adresse du protocole Internet, les listes de sites consultés et des renseignements sur les opérations effectuées, y compris la date, l’heure, la durée et la nature de la visite ou de l’opération. Ils peuvent aussi s’étendre à de l’information sur l’usage fait de codes d’autorisation attribués à des particuliers, y compris les cas où les codes ont pu être utilisés avec succès ou non, la date, l’heure et la fréquence d’utilisation.</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Employees of the government institution and other individuals using institutional electronic networks, including: student employees; contract staff and agency personnel; members of the public; Ministerial staff; or Members of Parliament that send e-mail to the government institution or specific individuals within the government institution.</t>
@@ -1958,6 +2024,7 @@
           <t>The information may be used to substantiate any disciplinary action taken where violation of institutional policies or the Policy on the Use of Electronic Networks is determined, and to support compliance with other relevant Treasury Board policy instruments or policy directions. This information may be shared for disciplinary purposes (refer to PSE 901 Employee Personnel Record and PSE 911 Discipline ). If an internal investigation determines that criminal actions may have taken place, the information may be shared with appropriate police authorities. This information may be used to provide reports to management. The information may also be used for research, planning, audit and evaluation purposes.  |  Links: PSE 901 Employee Personnel Record (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse901); PSE 911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2015,6 +2082,7 @@
           <t>PSE 916</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>pse916</t>
@@ -2045,6 +2113,9 @@
           <t>Les dossiers contenant des renseignements décrits dans ce fichier sont traités de façon confidentielle en ce qui touche la participation d’un employé au Programme d’aide aux employés. Ces dossiers peuvent comprendre des avis de mise en rapport volontaire ou obligatoire (connexe au rendement au travail); des dossiers de mise en rapport avec des professionnels de la santé ou un organisme de réadaptation, et les rapports et la correspondance provenant de ces derniers; les interprétations non médicales concernant les capacités ou les limites de travail de l’employé. Tous les renseignements médicaux personnels sont conservés à titre de renseignements médicaux protégés dans un fichier administré par l’Agence des services d’hygiène du travail et du milieu. Les dossiers ayant trait aux lacunes en matière de rendement de l’employé, à l’absentéisme et aux questions disciplinaires doivent être conservés dans le fichier pertinent de renseignements personnels de l’organisme ou du ministère, et non dans les dossiers du Programme d’aide aux employés.</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
@@ -2070,6 +2141,7 @@
           <t>To support decisions regarding employee assistance measures.</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2127,6 +2199,7 @@
           <t>PSE 912</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>pse912</t>
@@ -2162,6 +2235,7 @@
           <t>Bank formerly called Performance Management Reviews. Description last updated: March 2014.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>2014-03-01</t>
@@ -2194,7 +2268,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Les renseignements peuvent être utilisés ou divulgués pour les raisons suivantes : établissement de rapports à la haute direction, évaluation, audit, gestion des talents et planification de la relève, analyse des politiques, recherche et statistique. Dans le cas des institutions faisant partie de l’administration publique centrale, les renseignements peuvent être communiqués au Secrétariat du Conseil du Trésor du Canada; voir SCT PCE 754 Programme de gestion du rendement pour les employés . Les renseignements peuvent être communiqués à d’autres programmes et activités de l’institution; voir POE 911 – Mesures disciplinaires , POE 916 – Aide aux employés , POE 901 – Dossier personnel d’un employé , POE 910 – Griefs , POU 935 – Planification des ressources humaines , POE 907 – Santé et sécurité au travail , POE 904 – Rémunération et avantages , POE 920 – Programme de la reconnaissance , POE 902 – Dotation et POE 905 – Formation et perfectionnement .  |  Links: SCT PCE 754 Programme de gestion du rendement pour les employés (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-fra.asp#SCTPCE754); POE 911 – Mesures disciplinaires (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe911); POE 916 – Aide aux employés (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe916); POE 901 – Dossier personnel d’un employé (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe901); POE 910 – Griefs (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe910); POU 935 – Planification des ressources humaines (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou935); POE 907 – Santé et sécurité au travail (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071); POE 904 – Rémunération et avantages (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe904); POE 920 – Programme de la reconnaissance (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe920); POE 902 – Dotation (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021); POE 905 – Formation et perfectionnement (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe905)</t>
+          <t>Les renseignements peuvent être utilisés ou divulgués pour les raisons suivantes : établissement de rapports à la haute direction, évaluation, audit, gestion des talents et planification de la relève, analyse des politiques, recherche et statistique. Dans le cas des institutions faisant partie de l’administration publique centrale, les renseignements peuvent être communiqués au Secrétariat du Conseil du Trésor du Canada; voir SCT PCE 754 Programme de gestion du rendement pour les employés . Les renseignements peuvent être communiqués à d’autres programmes et activités de l’institution; voir POE 911 – Mesures disciplinaires , POE 916 – Aide aux employés , POE 901 – Dossier personnel d’un employé , POE 910 – Griefs , POU 935 – Planification des ressources humaines , POE 907 – Santé et sécurité au travail , POE 904 – Rémunération et avantages , POE 920 – Programme de la reconnaissance , POE 902 – Dotation et POE 905 – Formation et perfectionnement .  |  Links: SCT PCE 754 Programme de gestion du rendement pour les employés (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-fra.asp#SCTPCE754); POE 911 – Mesures disciplinaires (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe911); POE 916 – Aide aux employés (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe916); POE 901 – Dossier personnel d’un employé (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe901); POE 910 – Griefs (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe910); POU 935 – Planification des ressources humaines (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou935); POE 907 – Santé et sécurité au travail (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907); POE 904 – Rémunération et avantages (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe904); POE 920 – Programme de la reconnaissance (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe920); POE 902 – Dotation (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902); POE 905 – Formation et perfectionnement (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe905)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2289,11 +2363,15 @@
           <t>Ce dossier décrit les renseignements sur l’emploi d’une personne dans les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques (y compris le service militaire, les désignations ou certifications professionnelles), la citoyenneté, la date et le lieu de naissance, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, les pouvoirs délégués accordés ou les biens prêtés aux employés (p. ex., les pouvoirs de dotation ou de signature de documents financiers, l’utilisation de matériel institutionnel), les réaménagements des horaires de travail (p. ex., télétravail, semaine de travail comprimée), les renseignements liés à la pension de retraite, les avantages sociaux, la formation et le perfectionnement, les griefs, les incidents de sécurité, toute autre exigence liée à l’emploi (p. ex., permis de port d’arme à feu, autorisations de sécurité, renseignements sur le passeport/visa), les renseignements financiers (pour l’administration de la paye), les renseignements médicaux (y compris tous les besoins spéciaux déterminés dans le cadre de l’obligation de prendre des mesures d’adaptation, ou en cas d’urgence), d’autres numéros d’identification, la signature et le numéro d’assurance sociale (NAS). Les informations sur l'équité en matière d'emploi ne seront utilisées qu'aux fins principales, et non pour les utilisations compatibles énumérées.</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, emergency contacts of employees, and may also include spouses, dependants, and beneficiaries.</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Personal information is used to facilitate personnel administration in the employing institution and to ensure continuity and accuracy when an employee is transferred to another institution. For most government institutions, personal information is collected under the authority of the Public Service Employment Act (PSEA). For those institutions not subject to the (PSEA), consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection. The Social Insurance Number is collected pursuant to the Income Tax Act.</t>
@@ -2309,6 +2387,7 @@
           <t>Information is disclosed to Canada Revenue Agency refer to Individual Returns and Payment Processing – CRA PPU 005 and to the Province of Quebec (where applicable) for income tax purposes. Information is also disclosed to Employment and Social Development Canada (ESDC) for employment insurance and pension purposes. Information may also be disclosed to Public Works and Government Services Canada (PWGSC) to facilitate payment of salary including direct deposit refer to Bank Public Service Compensation Systems - PWGSC PCE 705 . Where applicable, information may also be disclosed to various provincial health insurance plans or third-party group insurance companies. Information may be used to confirm the identity of employees for access to government and institutional information technology infrastructure. Where applicable, information may be disclosed to Shared Services Canada (SSC). Selected information is shared with previous employers for the purpose of finalizing payments, including retroactive payments and the recovery of outstanding amounts owing to the Crown. Information may be used for general human resource management purposes, including to verify and report on policy compliance. In instances of suspected non-compliance, information may be disclosed to the institution’s security and/or staff relations officials for further investigations or disciplinary actions (refer to PSU 939 Security Incidents and Privacy Breaches and PSE 911 Discipline ). Information may also be used or disclosed for program evaluation purposes.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Public Service Compensation Systems - PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); PSU 939 Security Incidents and Privacy Breaches (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#psu939); PSE 911 Discipline (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2324,9 +2403,15 @@
           <t>98/005 and 98/018</t>
         </is>
       </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>PRN 920</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>NDP 920</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2356,6 +2441,7 @@
           <t>PSE 918</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>pse918</t>
@@ -2386,6 +2472,9 @@
           <t>Les dossiers contenant les renseignements décrits dans ce fichier comprennent des renseignements personnels sur les employés, notamment sur leurs études; leurs antécédents professionnels et leurs projets de carrière; leur formation et leur perfectionnement. Tous ces renseignements ont été recueillis au moyen de questionnaires ou d’entrevues, ou compilés à partir de leurs dossiers ou des systèmes de données automatisés. Les répondants, qui sont libres de fournir ces renseignements, indiquent leur sexe et s’ils sont autochtones, handicapés ou font partie d’une minorité visible. Le Code d’identification de dossier personnel peut servir à identifier les employés lorsque les institutions fédérales ne peuvent pas utiliser un questionnaire anonyme ou lorsqu’il est nécessaire d’avoir ces indicatifs afin de pouvoir trouver le dossier de l’employé.</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
@@ -2403,7 +2492,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Ces dossiers ont pour but de recueillir toute la documentation nécessaire à la mise en œuvre de la politique relative à l’équité en matière d’emploi pour toutes les institutions fédérales. C’est grâce à ces renseignements qu’il est possible d’avoir toutes les données au sujet des employés, présentées selon leur sexe et leur groupe cible (femmes, autochtones et personnes handicapées et personnes faisant partie de minorités visibles). Ces renseignements sont utilisés afin de réaliser un profil personnel des employés et de comparer la situation des membres des groupes cibles avec celles des autres groupes au sein des ministères et organismes fédéraux et avec leurs homologues sur le marché du travail. Le Code d’identification de dossier personnel peut servir à établir un lien entre les renseignements contenus dans ce fichier et ceux conservés dans un autre fichier comprenant des renseignements sur les employés (p. ex., le Système d’information pour la gestion du personnel) et ce, à des fins statistiques et lorsque la conservation de tels renseignements est conforme aux usages pour lesquels les renseignements personnels ont été recueillis. Il est possible d’obtenir des données d’auto-identification des dossiers institutionnels qui sont décrits dans le Fichier de renseignements personnels Dotation – POE 902 .  |  Links: Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021)</t>
+          <t>Ces dossiers ont pour but de recueillir toute la documentation nécessaire à la mise en œuvre de la politique relative à l’équité en matière d’emploi pour toutes les institutions fédérales. C’est grâce à ces renseignements qu’il est possible d’avoir toutes les données au sujet des employés, présentées selon leur sexe et leur groupe cible (femmes, autochtones et personnes handicapées et personnes faisant partie de minorités visibles). Ces renseignements sont utilisés afin de réaliser un profil personnel des employés et de comparer la situation des membres des groupes cibles avec celles des autres groupes au sein des ministères et organismes fédéraux et avec leurs homologues sur le marché du travail. Le Code d’identification de dossier personnel peut servir à établir un lien entre les renseignements contenus dans ce fichier et ceux conservés dans un autre fichier comprenant des renseignements sur les employés (p. ex., le Système d’information pour la gestion du personnel) et ce, à des fins statistiques et lorsque la conservation de tels renseignements est conforme aux usages pour lesquels les renseignements personnels ont été recueillis. Il est possible d’obtenir des données d’auto-identification des dossiers institutionnels qui sont décrits dans le Fichier de renseignements personnels Dotation – POE 902 .  |  Links: Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2411,6 +2500,7 @@
           <t>The government institution may collect data for statistical purposes, for purposes relating to individuals, or for both. Personal data are released to the Treasury Board of Canada Secretariat for statistical purposes only (refer to Central Personal Information Bank Employment Equity Data Bank - TBS PCE 739 ). The information gathered will be used for institutional purposes in the government’s employment equity program to identify and eliminate systemic discrimination in employment and to introduce temporary special measures to ensure that target groups participate in and are equitably represented in the federal public service. It may also be used for policy and planning purposes related to employment equity.  |  Links: Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp)</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2468,6 +2558,7 @@
           <t>PSU 902</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>psu902</t>
@@ -2475,7 +2566,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>poe902</t>
+          <t>pou902</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2498,6 +2589,9 @@
           <t>Les dossiers contenant les renseignements décrits dans ce fichier comprennent la correspondance générale du ministre ou du secrétaire d’État, de leur personnel ainsi que celle d’autres cadres supérieurs au sein de l’institution. Les dossiers utilisés pour préparer les réponses à la correspondance reçue peuvent contenir des renseignements personnels particuliers qui sont fournis parfois par des agents de l’institution afin de donner suite aux questions et aux préoccupations soulevées dans le courrier d’arrivée. Les renseignements personnels peuvent comprendre le nom du correspondant, ses coordonnées ainsi que d’autres renseignements que l’expéditeur et/ou le répondant a inclus dans la correspondance.</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>General public, Members of Parliament, and officials representing other levels of government or international governments and agencies, external organizations and/or businesses.</t>
@@ -2523,6 +2617,7 @@
           <t>Incoming correspondence may be forwarded to other federal or provincial institutions for a full or partial response if it is determined by the receiving institution that the issue(s) contained within the correspondence fall under the jurisdiction of, and should be addressed by, the other institution(s). In some cases, incoming correspondence and the response may be copied to another federal or provincial institution where the correspondence impacts on their roles and responsibilities. The information may be used in an aggregate format to report on system use, growth of the information collection, etc. The Executive Correspondence Management System may be integrated with the institution’s Automated Document, Records and Information Management System.</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2560,7 +2655,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902</t>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou902</t>
         </is>
       </c>
     </row>
@@ -2580,6 +2675,7 @@
           <t>PSU 942</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>psu942</t>
@@ -2610,11 +2706,15 @@
           <t>Ce fichier décrit des renseignements personnels inhérents à la fonction et aux activités d’évaluation d’une institution fédérale. Les renseignements personnels dont il est question peuvent comprendre le nom, les coordonnées, des données démographiques, des renseignements financiers, des numéros d’identification, le sexe, des titres de poste, ainsi que des opinions et des points de vue sur, ou concernant, des individus et recueillis, dans certains cas, avec le consentement éclairé des personnes visées.</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Program participants, managers, employees, or partners of the program or institution, including government representatives from other jurisdictions, representatives of businesses and private sector organizations, academics or other experts in the program area, and other stakeholders including members of the general public.</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Personal information is used in data collection and analysis when undertaking evaluations. In some cases, a limited amount of personal information, (typically names and /or titles of academics or other experts) may appear in evaluation reports where informed consent has been given by the person or persons to whom the information relates. For many institutions, information is collected pursuant to sections 7 and 42.1 of the Financial Administration Act. For those not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -2630,6 +2730,7 @@
           <t>Information may be shared with the deputy head of the institution, the government institution Evaluation Committee, and program managers. Information may be also be shared with (1) other government institutions or other partners involved in managing or delivering the program and in undertaking the evaluation; (2) Treasury Board Secretariat officials; and (3) consultants performing evaluation work on behalf of the institution. Final evaluation reports are made publicly available.</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2722,6 +2823,9 @@
           <t>Ce fichier décrit l’information sur les employés fédéraux de la catégorie EX qui s’inscrivent à l’outil de gestion des talents des cadres supérieurs. Les renseignements personnels peuvent comprendre le nom, les coordonnées de la personne et du superviseur, le numéro d’identification de l’employé, de l’information sur l’équité en emploi, des renseignements biographiques, des renseignements sur les études, des renseignements personnels de l’employé, la date de naissance, le sexe, les opinions et points de vue sur, ou concernant, des individus, la photo et la signature.</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Employees at the EX-01 to EX-02 category and levels who choose to register for this tool. The tool is mandatory for employees at the EX-03, EX-04 and EX-05 levels (Assistant Deputy Minister levels).</t>
@@ -2747,6 +2851,7 @@
           <t>Information collected for executives who are at the ADM or equivalent level may be shared with the Clerk of the Privy Council’s Committee of Senior Officials. Information may also be shared with/described in the Standard Personal Information Banks: Employee Performance Management Program – PSE 912 , Training and Development - PSE 905 , and Human Resources Planning - PSU 935 . Information may also be used or disclosed for program evaluation.  |  Links: Employee Performance Management Program – PSE 912 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse912); Training and Development - PSE 905 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905); Human Resources Planning - PSU 935 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935)</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2804,6 +2909,7 @@
           <t>PSU 918</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>psu918</t>
@@ -2834,6 +2940,9 @@
           <t>Sont décrits dans ce fichier les renseignements recueillis à l’appui des nominations du gouverneur en conseil dans les institutions fédérales. Les renseignements personnels recueillis peuvent comprendre: le nom complet de la personne, ses coordonnées, sa langue officielle de préférence, sa date de naissance, son pays natal, sa citoyenneté, son sexe, sa situation de famille, son numéro d’assurance sociale (NAS), un numéro d’identification exclusif (p. ex., un numéro d’employé unique), les modalités de sa nomination, y compris sa rémunération (p. ex., traitement, honoraires, indemnité quotidienne) et ses avantages sociaux, sa signature, ses limitations physiques et toute autre information médicale pertinente, des photographies ou d’autres enregistrements visuels, sa scolarité, sa situation d’emploi, ses antécédents de travail, ses affiliations professionnelles, de l’information sur ses cartes de crédit et son établissement bancaire, sa cote de sécurité au gouvernement, des données biographiques (y compris des renseignements sur les membres de sa famille), toute déclaration de conflit d’intérêts, des lettres de référence/de recommandation, la date de nomination, la durée de la nomination et la date de démission, s’il y a lieu.</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Current and former appointees and their family members.</t>
@@ -2859,6 +2968,7 @@
           <t>Personal information about the appointee is contained in the Order in Council document which includes full name, contact information, the position to which s/he is being appointed, the length and tenure of the appointment, and the terms and conditions of the appointment (e.g., remuneration, benefits, vacation leave, etc.). This information is provided by the Privy Council Office to the institution (refer to Governor in Council Personnel Records - PCO PPU 020 ). Governor in Council Personnel Records - PCO PPU 020). Additionally, this information may be used in the preparation of reports for senior management and broader audiences (e.g., Annual Reports) and communications materials (e.g., press releases, biographies, etc.) that may be disseminated in multiple formats, including the institution’s website. In some instances, the Privy Council Office receives notes and performance ratings to support the conduct of performance evaluations of selected individuals (refer to Governor in Council Personnel Records - PCO PPU 020 ). The Social Insurance Number (SIN) is collected pursuant to the Income Tax Act (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and, where applicable, the Province of Quebec Income Tax Act.  |  Links: Governor in Council Personnel Records - PCO PPU 020 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Governor in Council Personnel Records - PCO PPU 020 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -2916,6 +3026,7 @@
           <t>PSE 910</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>pse910</t>
@@ -2956,6 +3067,7 @@
           <t>Pour les institutions assujetties à la Loi sur les relations de travail dans la fonction publique, l’article 208 de la Loi confère à un employé le droit de présenter un grief individuel à moins qu’une procédure administrative de réparation ne soit prévue dans une loi fédérale, distincte de la Loi canadienne sur les droits de la personne.</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Current and past employees of government institutions, their representatives or bargaining agents, and any other witness or individual who may be involved in the grievance process including individuals who serve as mediators, adjudicators, or arbitrators.</t>
@@ -2981,6 +3093,7 @@
           <t>Information concerning grievances filed under the Public Service Labour Relations Act may be shared with the Public Service Labour Relations Board (refer to Central Personal Information Banks: Applications for Extension of Time - PSLRB PCE 710 , Applications for an extension of time in respect of a grievance - PSLRB PCE 715 , Complaint/Grievance Mediation - PSLRB PCE 726 , Complaints under Section 190 of the Public Service Labour Relations Act (PSLRA) - RLT PCE 730 , and Requests for Review of Decisions – PSLRB PCE 793 . Certain complaints may be referred to mediation, adjudication, or arbitration by the Public Service Labour Relations Board (refer to Central Personal Information Banks: References of Grievances to Adjudication - PSLRB PCE 791 and Reference to Adjudication of Individual Grievances - PSLRB PCE 792 ). In these cases, information may be disclosed to individuals who are appointed by the Public Service Labour Relations Board or by a government institution to serve as mediators, adjudicators or arbitrators. Full-text versions of decisions are posted on the Public Service Labour Relations Board website. In some cases, information may be shared with the Canadian Human Rights Commission where a party to a grievance raises an issue involving the interpretation or application of the Canadian Human Rights Act within the context of a request for arbitration of the grievance. Aggregate information may be used or disclosed for annual reporting purposes. Some information about grievances may also be shared with/described in Standard Personal Information Banks Employee Personnel Record - PSE 901 and Discipline - PSE 911 . Information may also be used or disclosed for evaluation purposes.  |  Links: Applications for Extension of Time - PSLRB PCE 710 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Applications for an extension of time in respect of a grievance - PSLRB PCE 715 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Complaint/Grievance Mediation - PSLRB PCE 726 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Complaints under Section 190 of the Public Service Labour Relations Act (PSLRA) - RLT PCE 730 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Requests for Review of Decisions – PSLRB PCE 793 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); References of Grievances to Adjudication - PSLRB PCE 791 (http://www.pslrb-crtfp.gc.ca/reports/infosource_e.asp); Reference to Adjudication of Individual Grievances - PSLRB PCE 792 (http://pslrb-crtfp.gc.ca/reports/intro_e.asp); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3038,6 +3151,7 @@
           <t>PSE 919</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>pse919</t>
@@ -3088,6 +3202,7 @@
           <t>Employees and other persons working for a government institution, or other persons involved in alleged occurrences of harassment and violence in federal institutions.</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Information is used to prevent, resolve and investigate harassment and violence notices of occurrence (including through early resolution and conciliation processes), ensuring that all parties involved are treated with respect and dignity throughout the process. Procedural fairness is upheld by providing the principal party and responding party with the opportunity to be heard, ensuring that decisions are made impartially and maintaining transparency in the resolution process.</t>
@@ -3165,6 +3280,7 @@
           <t>PSU 908</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>psu908</t>
@@ -3195,11 +3311,15 @@
           <t>Ce fichier décrit les renseignements liés à la fourniture de breuvages, de repas, de visites guidées ou d’autres divertissements remboursés par les institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements personnels de l’employé, le numéro d’identification d’employé et les renseignements financiers.</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Employees of the government institution who incur hospitality expenses, their spouses, other attendees, private sector hospitality providers and/or other individuals who may be paid out of the Consolidated Revenue Fund (i.e. who receive a fee, honorarium or per diem allowance).</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Personal information is used to administer the hospitality expenses and reimbursements of government institutions. For most government institutions, personal information is collected pursuant to the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
@@ -3215,6 +3335,7 @@
           <t>Where applicable, hospitality expenses incurred by the Minister, Parliamentary Secretary, exempt staff, and by senior level employees (i.e. Deputy Minister, Associate Deputy Minister, Assistant Deputy Minister, and equivalent) may be proactively disclosed on government institutions’ websites. Information may be shared with/described in Standard Personal Information Bank Accounts Payable - PSU 931 . Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931)</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3240,6 +3361,7 @@
           <t>PRN 933, PRN 935</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu908</t>
@@ -3302,6 +3424,9 @@
           <t>Ce fichier décrit l’information liée à la gestion salariale et à la planification des ressources humaines, ce qui comprend les fonctions de compte rendu et d’établissement des prévisions. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, les renseignements sur l’éducation, le numéro d’identification de l’employé, les renseignements sur l’équité en emploi, les renseignements personnels de l’employé, et les opinions et points de vue sur, ou concernant, des individus.</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, job applicants, students, casual and contract employees, and Interchange Canada participants.</t>
@@ -3327,6 +3452,7 @@
           <t>Personal information may be shared with other government institutions in cases of transfer of section of the public service under the Public Service Rearrangement and Transfer of Duties Act. Personal information may be shared with provincial or municipal governments, and institutions thereof, or private sector institutions in cases of devolution or privatization of a program or activity. Some employee information may also be shared with/described in the Standard Personal Information Banks Employment Equity Program - PSE 918 , Employee Personal Record - PSE 901 , Pay and Benefits - PSE 904 , Staffing - PSE 902 , Training and Development - PSE 905 , and Official Languages - PSE 906 . Information may be also be used or disclosed for program evaluation.  |  Links: Employment Equity Program - PSE 918 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse918); Employee Personal Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904); Staffing - PSE 902 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse902); Training and Development - PSE 905 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse905); Official Languages - PSE 906 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse906)</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator</t>
@@ -3384,6 +3510,7 @@
           <t>PSU 941</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>psu941</t>
@@ -3424,6 +3551,7 @@
           <t>Les renseignements personnels qui se trouvent dans les documents de l’institution peuvent être divulgués au Bureau du vérificateur général pour des études ou des vérifications.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Employees and former employees of the institution, contractors, representatives of companies.</t>
@@ -3449,6 +3577,7 @@
           <t>Information may be shared with responsible managers, and in some cases, the government institution Audit Committee, the Audit Committee of the Board of Directors, the Board of Directors, and/or the Office of the Auditor General. Information may be also be shared with: 1) Human Resources for disciplinary measures (refer to Discipline – PSE 911 ); 2) Security (refer to Security Incidents and Privacy Breaches – PSU 939 ); 3) Investigative personnel and law enforcement agencies in the event of an alleged criminal offence; and 4) consultants performing internal audit work on behalf of the institution’s Chief Audit Executive.  |  Links: Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911); Security Incidents and Privacy Breaches – PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu939)</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3469,6 +3598,7 @@
           <t>99/004</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
           <t>NDP 916</t>
@@ -3501,6 +3631,7 @@
           <t>PSU 915</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>psu915</t>
@@ -3541,11 +3672,13 @@
           <t>Ces renseignements peuvent être stockés sous forme papier ou électronique (p. ex., dans des bases de données ou dans des sites Web, y compris les applications de médias sociaux, etc.). Bien qu’une institution ne demande pas les adresses du protocole Internet expressément, celles-ci peuvent être saisies de manière électronique à la réception d’un courriel.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Employees and other individuals with access to institutional networks including individuals who have prepared information for dissemination, such as publication on the institution’s intranet, or who act as contact points within the institution.</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Personal information is used to manage internal communications. For many institutions, personal information is collected under the authority of the Financial Administration Act, and in accordance with the Communications Policy of the Government of Canada. For those institutions not subject to the Act or the Policy, consult the institution’s Access to Information and Privacy Coordinator to determine the legal authority for the collection.</t>
@@ -3561,6 +3694,7 @@
           <t>The names, photographs, recordings and other personal information about individuals who work for the institution may be included in documentation posted on the institution’s intranet: e.g., within speeches, newsletters, etc. Information may be used or disclosed to provide statistical reports to management as well as for program evaluation.</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3618,6 +3752,7 @@
           <t>PSU 936</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>psu936</t>
@@ -3648,11 +3783,15 @@
           <t>Ce fichier décrit l’information sur les personnes qui utilisent les installations, les collections et les services de bibliothèques des institutions fédérales. Les services peuvent comprendre les prêts, les références et la recherche, ainsi que les services d’avertissement et de mises au courant, dont l’évaluation des demandes des clients quant aux nouvelles acquisitions. Les renseignements personnels peuvent comprendre le nom, les coordonnées, l’affiliation de l’organisme, le sujet de recherche, d’autres numéros d’identification, y compris le numéro de carte de l’utilisateur et sa date d’expiration, ainsi que le numéro de code à barres du client.</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Full-and part-time, casual, and term employees of government institutions, agency employees, members of the general public, researchers, and employees of non-government institution libraries.</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Personal information is used to support the delivery of library services of government institutions, such as identifying user preferences, researching topics, analyzing trends in information needs, processing inter-library loans, and controlling the circulation of material.</t>
@@ -3668,6 +3807,7 @@
           <t>Information may be used or disclosed for program evaluation.</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3760,6 +3900,9 @@
           <t>Ce fichier décrit l’information recueillie par les titulaires d’une charge publique désignée (p. ex., les administrateurs généraux actuels et les anciens administrateurs généraux, les sous-ministres adjoints, les cadres supérieurs des Forces canadiennes, etc.) au sujet de la vérification des activités des lobbyistes sur demande du commissaire au lobbying. Les renseignements personnels peuvent comprendre le nom, les coordonnées, de l’information financière, des renseignements biographiques, la date et de l’heure de l’activité de communication/lobbying, ainsi que les opinions et les points de vue des individus sur le sujet.</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Designated public office holders and lobbyists as defined in the Lobbying Act.</t>
@@ -3785,6 +3928,7 @@
           <t>Information may be made accessible to the public via the website of the Office of the Commissioner of Lobbying of Canada (refer to Information-Specific Personal Information Bank Lobbyist Registry - OCL PPU 039 ). Information may be also be used or disclosed for program evaluation.  |  Links: Lobbyist Registry - OCL PPU 039 (https://lobbycanada.gc.ca/eic/site/012.nsf/eng/00843.html)</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3842,6 +3986,7 @@
           <t>PSU 919</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>psu919</t>
@@ -3872,6 +4017,9 @@
           <t>Ce fichier décrit les renseignements personnels utilisés dans le processus d’identification et de sélection des personnes qui seront nommées aux conseils d’administration, comités et conseils de diverses institutions. Les renseignements personnels peuvent comprendre : le nom complet de la personne, ses coordonnées, sa langue officielle de préférence, sa date de naissance, son pays natal, sa citoyenneté, son sexe, sa situation de famille, son appartenance à un groupe minoritaire, son numéro d’assurance sociale (NAS), un numéro d’identification exclusif (p. ex., un numéro d’employé unique), les modalités de sa nomination, y compris sa rémunération (p. ex., traitement, honoraires, indemnité quotidienne) et ses avantages sociaux, sa signature, ses limitations physiques et toute autre information médicale pertinente, des photographies ou d’autres enregistrements visuels, sa scolarité, sa situation d’emploi, ses antécédents de travail, ses activités bénévoles, ses affiliations professionnelles, de l’information sur ses cartes de crédit et son établissement bancaire, sa cote de sécurité au gouvernement, des données biographiques (y compris des renseignements sur les membres de sa famille), toute déclaration de conflit d’intérêts, des lettres de référence/de recommandation, la date de nomination, la durée de la nomination et la date de démission, s’il y a lieu.</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Candidates, as well as current and former members of Boards, Committees, and Councils, their family members, and individuals whose names have been provided as personal references.</t>
@@ -3897,6 +4045,7 @@
           <t>This information may be used in the preparation of reports for senior management and broader audiences (e.g., Annual Reports), planning and evaluation purposes, and communications materials (e.g., press releases, biographies, etc.) that may be disseminated in multiple formats, including the institution’s website. With consent of the individual, this information may be shared with other Government of Canada institutions for uses consistent with the mandate of the Board, Committee or Council on which personal information is collected to fill positions (Refer to Members of Boards, Committees and Councils – PSU 919 of the specific government institution). Information may be disclosed to the Canada Revenue Agency (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and, where applicable, the Province of Quebec for income tax purposes. Assistance of third party service providers may be used during the selection process.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html)</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -3954,6 +4103,7 @@
           <t>PSE 907</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>pse907</t>
@@ -3961,7 +4111,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>poe9071</t>
+          <t>poe907</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3984,11 +4134,15 @@
           <t>Ce fichier décrit l’information qui est utilisée dans le but d’appuyer une activité liée à la santé et à la sécurité du travail dans une institution fédérale, y compris la prévention des accidents et des blessures ou des maladies de nature professionnelle; une autorisation de congé payé liée à un accident du travail ou une maladie professionnelle; les services d’aide aux employés; les évaluations sur l’aptitude à retourner au travail; l’obligation de prendre des mesures d’adaptation; les évaluations de santé et de nature ergonomique; les plaintes relatives à la santé et à la sécurité; l’indemnisation des accidentés; la réadaptation et le recyclage. Les renseignements personnels peuvent comprendre le nom, les coordonnées, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, la nature de la plainte, les renseignements médicaux, les opinions et les points de vue sur, ou concernant, des individus, et la signature.</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions, including casual and contract employees; private sector health practitioners; health and safety professionals; attendants for persons requiring assistance; family members who are part of the same household and eligible for corporate rates for Wellness programs; and individuals designated as emergency contacts of employees</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Personal information is used to administer occupational safety and health activities in government institutions, which includes the promotion of a safe and healthy workplace for employees and others, provision of corporate Wellness programs, the prevention of accidents, occupational injuries and illnesses and, where applicable, the investigation of occurrences of such injuries and illnesses. Information may be collected pursuant to paragraph 7(1)(e) and subsection 11.1 of the Financial Administration Act; sections 114 and 240 of the Public Service Labour Relations Act; Part II of the Canada Labour Code and Part XVI of the Canada Occupational Health and Safety Regulations, the Government Employees Compensation Act, and the National Joint Council Directives.</t>
@@ -4004,6 +4158,7 @@
           <t>Information may be used or disclosed for the following reasons: to support decisions related to worker’s compensation and injury-on-duty leave; as a means of preventing injuries and illnesses and subsequent disabilities arising out of, or aggravated by, conditions of work; to establish that individuals subject to certain identified occupational risks are able to continue working without detriment to their health or safety or to that of others; and to establish the conditions under which certain individuals with identified illnesses or disabilities are able to continue to work under controlled conditions. Information may be shared with private sector health care providers. Information may be used to communicate with contacts of employees in emergency situations. Information concerning occupational health evaluations including related personal medical information is retained by Health Canada in the Corporate Services Branch under medical confidential status (refer to Central Personal Information Bank: Public Service Occupational Health Program - HC PCE 701 ). Information with respect to safety and health complaints and causes of accidents/injuries for accident prevention and health protection purposes is used to support the effective administration of each institution’s safety and health activity; such information is also disclosed to the institution’s work place health and safety committee. Information is also used to process payments and charge-backs with respect to injury compensation claims. Information related to injury compensation claims, including related correspondence and amounts paid, is retained by Employment and Social Development Canada and is shared with the institution of the affected employee and, where applicable, the relevant provincial or territorial workers’ compensation board. Employment and Social Development Canada holds information pertaining to employee compensation amounts, which are charged to institutions and distributed on a cost-recovery basis (refer to Personal Information Bank: Federal Workers Compensation - ESDC PPU 032 ). Information may also be shared with Employment and Social Development Canada, specifically, with safety officers for the purposes of accident and refusal to work investigations and the stipulation of corrective measures. Information may be shared with/described in other Standard Personal Information Banks pertaining to human resources activities including: Employee Personnel Record - PSE 901 ; Attendance and Leave - PSE 903 ; Employee Assistance - PSE 916 ; Pay and Benefits - PSE 904 ; and Grievances - PSE 910 . The investigation and settlement of vehicle accidents is also described in Standard Personal Information Bank Vehicle, Ship, Boat and Aircraft Accidents - PSE 908 . Information may also be used or disclosed for planning and program evaluation purposes.  |  Links: Public Service Occupational Health Program - HC PCE 701 (https://www.canada.ca/en/health-canada/corporate/about-health-canada/activities-responsibilities/access-information-privacy/info-source-federal-government-employee-information.html#a3.14); Federal Workers Compensation - ESDC PPU 032 (http://www.esdc.gc.ca/eng/transparency/ati/reports/infosource/index.shtml); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Attendance and Leave - PSE 903 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse903); Employee Assistance - PSE 916 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse916); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910); Vehicle, Ship, Boat and Aircraft Accidents - PSE 908 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse908)</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4041,7 +4196,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071</t>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907</t>
         </is>
       </c>
     </row>
@@ -4061,6 +4216,7 @@
           <t>PSE 906</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>pse906</t>
@@ -4131,6 +4287,7 @@
           <t>To support and document decisions concerning individual employees on staffing, entitlement to bilingual bonus where applicable, transfers and promotions; and to aid in determining the linguistic status of employees and auditing of the administration of official language programs. Information may be disclosed to federal government institutions, the Public Service Commission and Treasury Board of Canada Secretariat where applicable for recruitment and staffing purposes (refer to Institution-Specific Personal Information Banks: for the Public Service Commission of Canada: Executive Resourcing - PSC PCE 746 ; for Treasury Board of Canada Secretariat: Employment Equity Data Bank - TBS PCE 739 ).  |  Links: Executive Resourcing - PSC PCE 746 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp)</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4188,6 +4345,7 @@
           <t>PSU 938</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>psu938</t>
@@ -4238,6 +4396,7 @@
           <t>Current and former employees of government institutions, representatives of other levels of government, representatives of the academic and business communities, members of the general public (including parents and guardians where minors are concerned), and event speakers and facilitators.</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>The information is used to enable individuals to participate in national and/or international outreach activities sponsored by government institutions. Such activities facilitate information exchanges in areas of common interest to institutions and their stakeholders and allow for the sharing of knowledge, expertise, and best practices. Personal information is collected pursuant to various federal laws and regulations. For the specific collection authority(ies), consult the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4253,6 +4412,7 @@
           <t>With notification, the proceedings of some outreach activities that are recorded may be made publicly available, including on the Internet. With consent, the information may be used to establish mailing lists to inform participants of future events or to contact individuals to seek views on issues of mutual interest. Information may be used to moderate public discussion on the social media platforms used by the institution. Information may be also be used or disclosed for program evaluation.</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4310,6 +4470,7 @@
           <t>PSE 914</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>pse914</t>
@@ -4340,11 +4501,15 @@
           <t>Ce fichier décrit les renseignements personnels liés aux demandes de permis de stationnement et aux détenteurs de permis de stationnement pour des propriétés louées par ou appartenant à des institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées à la maison et au travail, les renseignements biographiques, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, les renseignements médicaux (pour ceux qui demandent un stationnement pour les personnes handicapées), les renseignements d’identification du véhicule, les critères de tarification, et la signature.</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Employees of the institution, passengers, contractors or other individuals, property owners or representatives.</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Personal information is used for the administration of parking privileges and to authorize payroll deductions. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -4360,6 +4525,7 @@
           <t>Where government or other property is damaged, the accident may be reported to the Royal Canadian Mounted Police (refer to Central Personal Information Bank Protection of Personnel and Government Property - RCMP PPU 055) or to other policing authorities, or to the person(s) in charge or in control of the property. Information may be shared with Public Works and Government Services for the purpose of payroll deduction (refer to Central Personal Information Bank Public Service Compensation Systems - PWGSC PCE 705 ). Payroll deduction information may be shared with/described in Standard Personal Information Bank Pay and Benefits - PSE 904 . Information may also be used or disclosed for evaluation or reporting purposes.  |  Links: Public Service Compensation Systems - PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Pay and Benefits - PSE 904 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse904)</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4417,6 +4583,7 @@
           <t>PSE 904</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>pse904</t>
@@ -4447,11 +4614,15 @@
           <t>Ce fichier décrit les renseignements liés à l’administration de la rémunération et des avantages sociaux au sein des institutions fédérales. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, la date de naissance, la date du décès, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers, et le numéro d’assurance sociale (NAS).</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Current and former employees of government institutions.</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Personal information is shared with Public Works and Government Services and is used to disburse salaries and allowances and to process deductions and orders for garnishment and diversion of funds. Personal information is collected under various Acts including the Financial Administration Act, the Government Employees Compensation Act, and the Public Service Labour Relations Act. The Social Insurance Number (SIN) is collected pursuant to the Income Tax Act, Canada Pension Plan, and the Employment Insurance Act, and for some institutions, the SIN is shared with Public Works and Government Services to create the Personal Record Identifier.</t>
@@ -4467,6 +4638,7 @@
           <t>Information is shared with Public Works and Government Services Canada (refer to Public Service Compensation Systems -PWGSC PCE 705 and Public Service Pensions Data Bank - PWGSC PCE 702 ). Information, including the SIN, is disclosed to the Canada Revenue Agency (refer to Individual Returns and Payment Processing – CRA PPU 005 ) and the Province of Quebec (if applicable) for taxation and pension purposes. Information may also be shared with the Department of Justice Canada to administer the Family Orders and Agreements Enforcement Assistance Act and the Garnishment, Attachment and Pension Diversion Act (refer to Family Orders and Agreements Enforcement Assistance - JUS PPU 125 and Garnishment Registry - JUS PPU 150 ). Information may be shared with third party service providers, for select institutions. Some information on pay and benefits may also be shared with/described in the Standard Personal Information Banks Employee Personnel File - PSE 901 , Grievances - PSE 910 , and Discipline - PSE 911 . Information may also be used or disclosed for program evaluation.  |  Links: Public Service Compensation Systems -PWGSC PCE 705 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Public Service Pensions Data Bank - PWGSC PCE 702 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/ressources-resources/infosource-eng.html); Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Family Orders and Agreements Enforcement Assistance - JUS PPU 125 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/index.html); Garnishment Registry - JUS PPU 150 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/p3.html); Employee Personnel File - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Grievances - PSE 910 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse910); Discipline - PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4564,6 +4736,8 @@
           <t>(1) Information may be stored in either hard copy format or electronically (e.g. in databases). (2) Some institutions have developed institution-specific security screening personal information banks. Individuals seeking access to their information in PSU 917 may also want to request that other institutional PIBs related to security screening be included in the access to information request if they have worked in or for the following departments which maintain separate PIBs: Public Services and Procurement Canada (Industry Personnel Clearance and Reliability Records – PWGSC PPU 015) ; National Defence / Canadian Armed Forces (Personnel Security Investigation File – DND PPU 834) ; Privy Council Office (Security Clearance and Assessments Bank – PCO PPE 801) ; Royal Canadian Mounted Police (Security Reliability Screening Records – RCMP PPU 065) ; and Canadian Security Intelligence Service (Employee Security – SIS PPE 815) .  |  Links: Public Services and Procurement Canada (Industry Personnel Clearance and Reliability Records – PWGSC PPU 015) (https://www.tpsgc-pwgsc.gc.ca/aiprp-atip/infosource2014-eng.html); National Defence / Canadian Armed Forces (Personnel Security Investigation File – DND PPU 834) (https://www.forces.gc.ca/en/transparency-access-info-privacy/info-source-toc.page); Privy Council Office (Security Clearance and Assessments Bank – PCO PPE 801) (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Royal Canadian Mounted Police (Security Reliability Screening Records – RCMP PPU 065) (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/pib-frp-eng.htm); Canadian Security Intelligence Service (Employee Security – SIS PPE 815) (https://www.csis.gc.ca/tp/nfsrc-en.php)</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Job applicants, all current and former employees (students, agency and casual employees, persons on loan, assignment or secondment, exempt staff of ministers, ministers of state and parliamentary secretaries, locally engaged staff), volunteers, contractors, foreign and domestic visitors, immediate relatives, current and former spouse/common law partner, associates, cohabitants, individuals who give character references (including neighbours), current/former employers, parents or guardians of job applicants and employees under the age of 18.</t>
@@ -4586,12 +4760,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Where required, personal information may be shared in accordance with the institution's enabling legislation and within the parameters of the Privacy Act, with the Royal Canadian Mounted Police ( Canadian Criminal Real Time Identification Services – RCMP OPS 1214 and Personnel Security Records – RCMP ADM 445 ) and the Canadian Security Intelligence Service ( Security Assessments/Advice Records – CSIS PPU 005 ) to conduct security screening verifications, inquiries and/or assessments in accordance with the Policy on Government Security. Information may be shared with the Canadian Human Rights Commission ( Human Rights Litigation Records – CHRC DRP 020 , Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 ), the Public Service Labour Relations and Employment Board ( Complaint/Grievance Mediation Records – PSLRB ROP 579 ), Justice Canada ( Litigation Services Records – JUS 3.0.5 ) or the Security Intelligence Review Committee ( Complaints Records – SIR COM 001 ) when an individual challenges a decision to deny, suspend or revoke a the required security status or security clearance. Information may be disclosed to the Privy Council Office ( Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 ) should the individual pose a potential risk to national security or is part of a national security-related investigation. The security screening status of an individual may be shared internally within institutions with human resource officials to update the individual's personnel file ( Employee Personnel Record – PSE 901 , Governor in Council Appointments – PSU 918 , Members of Boards Committees and Councils – PSU 919 ). Information may be shared within or between government institutions for staffing purposes ( Staffing – PSE 902 ). Information may be shared within institutions with departmental security officials for issuance of access cards and badges ( Physical Access Controls PSU 907 ). Information may be shared within institutions with departmental security officials in cases of adverse information for investigation ( Security – PRN 931 or Security Incidents and Privacy Breaches – PSU 939 ). Biographical information, including name, date of birth, employment and/or educational history, may be shared with individuals or entities outside the government institution to confirm identity and conduct required inquiries or verifications including: authorized credit reporting agencies, personal and/or professional referees, and educational institutions and/or professional organizations. Information, including the results of security screening checks, may be disclosed to an individual’s manager, labour relations advisors, and/or an institutional security screening advisory board, on a need to know basis, when a decision to deny, revoke or suspend pending an investigation is being considered. Information, including completed security screening forms, the results of security screening checks and decisions made by a department may be shared between institutional security officials to enable transferability of security screening and to help ensure that individuals are not engaged by another government institution without regard to the circumstances leading to any previous denial or revocation which may have taken place in another institution. Select anonymized information may be used or disclosed for program evaluation.  |  Links: Canadian Criminal Real Time Identification Services – RCMP OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Personnel Security Records – RCMP ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Security Assessments/Advice Records – CSIS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-en.php); Human Rights Litigation Records – CHRC DRP 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Complaint/Grievance Mediation Records – PSLRB ROP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_e.asp); Litigation Services Records – JUS 3.0.5 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/p3.html); Complaints Records – SIR COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-eng.html); Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Employee Personnel Record – PSE 901 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Governor in Council Appointments – PSU 918 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Members of Boards Committees and Councils – PSU 919 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Staffing – PSE 902 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Physical Access Controls PSU 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu907); Security – PRN 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-classes-records.html); Security Incidents and Privacy Breaches – PSU 939 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp)</t>
+          <t>Where required, personal information may be shared in accordance with the institution's enabling legislation and within the parameters of the Privacy Act, with the Royal Canadian Mounted Police ( Canadian Criminal Real Time Identification Services – RCMP OPS 1214 and Personnel Security Records – RCMP ADM 445 ) and the Canadian Security Intelligence Service ( Security Assessments/Advice Records – CSIS PPU 005 ) to conduct security screening verifications, inquiries and/or assessments in accordance with the Policy on Government Security. Information may be shared with the Canadian Human Rights Commission ( Human Rights Litigation Records – CHRC DRP 020 , Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 ), the Public Service Labour Relations and Employment Board ( Complaint/Grievance Mediation Records – PSLRB ROP 579 ), Justice Canada ( Litigation Services Records – JUS 3.0.5 ) or the Security Intelligence Review Committee ( Complaints Records – SIR COM 001 ) when an individual challenges a decision to deny, suspend or revoke a the required security status or security clearance. Information may be disclosed to the Privy Council Office ( Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 ) should the individual pose a potential risk to national security or is part of a national security-related investigation. The security screening status of an individual may be shared internally within institutions with human resource officials to update the individual's personnel file ( Employee Personnel Record – PSE 901 , Governor in Council Appointments – PSU 918 , Members of Boards Committees and Councils – PSU 919 ). Information may be shared within or between government institutions for staffing purposes ( Staffing – PSE 902 ). Information may be shared within institutions with departmental security officials for issuance of access cards and badges ( Physical Access Controls PSU 907 ). Information may be shared within institutions with departmental security officials in cases of adverse information for investigation ( Security – PRN 931 or Security Incidents and Privacy Breaches – PSU 939 ). Biographical information, including name, date of birth, employment and/or educational history, may be shared with individuals or entities outside the government institution to confirm identity and conduct required inquiries or verifications including: authorized credit reporting agencies, personal and/or professional referees, and educational institutions and/or professional organizations. Information, including the results of security screening checks, may be disclosed to an individual’s manager, labour relations advisors, and/or an institutional security screening advisory board, on a need to know basis, when a decision to deny, revoke or suspend pending an investigation is being considered. Information, including completed security screening forms, the results of security screening checks and decisions made by a department may be shared between institutional security officials to enable transferability of security screening and to help ensure that individuals are not engaged by another government institution without regard to the circumstances leading to any previous denial or revocation which may have taken place in another institution. Select anonymized information may be used or disclosed for program evaluation.  |  Links: Canadian Criminal Real Time Identification Services – RCMP OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Personnel Security Records – RCMP ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-eng.htm); Security Assessments/Advice Records – CSIS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-en.php); Human Rights Litigation Records – CHRC DRP 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Human Rights Complaints Dispute Resolution Records – CHRC DRP 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-eng.pdf); Complaint/Grievance Mediation Records – PSLRB ROP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_e.asp); Litigation Services Records – JUS 3.0.5 (http://www.justice.gc.ca/eng/trans/atip-aiprp/infosource/p3.html); Complaints Records – SIR COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-eng.html); Security and Intelligence Information Files – Personal Information Bank– PCO PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=eng&amp;page=information&amp;sub=publications&amp;doc=info-source/index-eng.htm); Employee Personnel Record – PSE 901 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Governor in Council Appointments – PSU 918 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Members of Boards Committees and Councils – PSU 919 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Staffing – PSE 902 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp); Physical Access Controls PSU 907 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu907); Security – PRN 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-classes-records.html); Security Incidents and Privacy Breaches – PSU 939 (https://www.tbs-sct.gc.ca/hgw-cgf/oversight-surveillance/atip-aiprp/ai/spib-frpo-eng.asp)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Au besoin, les renseignements personnels peuvent être communiqués conformément à la loi habilitante de l'institution et dans les paramètres de la Loi sur la protection des renseignements personnels, à la Gendarmerie royale du Canada ( Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 et Fichiers sur la sécurité du personnel GRC ADM 445 ) et au Service canadien du renseignement de sécurité ( Évaluations de sécurité/Avis – SCRS PPU 005 ) pour qu’ils effectuent des vérifications, des enquêtes et/ou des évaluations de filtrage de sécurité, conformément à la Politique sur la sécurité du gouvernement. Les informations peuvent être communiquées à la Commission canadienne des droits de la personne ( Contentieux en matière de droits de la personne – CCDP REG 020 , Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 ), Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 ) , à la Commission des relations de travail et de l’emploi dans la fonction publique, au ministère de la Justice Canada ( Services de contentieux – JUS 3.0.5 ) ou au Comité de surveillance des activités de renseignement de sécurité ( Plaintes – SCA COM 001 ) lorsqu’une personne conteste une décision visant à refuser, à suspendre ou à révoquer une autorisation de sécurité ou une autorisation d’accès aux sites ou au Bureau du Conseil privé ( Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 ) si la personne pose un risque potentiel à la sécurité nationale ou fait l’objet d’une enquête liée à la sécurité nationale. La cote de filtrage de sécurité d’une personne peut être communiquée à l’interne au sein des institutions aux responsables des ressources humaines afin de mettre à jour le dossier personnel de la personne concernée ( Dossier personnel d’un employé – POE 901, Nominations par le Gouverneur en conseil – POU 918 , Membres de conseils d’administration, de comités et de conseils – POU 919 ). Les informations peuvent être communiquées au sein d’une institution fédérale et entre elles aux fins de dotation ( Dotation – POE 902 ). Les informations peuvent être communiquées au sein des institutions aux responsables de la sécurité ministérielle pour la délivrance de cartes d’accès et de laissez-passer ( Contrôles d’accès physique – POU 907 ). Les informations peuvent être communiquées pour enquête au sein des institutions aux responsables de la sécurité ministérielle dans les cas d’informations préjudiciables ( Sécurité – NDP 931 ou Incidents de sécurité et atteintes à la vie privée – POU 939 ). Les informations peuvent être communiquées à des entités de l’extérieur de l’institution fédérale, y compris les bureaux de crédit pour qu’elles réalisent des enquêtes sur la situation financière. Les renseignements, y compris les résultats du filtrage de sécurité, peuvent être communiqués au gestionnaire d’une personne, aux conseillers en relations de travail, et/ou au conseil consultatif du filtrage de sécurité institutionnel, en fonction du besoin de savoir, lorsqu’une décision de refuser, de révoquer ou de suspendre en attente d’une enquête fait l’objet d’un examen. Les renseignements, y compris les formulaires d’enquête de sécurité dûment remplis, les résultats des vérifications du filtrage de sécurité et les décisions prises par un ministère peuvent être communiqués entre les responsables de sécurité institutionnels afin de permettre la transférabilité du filtrage de sécurité et d’aider à veiller à ce que les personnes ne soient pas engagées par une institution fédérale ou un ministère compte non tenu des circonstances menant à une révocation ou à un refus antérieur qui pourrait avoir eu lieu dans une autre institution. Certaines informations rendues anonymes peuvent être utilisées ou divulguées pour l’évaluation d’un programme.  |  Links: Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Fichiers sur la sécurité du personnel GRC ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Évaluations de sécurité/Avis – SCRS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-fr.php); Contentieux en matière de droits de la personne – CCDP REG 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_f.asp); Services de contentieux – JUS 3.0.5 (http://www.justice.gc.ca/fra/trans/aiprp-atip/infosource/p3.html); Plaintes – SCA COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-fra.html); Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=fra&amp;page=information&amp;sub=publications&amp;doc=info-source/index-fra.htm); Dossier personnel d’un employé – POE 901, Nominations par le Gouverneur en conseil – POU 918 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Membres de conseils d’administration, de comités et de conseils – POU 919 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html); Contrôles d’accès physique – POU 907 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907); Sécurité – NDP 931 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/categories-documents-ordinaires.html); Incidents de sécurité et atteintes à la vie privée – POU 939 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/fichiers-renseignements-personnels-ordinaires.html)</t>
+          <t>Au besoin, les renseignements personnels peuvent être communiqués conformément à la loi habilitante de l'institution et dans les paramètres de la Loi sur la protection des renseignements personnels, à la Gendarmerie royale du Canada ( Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 et Fichiers sur la sécurité du personnel GRC ADM 445 ) et au Service canadien du renseignement de sécurité ( Évaluations de sécurité/Avis – SCRS PPU 005 ) pour qu’ils effectuent des vérifications, des enquêtes et/ou des évaluations de filtrage de sécurité, conformément à la Politique sur la sécurité du gouvernement. Les informations peuvent être communiquées à la Commission canadienne des droits de la personne ( Contentieux en matière de droits de la personne – CCDP REG 020 , Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 ), Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 ), à la Commission des relations de travail et de l’emploi dans la fonction publique, au ministère de la Justice Canada ( Services de contentieux – JUS 3.0.5 ) ou au Comité de surveillance des activités de renseignement de sécurité ( Plaintes – SCA COM 001 ) lorsqu’une personne conteste une décision visant à refuser, à suspendre ou à révoquer une autorisation de sécurité ou une autorisation d’accès aux sites ou au Bureau du Conseil privé ( Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 ) si la personne pose un risque potentiel à la sécurité nationale ou fait l’objet d’une enquête liée à la sécurité nationale. La cote de filtrage de sécurité d’une personne peut être communiquée à l’interne au sein des institutions aux responsables des ressources humaines afin de mettre à jour le dossier personnel de la personne concernée ( Dossier personnel d’un employé – POE 901 , Nominations par le Gouverneur en conseil – POU 918 , Membres de conseils d’administration, de comités et de conseils – POU 919 ). Les informations peuvent être communiquées au sein d’une institution fédérale et entre elles aux fins de dotation ( Dotation – POE 902 ). Les informations peuvent être communiquées au sein des institutions aux responsables de la sécurité ministérielle pour la délivrance de cartes d’accès et de laissez-passer ( Contrôles d’accès physique – POU 907 ). Les informations peuvent être communiquées pour enquête au sein des institutions aux responsables de la sécurité ministérielle dans les cas d’informations préjudiciables ( Sécurité – NDP 931 ou Incidents de sécurité et atteintes à la vie privée – POU 939 ). Les informations peuvent être communiquées à des entités de l’extérieur de l’institution fédérale, y compris les bureaux de crédit pour qu’elles réalisent des enquêtes sur la situation financière. Les renseignements, y compris les résultats du filtrage de sécurité, peuvent être communiqués au gestionnaire d’une personne, aux conseillers en relations de travail, et/ou au conseil consultatif du filtrage de sécurité institutionnel, en fonction du besoin de savoir, lorsqu’une décision de refuser, de révoquer ou de suspendre en attente d’une enquête fait l’objet d’un examen. Les renseignements, y compris les formulaires d’enquête de sécurité dûment remplis, les résultats des vérifications du filtrage de sécurité et les décisions prises par un ministère peuvent être communiqués entre les responsables de sécurité institutionnels afin de permettre la transférabilité du filtrage de sécurité et d’aider à veiller à ce que les personnes ne soient pas engagées par une institution fédérale ou un ministère compte non tenu des circonstances menant à une révocation ou à un refus antérieur qui pourrait avoir eu lieu dans une autre institution. Certaines informations rendues anonymes peuvent être utilisées ou divulguées pour l’évaluation d’un programme.  |  Links: Services canadiens d'identification criminelle en temps réel – GRC OPS 1214 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Fichiers sur la sécurité du personnel GRC ADM 445 (http://www.rcmp-grc.gc.ca/atip-aiprp/infosource/cor-cds-fra.htm); Évaluations de sécurité/Avis – SCRS PPU 005 (https://www.csis.gc.ca/tp/nfsrc-fr.php); Contentieux en matière de droits de la personne – CCDP REG 020 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Règlement des différends faisant l’objet d’une plainte — Droits de la personne – CCDP REG 010 (http://www.chrc-ccdp.gc.ca/sites/default/files/info_source2016-fra.pdf); Médiation des plaintes et des griefs – fichier de renseignements personnels – CRTFP OGP 579 (http://pslrb-crtfp.gc.ca/reports/1314/infosource_f.asp); Services de contentieux – JUS 3.0.5 (http://www.justice.gc.ca/fra/trans/aiprp-atip/infosource/p3.html); Plaintes – SCA COM 001 (http://www.sirc-csars.gc.ca/prddpr/is/2013/index-fra.html); Fichiers d’information sur la sécurité et le renseignement – Fichier de renseignements personnels – BCP PPU 005 (http://www.pco-bcp.gc.ca/index.asp?lang=fra&amp;page=information&amp;sub=publications&amp;doc=info-source/index-fra.htm); Dossier personnel d’un employé – POE 901 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe901); Nominations par le Gouverneur en conseil – POU 918 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou918); Membres de conseils d’administration, de comités et de conseils – POU 919 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou919); Dotation – POE 902 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902); Contrôles d’accès physique – POU 907 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou907); Sécurité – NDP 931 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-renseignements-personnels/acces-information/info-source/categories-documents-ordinaires.html#ndp931); Incidents de sécurité et atteintes à la vie privée – POU 939 (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou939)</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4609,6 +4783,9 @@
           <t>98/001</t>
         </is>
       </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu917</t>
@@ -4636,6 +4813,7 @@
           <t>PSU 907</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>psu907</t>
@@ -4643,7 +4821,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>poe907</t>
+          <t>pou907</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4676,6 +4854,7 @@
           <t>Ce fichier de renseignements personnels correspondait auparavant à deux fichiers de renseignements personnels distincts : Surveillance vidéo, registres de contrôle d’accès des visiteurs et laissez-passer POU 907 et Cartes d'identification et laissez-passer POE 917).</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Employees, and those on assignment or contract and visitors who require access to a government institution or any other person within proximity of video surveillance recording capabilities.</t>
@@ -4701,6 +4880,7 @@
           <t>The  information may be used or disclosed to assist security officials in the  monitoring of activities and/or the issuance of access passes. Information may  be used for identification purposes in support of personnel security screening.  Information may be used to support compliance with other relevant Treasury Board policy instruments and policy directions. Additionally, records and recordings may record entry  and exit times from facilities and may be used in the event of security-related  incidents such as thefts or emergency situations. In such cases, this  information may be shared with appropriate law enforcement agencies, emergency  workers, appropriate staff relations officers, or investigative bodies for  further investigations, charges or disciplinary actions (refer to Security  Incidents and Privacy Breaches PSU 939 and Discipline  PSE 911 ). Video information that reveals evidence of illegal activity,  employee misconduct or accidents may be disclosed to appropriate staff  relations, facility owners, enforcement or investigative bodies for further  investigations, charges or disciplinary actions.  |  Links: Security  Incidents and Privacy Breaches PSU 939 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#psu939); Discipline  PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4738,7 +4918,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907</t>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#pou907</t>
         </is>
       </c>
     </row>
@@ -4758,6 +4938,7 @@
           <t>PSU 912</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>psu912</t>
@@ -4788,11 +4969,15 @@
           <t>Ce fichier décrit les renseignements contenus dans les ententes conclues entre les institutions fédérales, et une personne ou une société, afin de fournir des biens ou des services, de construire des ouvrages ou de louer des biens réels. Les renseignements personnels peuvent comprendre le nom, les coordonnées (y compris le nom commercial), les renseignements biographiques, les renseignements sur les études, les renseignements financiers, les évaluations/analyses, le numéro d’assurance sociale (NAS), un autre numéro d’identification (p. ex., numéro d’entreprise), et la signature.</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Individuals representing themselves or employed through private companies (including temporary help services) who have submitted responses to Requests for Proposals and who have been engaged through contracts or standing offers with government institutions and individuals who are provided as professional references.</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Personal information is used to manage the contracting process, which includes the request for and receipt of proposals, evaluation of bids, selection of contractor, preparation, negotiation, execution, and award of contract, the disbursement of funds for services, deliverables, or both as specified within the contract, and post-contract evaluation. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority. The SIN is collected pursuant to the Income Tax Act.</t>
@@ -4808,6 +4993,7 @@
           <t>Information is used to maintain an inventory of potential contractors. Information may also be used to recover overpayments and debts owed to the Crown and, where applicable, to enable execution of orders of garnishment, attachment, or diversion of funds in accordance with the Garnishment, Attachment and Pension Diversion Act and related regulations. Information may be used to confirm the identity of contractors (where required) for access to governmental and institutional websites and databases and for the loan of equipment and/or supplies. Information, including the Social Insurance Number and Business Number, is disclosed to the Canada Revenue Agency in T4A-NR Supplementary and T1204 slips (refer to Individual Returns and Payment Processing – CRA PPU 005 and Business Returns and Payment Processing – CRA PPU 047 ) and the Province of Quebec (if applicable) for tax purposes. The information may be shared with/described in Standard Personal Information Banks Accounts Payable - PSU 931 and Accounts Receivable - PSU 932 for payment administration. Selected information on contracts for $10,000 or more, including the fact that a contractor is a former public servant in receipt of a Public Service Superannuation Act pension, may be made available on institutions’ websites, in compliance with proactive disclosure procedures. Information may also be used or disclosed for evaluation or reporting purposes.  |  Links: Individual Returns and Payment Processing – CRA PPU 005 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Business Returns and Payment Processing – CRA PPU 047 (http://www.cra-arc.gc.ca/gncy/tp/nfsrc/nfsrc-eng.html); Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable - PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4865,6 +5051,7 @@
           <t>PSU 914</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>psu914</t>
@@ -4915,6 +5102,7 @@
           <t>Members of the public, representatives of private sector organizations and other government institutions (i.e., municipal, provincial/territorial, and international), employees and other representatives of government institutions, who have requested information from, or submitted information to, a government institution; parents and guardians of minors; employees and other individuals with access to institutional networks, including individuals who have prepared information for dissemination, such as publication on the institution’s extranet or internet sites or who act as contact points within the institution.</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Personal information is used to disseminate information about the functions, programs, and activities of the institution, including about employees of the institution. For many institutions, personal information is collected under the authority of the Financial Administration Act (FAA), and in accordance with the Communications Policy of the Government of Canada. For those institutions not subject to the FAA or the Communications Policy of the Government of Canada, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -4930,6 +5118,7 @@
           <t>The names, photographs, recordings and other personal information about individuals who work for the institution may be included in documentation posted on the institution’s extranet or Internet sites; e.g., within speeches, newsletters, etc. With consent of the individual, information may be shared with other areas of the institution for program-specific mailing/distribution lists and/or telephone lists. Information may be used to moderate public discussion on the social media platforms used by the institution. Responses to enquiries and any other relevant information are accounted for by the institution-specific personal information bank related to the program area that sent the response. Requests for information may be transferred when the requested information, e.g., inquiry or complaint, falls under the responsibility of another institution, refer to Executive Correspondence - PSU 902 . Some information may also be posted on government institutions’ websites for proactive disclosure purposes. Information may also be used or disclosed to provide statistical reports to management as well as for program evaluation.  |  Links: Executive Correspondence - PSU 902 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu902)</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -4987,6 +5176,7 @@
           <t>PSU 948</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>psu914a</t>
@@ -5017,6 +5207,9 @@
           <t>Ce fichier contient les renseignements liés à la gestion des biens immobiliers fédéraux et autres biens immobiliers utilisés ou acquis par une institution fédérale. Les biens immobiliers font référence à tout droit, intérêt ou profit dans des terres, y compris les mines, les minéraux et les améliorations qui leur sont apportées, sur ou sous terre. Les renseignements personnels peuvent comprendre le nom, les renseignements biographiques, les coordonnées, la taille de la famille, les antécédents en matière de crédit, les modalités relativement à la location, les renseignements financiers, les renseignements concernant les transactions liées à la propriété, y compris les évaluations, et une description de la propriété, y compris des photos.</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Former or current tenants or applicants for tenancy of federal real property, real property owners, licensees, lessees, and property appraisers.</t>
@@ -5042,6 +5235,7 @@
           <t>Information may be used or disclosed for the following purposes: to collect debts owed by tenants as a result of their tenancy; for credit checks; for property tax payments, that is, information may be disclosed to municipalities in which the properties are located for tax assessments and administration of the payments-in-lieu of taxes program and for evaluation or reporting to senior management. Information may be shared with or described in the Standard Personal Information Banks Accounts Payable – PSU 931 , and Accounts Receivable – PSU 932 .  |  Links: Accounts Payable – PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable – PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5099,6 +5293,7 @@
           <t>PSE 920</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>pse920</t>
@@ -5169,6 +5364,7 @@
           <t>The information may be used or disclosed for the following purposes: reporting to senior management, evaluation and audit. Some elements of the information may be published on the Internet, intranet or other medium. Information may be shared with PSE 904 Pay and Benefit in cases where awards qualify as income. Information may be shared with PSE 901 Employee Personnel Record.</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5226,6 +5422,7 @@
           <t>PSU 910</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>psu910</t>
@@ -5256,6 +5453,9 @@
           <t>Ces renseignements sont utilisés pour consigner des données sur les processus liés à la réinstallation d’employés et de leur famille. Les renseignements personnels recueillis comprennent le nom de la personne, le titre de son poste, le nom de son organisation, son numéro de téléphone au bureau et l’adresse du bureau, la classification et le niveau de son poste, son code d’identification de dossier personnel, le nom du fonctionnaire ou du gestionnaire de l’institution à qui les pouvoirs ont été délégués, des signatures, le nom de son conjoint ou de son conjoint de fait, le nom de ses enfants et de membres de sa famille élargie, ses besoins spéciaux sur le plan médical dont on pourrait avoir à tenir compte, ses relevés mensuels de cartes de crédit, ses déclarations personnelles de dépenses lorsqu’il n’est pas possible d’obtenir des reçus ou que les reçus ont été détruits par inadvertance, les coûts liés à son hypothèque ou à son loyer, les frais juridiques et les frais immobiliers.</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Employees who relocate and their spouses or common-law partners, their children and/or extended family members. Also includes individuals representing third party suppliers, such as moving and storage companies.</t>
@@ -5281,6 +5481,7 @@
           <t>Non-personal information may be used to provide reports on employee relocations to management. The information may also be used for research, planning, audit and evaluation purposes.</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5296,6 +5497,7 @@
           <t>98/001 and 99/004</t>
         </is>
       </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>PRN 936</t>
@@ -5470,6 +5672,7 @@
           <t>PSE 902</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>pse902</t>
@@ -5477,7 +5680,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>poe9021</t>
+          <t>poe902</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5510,11 +5713,13 @@
           <t>Les personnes qui demandent des renseignements décrits dans ce fichier doivent fournir un numéro de concours, s’il y a lieu.</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Employees of the institution and other individuals who apply for employment in the institution including through recruitment initiatives, as well as individuals who provide references or are supervisors of applicants.</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Personal information is used to administer recruitment and staffing activities in government institutions, which includes maintaining an inventory of potential candidates for future staffing actions. For most government institutions, personal information is collected pursuant to the Public Service Employment Act, the Employment Equity Act, and the Canadian Human Rights Act (section 16). For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -5530,6 +5735,7 @@
           <t>Information may be disclosed to the Public Service Commission, Treasury Board Secretariat and other government institutions for recruitment, employment equity, and staffing purposes, including complaints (refer to Institution-Specific Personal Information Banks: for the Public Service Commission of Canada: Applicant Inventories and Referrals - PSC PPU 015 ; Assessment by the Personnel Psychology Centre - PSC PCU 025 , Second Language Evaluation (SLE) Test Results - PSC PPU 030 , Executive Resourcing - PSC PCE 746 , Analytical Environment - PSC PCE 761 , and Investigations, Mediation and Conciliation - PSC PPU 010 ; for Treasury Board of Canada Secretariat: Employment Equity Data Bank - TBS PCE 739 and Workforce Adjustment Monitoring (WFAM) System - TBS PCE 804 ). Information relating to staffing complaints may be shared with the Public Service Commission (refer to Institution-Specific Personal Information Bank Investigations, Mediation and Conciliation - PSC PPU 010 ) and the Federal Public Service Staffing Tribunal with Public Sector Labour Relations and Employment Board, when required. On request, selected information may be disclosed to a participant in a staffing process. Information may also be shared with third party service providers to manage recruitment initiatives. Information may also be used or disclosed for human resources planning and studies (refer to Standard Personal Information Bank Human Resources Planning - PSU 935 ) and staffing decisions may also be described in Standard Personal Information Bank Employee Personnel Record - PSE 901 . Voluntary self identification information relating to employment equity programs and services is also described in Standard Personal Information Bank Employment Equity and Diversity - PSE 918 . Selected information about reclassifications may be proactively disclosed on government institutions’ websites. Information may also be used or disclosed for program evaluation and reporting purposes.  |  Links: Applicant Inventories and Referrals - PSC PPU 015 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Assessment by the Personnel Psychology Centre - PSC PCU 025 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Second Language Evaluation (SLE) Test Results - PSC PPU 030 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Executive Resourcing - PSC PCE 746 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Analytical Environment - PSC PCE 761 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Investigations, Mediation and Conciliation - PSC PPU 010 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Employment Equity Data Bank - TBS PCE 739 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg02-eng.asp); Workforce Adjustment Monitoring (WFAM) System - TBS PCE 804 (http://www.tbs-sct.gc.ca/atipo-baiprp/sfg-srg/sfg-srg00-eng.asp); Investigations, Mediation and Conciliation - PSC PPU 010 (http://www.psc-cfp.gc.ca/abt-aps/atip-aiprp/infosource/2012/index-eng.htm); Human Resources Planning - PSU 935 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu935); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901); Employment Equity and Diversity - PSE 918 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse918)</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5567,7 +5773,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9021</t>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe902</t>
         </is>
       </c>
     </row>
@@ -5587,6 +5793,7 @@
           <t>PSE 905</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>pse905</t>
@@ -5617,11 +5824,15 @@
           <t>Ce fichier décrit les renseignements personnels recueillis à l’appui du programme de formation et de perfectionnement d’une institution (p. ex., les programmes de mentorat et d’orientation des carrières, les affectations et les modalités de travail de perfectionnement, etc.). Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements sur les études, le numéro d’identification d’employé, des renseignements sur l’équité en emploi, les renseignements personnels de l’employé, les renseignements financiers, les renseignements biographiques, ainsi que les résultats de l’analyse et de la formation.</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Individuals who are employed by government institutions who register for training or development courses or programs.</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Personal information is used to register and pay for approved training and development activities. Where applicable, government institutions may receive information from the Canada School of Public Service or other course providers about registration costs and training results. For most government institutions, personal information is collected under the authority of the Public Service Staff Relations Act and the Public Service Employment Act. For those institutions not subject to these Acts, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -5637,6 +5848,7 @@
           <t>Information may be used to link voluntary self-identification data to information contained in other banks (refer to Standard Personal Information Bank Employment Equity and Diversity - PSE 918) for the purpose of implementing and evaluating government policies relating to employment equity and diversity. Some information may also be shared with/described in the Standard Personal Information Banks Accounts Receivable - PSU 932 , Employee Performance Management Program – PSE 912 and Employee Personnel Record - PSE 901 . Information may also be used or disclosed for program evaluation.  |  Links: Accounts Receivable - PSU 932 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932); Employee Performance Management Program – PSE 912 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse912); Employee Personnel Record - PSE 901 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse901)</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5694,6 +5906,7 @@
           <t>PSU 909</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>psu909</t>
@@ -5724,11 +5937,15 @@
           <t>Ce fichier décrit les renseignements sur les employés qui se déplacent pour des activités officielles de leur institution. Les renseignements personnels peuvent comprendre le nom, les coordonnées, les renseignements biographiques, le numéro d’identification d’employé, les renseignements personnels de l’employé, les renseignements financiers et sur le passeport/visa, les antécédents de voyage, les demandes d’indemnité de voyages, le logement, les repas et les préférences. Les employés en voyages peuvent également être tenus de fournir la date de naissance et le sexe lorsqu’ils font des préparatifs de voyages.</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Employees of government institutions, Ministers, Parliamentary Secretary, exempt staff, and other individuals (may include term or casual employees, temporary staff, volunteers, students, consultants and contractors, or witnesses) who travel on official institutional business, their spouses or common-law partners and dependants.</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Personal information is used to process travel requirements for individuals who travel on behalf of the institution. For most government institutions, personal information is collected under the authority of the Financial Administration Act. For those institutions not subject to the Act, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -5744,6 +5961,7 @@
           <t>Travel expenses incurred by the Minister, Parliamentary Secretary, exempt staff, and by senior level employees (i.e., Deputy Minister, Associate Deputy Minister, Assistant Deputy Minister, or equivalent) may be proactively disclosed on government institutions’ websites. Some institutions may share information with Public Works and Government Services Canada to establish the Traveller Profile (refer to Central Personal Information Bank Shared Travel Services Initiative (STSI) Traveller Profile - PWGSC PCE 706 ). In some instances, information may also be shared with the Department of Foreign Affairs and International Trade Canada (e.g., official delegations to events in foreign countries). Information may also be shared with/described in Standard Personal Information Banks Accounts Payable - PSU 931 and Accounts Receivable – PSU 93 2. Information may be used or disclosed for program evaluation and reporting purposes.  |  Links: Shared Travel Services Initiative (STSI) Traveller Profile - PWGSC PCE 706 (http://www.tpsgc-pwgsc.gc.ca/aiprp-atip/index-eng.html); Accounts Payable - PSU 931 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu931); Accounts Receivable – PSU 93 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu932)</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5759,6 +5977,7 @@
           <t>98/001 and 99/004</t>
         </is>
       </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>PRN 934, PRN 935</t>
@@ -5796,6 +6015,7 @@
           <t>PSE 915</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>pse915</t>
@@ -5846,6 +6066,7 @@
           <t>Current and former employees of government institutions, family members, and other individuals with whom the employee may have a business interest.</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Personal information is used to provide direction and authorizations, support decision on transfers, discipline and termination of employment, if conflict of interest exists, resolve situations of perceived, potential and actual conflicts of interest in current and post-employment This includes conflicts of interest in relation to 1) assets and liabilities, 2) gifts, hospitality and other benefits, 3) outside employment or activities, 4) preferential treatment and 5) solicitation. Personal information is also used in assessing the need for the establishment of a blind trust or for approving reimbursement for costs associated with such a divestment. Personal information is collected pursuant to section 5 and 6 of the PSDPA. Personal information is collected pursuant to sections 7 and 11.1 (1)(j) of the Financial Administration Act (FAA) for setting terms and conditions of employment. For those institutions not subject to the PSDPA or the FAA, consult the institution’s Access to Information and Privacy Coordinator to determine collection authority.</t>
@@ -5861,6 +6082,7 @@
           <t>In some cases, information may be disclosed to the Office of the Chief Human Resources Officer, Treasury Board Secretariat for the purpose of obtaining advice on possible conflicts of interest. In cases where an allegation of wrongdoing is made, information may be disclosed either to the Office of the Public Sector Integrity Commissioner of Canada, which may make recommendations where warranted to Deputy Heads of institutions, refer to Case Review and Investigation Files – PSIO PPU 005 or to the senior officer responsible for receiving and dealing with disclosures of wrongdoing in the government institution, refer to Disclosure of Wrongdoing in the Workplace – PSU 906 . Information may be shared with human resources officials where a conflict of interest results in discipline or termination of employment, refer to Discipline – PSE 911 . Information may also be used or disclosed for program evaluation, policy analysis, research, audit or statistical purposes.  |  Links: Case Review and Investigation Files – PSIO PPU 005 (http://www.psic.gc.ca/eng/about-us/publications#ATIP); Disclosure of Wrongdoing in the Workplace – PSU 906 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#psu906); Discipline – PSE 911 (https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse911)</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5886,6 +6108,7 @@
           <t>PRN 920, PRN 926</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse915</t>
@@ -5913,6 +6136,7 @@
           <t>PSE 908</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>pse908</t>
@@ -5940,9 +6164,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Les dossiers contenant des renseignements décrits dans ce fichier peuvent comprendre des rapports sur les accidents; des réclamations pour les dommages subis; des décisions du tribunal; des règlements des transactions et la correspondance concernant des accidents survenus à des véhicules, des bateaux, des embarcations et des avions loués ou appartenant à l’état, ainsi qu’à des véhicules, bateaux, embarcations et avions privés utilisés à des fins professionnelles. Les dossiers de santé et sécurité au travail ainsi que les dossiers d’autorisation de congés et de prestations liés à une blessure au travail ou à une maladie professionnelle sont décrits dans le fichier de renseignements personnels ordinaire, Santé et sécurité au travail – POE 907.  |  Links: Santé et sécurité au travail – POE 907. (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe9071)</t>
-        </is>
-      </c>
+          <t>Les dossiers contenant des renseignements décrits dans ce fichier peuvent comprendre des rapports sur les accidents; des réclamations pour les dommages subis; des décisions du tribunal; des règlements des transactions et la correspondance concernant des accidents survenus à des véhicules, des bateaux, des embarcations et des avions loués ou appartenant à l’état, ainsi qu’à des véhicules, bateaux, embarcations et avions privés utilisés à des fins professionnelles. Les dossiers de santé et sécurité au travail ainsi que les dossiers d’autorisation de congés et de prestations liés à une blessure au travail ou à une maladie professionnelle sont décrits dans le fichier de renseignements personnels ordinaire, Santé et sécurité au travail – POE 907.  |  Links: Santé et sécurité au travail – POE 907. (https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe907)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Employees of the institution.</t>
@@ -5968,6 +6195,7 @@
           <t>To determine liability for such accidents and to approve damage settlements.</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -5993,6 +6221,7 @@
           <t>PRN 922, PRN 945</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#pse908</t>
@@ -6020,6 +6249,7 @@
           <t>PSE 930</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>pse930</t>
@@ -6050,6 +6280,9 @@
           <t>Les dossiers contenant les renseignements décrits dans ce fichier peuvent renfermer des renseignements recueillis à partir d’enquêtes menées par des institutions fédérales auprès de leurs employés pour évaluer la demande de garderies en milieu de travail, à partir des dossiers des garderies en milieu de travail. Ces renseignements ont été compilés dans le but de déterminer l’aide financière permanente sur laquelle pourront compter les garderies pour ce qui est de la location des locaux, et d’évaluer la politique sur les garderies. Ils peuvent comprendre des données personnelles sur l’employé ou l’utilisateur, ou encore sur ses enfants, et peuvent porter sur la demande prévue en services de garderie, la probabilité qu’un employé inscrive un enfant dans une garderie parrainée par l’institution et les raisons qui pourraient l’inciter à l’y inscrire.</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>All federal employees included in Schedules I and IV of the Financial Administration Act.</t>
@@ -6075,6 +6308,7 @@
           <t>The information in these records will be used for administrative and statistical purposes associated with the establishment of a day care centre. It will also be used for the evaluation and monitoring of the federal public service workplace day care policy. The information may be disclosed to Treasury Board, the government institution, an authorized committee of the government institution, a custodian government institution and the Board of Directors of the Day Care Centre. Together with the linked information from the files identified below, this information will form the basis for tabulations of the extent and type of employee day care users.</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
           <t>For information about the length of time that specific types of common administrative records are maintained by a government institution, including the final disposition of those records, please contact the institution’s Access to Information and Privacy Coordinator.</t>
@@ -6113,44 +6347,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#poe930</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Categories of Personal Information</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Catégories de renseignements personnels</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/info-source/standard-personal-information-banks.html#categories</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/info-source/fichiers-renseignements-personnels-ordinaires.html#categories</t>
         </is>
       </c>
     </row>
